--- a/AAII_Financials/Quarterly/THCH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/THCH_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="92">
   <si>
     <t>THCH</t>
   </si>
@@ -656,199 +656,212 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>56800</v>
+        <v>60700</v>
       </c>
       <c r="E8" s="3">
-        <v>46500</v>
+        <v>57200</v>
       </c>
       <c r="F8" s="3">
-        <v>41600</v>
+        <v>46800</v>
       </c>
       <c r="G8" s="3">
-        <v>42200</v>
+        <v>41900</v>
       </c>
       <c r="H8" s="3">
-        <v>24700</v>
+        <v>42500</v>
       </c>
       <c r="I8" s="3">
-        <v>31000</v>
+        <v>24900</v>
       </c>
       <c r="J8" s="3">
+        <v>31200</v>
+      </c>
+      <c r="K8" s="3">
         <v>30900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>25100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>19300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>14600</v>
       </c>
-      <c r="N8" s="3">
-        <v>0</v>
-      </c>
       <c r="O8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>22300</v>
+        <v>25000</v>
       </c>
       <c r="E9" s="3">
-        <v>18000</v>
+        <v>22400</v>
       </c>
       <c r="F9" s="3">
-        <v>15400</v>
+        <v>18100</v>
       </c>
       <c r="G9" s="3">
-        <v>14600</v>
+        <v>15500</v>
       </c>
       <c r="H9" s="3">
+        <v>14700</v>
+      </c>
+      <c r="I9" s="3">
         <v>9300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
+        <v>10900</v>
+      </c>
+      <c r="K9" s="3">
         <v>10800</v>
       </c>
-      <c r="J9" s="3">
-        <v>10800</v>
-      </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>9000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>6700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>4900</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>34600</v>
+        <v>35700</v>
       </c>
       <c r="E10" s="3">
-        <v>28500</v>
+        <v>34800</v>
       </c>
       <c r="F10" s="3">
-        <v>26200</v>
+        <v>28700</v>
       </c>
       <c r="G10" s="3">
-        <v>27600</v>
+        <v>26400</v>
       </c>
       <c r="H10" s="3">
-        <v>15500</v>
+        <v>27800</v>
       </c>
       <c r="I10" s="3">
-        <v>20200</v>
+        <v>15600</v>
       </c>
       <c r="J10" s="3">
+        <v>20300</v>
+      </c>
+      <c r="K10" s="3">
         <v>20100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>16100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>12600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>9700</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -864,8 +877,9 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -905,8 +919,11 @@
       <c r="O12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -946,63 +963,69 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>600</v>
+        <v>1800</v>
       </c>
       <c r="E14" s="3">
         <v>600</v>
       </c>
       <c r="F14" s="3">
+        <v>600</v>
+      </c>
+      <c r="G14" s="3">
         <v>200</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>100</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>4</v>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E15" s="3">
         <v>4800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>4600</v>
       </c>
-      <c r="F15" s="3">
-        <v>16400</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>4</v>
+      <c r="G15" s="3">
+        <v>16500</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>4</v>
@@ -1016,8 +1039,8 @@
       <c r="K15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
+      <c r="L15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1028,8 +1051,11 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1042,90 +1068,97 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>81600</v>
+        <v>82900</v>
       </c>
       <c r="E17" s="3">
-        <v>64500</v>
+        <v>82100</v>
       </c>
       <c r="F17" s="3">
-        <v>59800</v>
+        <v>64900</v>
       </c>
       <c r="G17" s="3">
-        <v>63000</v>
+        <v>60200</v>
       </c>
       <c r="H17" s="3">
-        <v>47500</v>
+        <v>63400</v>
       </c>
       <c r="I17" s="3">
-        <v>49600</v>
+        <v>47800</v>
       </c>
       <c r="J17" s="3">
+        <v>50000</v>
+      </c>
+      <c r="K17" s="3">
         <v>48800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>40700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>29700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>23000</v>
       </c>
-      <c r="N17" s="3">
-        <v>0</v>
-      </c>
       <c r="O17" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-24700</v>
+        <v>-22200</v>
       </c>
       <c r="E18" s="3">
-        <v>-18000</v>
+        <v>-24900</v>
       </c>
       <c r="F18" s="3">
         <v>-18100</v>
       </c>
       <c r="G18" s="3">
-        <v>-20800</v>
+        <v>-18300</v>
       </c>
       <c r="H18" s="3">
-        <v>-22700</v>
+        <v>-20900</v>
       </c>
       <c r="I18" s="3">
-        <v>-18600</v>
+        <v>-22900</v>
       </c>
       <c r="J18" s="3">
+        <v>-18700</v>
+      </c>
+      <c r="K18" s="3">
         <v>-17900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-15600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-10400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-8500</v>
       </c>
-      <c r="N18" s="3">
-        <v>0</v>
-      </c>
       <c r="O18" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1141,60 +1174,64 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>600</v>
+      </c>
+      <c r="E20" s="3">
         <v>-6100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-5500</v>
       </c>
-      <c r="F20" s="3">
-        <v>-12000</v>
-      </c>
       <c r="G20" s="3">
+        <v>-12100</v>
+      </c>
+      <c r="H20" s="3">
         <v>-5600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-800</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>-500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>400</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-30600</v>
+        <v>-21300</v>
       </c>
       <c r="E21" s="3">
-        <v>-18900</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>4</v>
+        <v>-30800</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-19100</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>4</v>
@@ -1223,16 +1260,19 @@
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>600</v>
+      </c>
+      <c r="E22" s="3">
         <v>700</v>
-      </c>
-      <c r="E22" s="3">
-        <v>600</v>
       </c>
       <c r="F22" s="3">
         <v>600</v>
@@ -1241,17 +1281,17 @@
         <v>600</v>
       </c>
       <c r="H22" s="3">
+        <v>600</v>
+      </c>
+      <c r="I22" s="3">
         <v>500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>200</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
       <c r="L22" s="3">
         <v>0</v>
       </c>
@@ -1264,49 +1304,55 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-31400</v>
+        <v>-22200</v>
       </c>
       <c r="E23" s="3">
-        <v>-24100</v>
+        <v>-31600</v>
       </c>
       <c r="F23" s="3">
-        <v>-30800</v>
+        <v>-24300</v>
       </c>
       <c r="G23" s="3">
-        <v>-26900</v>
+        <v>-31000</v>
       </c>
       <c r="H23" s="3">
-        <v>-24200</v>
+        <v>-27100</v>
       </c>
       <c r="I23" s="3">
-        <v>-20900</v>
+        <v>-24400</v>
       </c>
       <c r="J23" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="K23" s="3">
         <v>-18900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-15600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-10900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-8100</v>
       </c>
-      <c r="N23" s="3">
-        <v>0</v>
-      </c>
       <c r="O23" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1346,8 +1392,11 @@
       <c r="O24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1387,90 +1436,99 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-31400</v>
+        <v>-22200</v>
       </c>
       <c r="E26" s="3">
-        <v>-24100</v>
+        <v>-31600</v>
       </c>
       <c r="F26" s="3">
-        <v>-30800</v>
+        <v>-24300</v>
       </c>
       <c r="G26" s="3">
-        <v>-26900</v>
+        <v>-31000</v>
       </c>
       <c r="H26" s="3">
-        <v>-24200</v>
+        <v>-27100</v>
       </c>
       <c r="I26" s="3">
-        <v>-20900</v>
+        <v>-24400</v>
       </c>
       <c r="J26" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="K26" s="3">
         <v>-18900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-15600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-10900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-8100</v>
       </c>
-      <c r="N26" s="3">
-        <v>0</v>
-      </c>
       <c r="O26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-31600</v>
+        <v>-22300</v>
       </c>
       <c r="E27" s="3">
-        <v>-24100</v>
+        <v>-31800</v>
       </c>
       <c r="F27" s="3">
-        <v>-30900</v>
+        <v>-24300</v>
       </c>
       <c r="G27" s="3">
-        <v>-26800</v>
+        <v>-31100</v>
       </c>
       <c r="H27" s="3">
-        <v>-24000</v>
+        <v>-27000</v>
       </c>
       <c r="I27" s="3">
-        <v>-20800</v>
+        <v>-24200</v>
       </c>
       <c r="J27" s="3">
+        <v>-20900</v>
+      </c>
+      <c r="K27" s="3">
         <v>-19100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-15300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-10900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-8000</v>
       </c>
-      <c r="N27" s="3">
-        <v>0</v>
-      </c>
       <c r="O27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1510,8 +1568,11 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1551,8 +1612,11 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1592,8 +1656,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1633,90 +1700,99 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E32" s="3">
         <v>6100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>5500</v>
       </c>
-      <c r="F32" s="3">
-        <v>12000</v>
-      </c>
       <c r="G32" s="3">
+        <v>12100</v>
+      </c>
+      <c r="H32" s="3">
         <v>5600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>800</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-400</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-31600</v>
+        <v>-22300</v>
       </c>
       <c r="E33" s="3">
-        <v>-24100</v>
+        <v>-31800</v>
       </c>
       <c r="F33" s="3">
-        <v>-30900</v>
+        <v>-24300</v>
       </c>
       <c r="G33" s="3">
-        <v>-26800</v>
+        <v>-31100</v>
       </c>
       <c r="H33" s="3">
-        <v>-24000</v>
+        <v>-27000</v>
       </c>
       <c r="I33" s="3">
-        <v>-20800</v>
+        <v>-24200</v>
       </c>
       <c r="J33" s="3">
+        <v>-20900</v>
+      </c>
+      <c r="K33" s="3">
         <v>-19100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-15300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-10900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-8000</v>
       </c>
-      <c r="N33" s="3">
-        <v>0</v>
-      </c>
       <c r="O33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1756,95 +1832,104 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-31600</v>
+        <v>-22300</v>
       </c>
       <c r="E35" s="3">
-        <v>-24100</v>
+        <v>-31800</v>
       </c>
       <c r="F35" s="3">
-        <v>-30900</v>
+        <v>-24300</v>
       </c>
       <c r="G35" s="3">
-        <v>-26800</v>
+        <v>-31100</v>
       </c>
       <c r="H35" s="3">
-        <v>-24000</v>
+        <v>-27000</v>
       </c>
       <c r="I35" s="3">
-        <v>-20800</v>
+        <v>-24200</v>
       </c>
       <c r="J35" s="3">
+        <v>-20900</v>
+      </c>
+      <c r="K35" s="3">
         <v>-19100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-15300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-10900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-8000</v>
       </c>
-      <c r="N35" s="3">
-        <v>0</v>
-      </c>
       <c r="O35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1860,8 +1945,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1877,31 +1963,32 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>35300</v>
+        <v>64200</v>
       </c>
       <c r="E41" s="3">
-        <v>50300</v>
+        <v>35500</v>
       </c>
       <c r="F41" s="3">
-        <v>33000</v>
+        <v>50700</v>
       </c>
       <c r="G41" s="3">
-        <v>52800</v>
+        <v>33200</v>
       </c>
       <c r="H41" s="3">
-        <v>39400</v>
+        <v>53200</v>
       </c>
       <c r="I41" s="3">
-        <v>54000</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>4</v>
+        <v>39600</v>
+      </c>
+      <c r="J41" s="3">
+        <v>54300</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>4</v>
@@ -1918,25 +2005,28 @@
       <c r="O41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>18800</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>34400</v>
+        <v>19000</v>
       </c>
       <c r="F42" s="3">
-        <v>51400</v>
+        <v>34600</v>
       </c>
       <c r="G42" s="3">
-        <v>52100</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>4</v>
+        <v>51800</v>
+      </c>
+      <c r="H42" s="3">
+        <v>52500</v>
       </c>
       <c r="I42" s="3" t="s">
         <v>4</v>
@@ -1953,37 +2043,40 @@
       <c r="M42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
+      <c r="N42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E43" s="3">
         <v>4100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1600</v>
       </c>
-      <c r="F43" s="3">
-        <v>11800</v>
-      </c>
       <c r="G43" s="3">
+        <v>11900</v>
+      </c>
+      <c r="H43" s="3">
         <v>1100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>9300</v>
       </c>
-      <c r="I43" s="3">
-        <v>10700</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>4</v>
+      <c r="J43" s="3">
+        <v>10800</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>4</v>
@@ -1994,38 +2087,41 @@
       <c r="M43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N43" s="3">
-        <v>0</v>
+      <c r="N43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E44" s="3">
         <v>10400</v>
-      </c>
-      <c r="E44" s="3">
-        <v>9800</v>
       </c>
       <c r="F44" s="3">
         <v>9900</v>
       </c>
       <c r="G44" s="3">
-        <v>7200</v>
+        <v>9900</v>
       </c>
       <c r="H44" s="3">
-        <v>7600</v>
+        <v>7300</v>
       </c>
       <c r="I44" s="3">
+        <v>7700</v>
+      </c>
+      <c r="J44" s="3">
         <v>5900</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K44" s="3" t="s">
         <v>4</v>
       </c>
@@ -2035,37 +2131,40 @@
       <c r="M44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N44" s="3">
-        <v>0</v>
+      <c r="N44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>18800</v>
+        <v>18600</v>
       </c>
       <c r="E45" s="3">
-        <v>16000</v>
+        <v>18900</v>
       </c>
       <c r="F45" s="3">
+        <v>16100</v>
+      </c>
+      <c r="G45" s="3">
         <v>3900</v>
       </c>
-      <c r="G45" s="3">
-        <v>16300</v>
-      </c>
       <c r="H45" s="3">
-        <v>13200</v>
+        <v>16400</v>
       </c>
       <c r="I45" s="3">
-        <v>10300</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>4</v>
+        <v>13300</v>
+      </c>
+      <c r="J45" s="3">
+        <v>10400</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>4</v>
@@ -2076,37 +2175,40 @@
       <c r="M45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N45" s="3">
+      <c r="N45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O45" s="3">
         <v>200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>87400</v>
+        <v>97800</v>
       </c>
       <c r="E46" s="3">
-        <v>112100</v>
+        <v>88000</v>
       </c>
       <c r="F46" s="3">
-        <v>110000</v>
+        <v>112800</v>
       </c>
       <c r="G46" s="3">
-        <v>129500</v>
+        <v>110800</v>
       </c>
       <c r="H46" s="3">
-        <v>69500</v>
+        <v>130400</v>
       </c>
       <c r="I46" s="3">
-        <v>80900</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>4</v>
+        <v>70000</v>
+      </c>
+      <c r="J46" s="3">
+        <v>81500</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>4</v>
@@ -2117,14 +2219,17 @@
       <c r="M46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N46" s="3">
+      <c r="N46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O46" s="3">
         <v>200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2158,37 +2263,40 @@
       <c r="M47" s="3">
         <v>0</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>4</v>
+      <c r="N47" s="3">
+        <v>0</v>
       </c>
       <c r="O47" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>234500</v>
+        <v>234300</v>
       </c>
       <c r="E48" s="3">
-        <v>228700</v>
+        <v>236100</v>
       </c>
       <c r="F48" s="3">
-        <v>230200</v>
+        <v>230300</v>
       </c>
       <c r="G48" s="3">
-        <v>87900</v>
+        <v>231700</v>
       </c>
       <c r="H48" s="3">
-        <v>80500</v>
+        <v>88500</v>
       </c>
       <c r="I48" s="3">
-        <v>76500</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>4</v>
+        <v>81100</v>
+      </c>
+      <c r="J48" s="3">
+        <v>77000</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>4</v>
@@ -2199,37 +2307,40 @@
       <c r="M48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N48" s="3">
-        <v>0</v>
+      <c r="N48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>18600</v>
+        <v>19000</v>
       </c>
       <c r="E49" s="3">
-        <v>18100</v>
+        <v>18800</v>
       </c>
       <c r="F49" s="3">
+        <v>18200</v>
+      </c>
+      <c r="G49" s="3">
         <v>13300</v>
       </c>
-      <c r="G49" s="3">
-        <v>11900</v>
-      </c>
       <c r="H49" s="3">
+        <v>12000</v>
+      </c>
+      <c r="I49" s="3">
         <v>11200</v>
       </c>
-      <c r="I49" s="3">
-        <v>10700</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>4</v>
+      <c r="J49" s="3">
+        <v>10800</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>4</v>
@@ -2240,14 +2351,17 @@
       <c r="M49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N49" s="3">
-        <v>0</v>
+      <c r="N49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2287,8 +2401,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2328,31 +2445,34 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E52" s="3">
         <v>11600</v>
       </c>
-      <c r="E52" s="3">
-        <v>11100</v>
-      </c>
       <c r="F52" s="3">
+        <v>11200</v>
+      </c>
+      <c r="G52" s="3">
         <v>11400</v>
       </c>
-      <c r="G52" s="3">
-        <v>10800</v>
-      </c>
       <c r="H52" s="3">
-        <v>9600</v>
+        <v>10900</v>
       </c>
       <c r="I52" s="3">
-        <v>9300</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>4</v>
+        <v>9700</v>
+      </c>
+      <c r="J52" s="3">
+        <v>9400</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>4</v>
@@ -2369,8 +2489,11 @@
       <c r="O52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2410,31 +2533,34 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>352100</v>
+        <v>362500</v>
       </c>
       <c r="E54" s="3">
-        <v>370000</v>
+        <v>354500</v>
       </c>
       <c r="F54" s="3">
-        <v>364800</v>
+        <v>372500</v>
       </c>
       <c r="G54" s="3">
-        <v>240200</v>
+        <v>367300</v>
       </c>
       <c r="H54" s="3">
-        <v>170900</v>
+        <v>241800</v>
       </c>
       <c r="I54" s="3">
-        <v>177400</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>4</v>
+        <v>172000</v>
+      </c>
+      <c r="J54" s="3">
+        <v>178600</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>4</v>
@@ -2445,14 +2571,17 @@
       <c r="M54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N54" s="3">
+      <c r="N54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O54" s="3">
         <v>200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2468,8 +2597,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2485,31 +2615,32 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>23900</v>
+        <v>28800</v>
       </c>
       <c r="E57" s="3">
-        <v>15000</v>
+        <v>24000</v>
       </c>
       <c r="F57" s="3">
-        <v>15800</v>
+        <v>15100</v>
       </c>
       <c r="G57" s="3">
-        <v>12700</v>
+        <v>16000</v>
       </c>
       <c r="H57" s="3">
-        <v>8000</v>
+        <v>12800</v>
       </c>
       <c r="I57" s="3">
-        <v>9500</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>4</v>
+        <v>8100</v>
+      </c>
+      <c r="J57" s="3">
+        <v>9600</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>4</v>
@@ -2526,31 +2657,34 @@
       <c r="O57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>53700</v>
+        <v>91600</v>
       </c>
       <c r="E58" s="3">
-        <v>62400</v>
+        <v>54100</v>
       </c>
       <c r="F58" s="3">
-        <v>56300</v>
+        <v>62800</v>
       </c>
       <c r="G58" s="3">
-        <v>50300</v>
+        <v>56700</v>
       </c>
       <c r="H58" s="3">
-        <v>58900</v>
+        <v>50600</v>
       </c>
       <c r="I58" s="3">
-        <v>26500</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>4</v>
+        <v>59300</v>
+      </c>
+      <c r="J58" s="3">
+        <v>26700</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>4</v>
@@ -2561,37 +2695,40 @@
       <c r="M58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N58" s="3">
+      <c r="N58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O58" s="3">
         <v>100</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>92900</v>
+        <v>86800</v>
       </c>
       <c r="E59" s="3">
-        <v>96700</v>
+        <v>93500</v>
       </c>
       <c r="F59" s="3">
-        <v>109900</v>
+        <v>97400</v>
       </c>
       <c r="G59" s="3">
-        <v>69000</v>
+        <v>110600</v>
       </c>
       <c r="H59" s="3">
-        <v>44000</v>
+        <v>69500</v>
       </c>
       <c r="I59" s="3">
-        <v>42300</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>4</v>
+        <v>44300</v>
+      </c>
+      <c r="J59" s="3">
+        <v>42600</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>4</v>
@@ -2602,37 +2739,40 @@
       <c r="M59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N59" s="3">
-        <v>100</v>
+      <c r="N59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O59" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P59" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>170500</v>
+        <v>207200</v>
       </c>
       <c r="E60" s="3">
-        <v>174100</v>
+        <v>171700</v>
       </c>
       <c r="F60" s="3">
-        <v>182000</v>
+        <v>175300</v>
       </c>
       <c r="G60" s="3">
-        <v>132000</v>
+        <v>183300</v>
       </c>
       <c r="H60" s="3">
-        <v>111000</v>
+        <v>132900</v>
       </c>
       <c r="I60" s="3">
-        <v>78300</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>4</v>
+        <v>111700</v>
+      </c>
+      <c r="J60" s="3">
+        <v>78900</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>4</v>
@@ -2643,37 +2783,40 @@
       <c r="M60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N60" s="3">
+      <c r="N60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O60" s="3">
         <v>200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>55800</v>
+        <v>57400</v>
       </c>
       <c r="E61" s="3">
-        <v>51600</v>
+        <v>56200</v>
       </c>
       <c r="F61" s="3">
-        <v>50100</v>
+        <v>52000</v>
       </c>
       <c r="G61" s="3">
-        <v>50700</v>
+        <v>50400</v>
       </c>
       <c r="H61" s="3">
-        <v>50500</v>
+        <v>51000</v>
       </c>
       <c r="I61" s="3">
-        <v>45600</v>
+        <v>50800</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>45900</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -2690,31 +2833,34 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>122600</v>
+        <v>117600</v>
       </c>
       <c r="E62" s="3">
-        <v>130200</v>
+        <v>123400</v>
       </c>
       <c r="F62" s="3">
-        <v>117400</v>
+        <v>131000</v>
       </c>
       <c r="G62" s="3">
-        <v>15600</v>
+        <v>118200</v>
       </c>
       <c r="H62" s="3">
+        <v>15700</v>
+      </c>
+      <c r="I62" s="3">
         <v>7700</v>
       </c>
-      <c r="I62" s="3">
-        <v>6600</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>4</v>
+      <c r="J62" s="3">
+        <v>6700</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>4</v>
@@ -2731,8 +2877,11 @@
       <c r="O62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2772,8 +2921,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2813,8 +2965,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2854,31 +3009,34 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>349300</v>
+        <v>382800</v>
       </c>
       <c r="E66" s="3">
-        <v>356100</v>
+        <v>351700</v>
       </c>
       <c r="F66" s="3">
-        <v>349800</v>
+        <v>358600</v>
       </c>
       <c r="G66" s="3">
-        <v>198300</v>
+        <v>352200</v>
       </c>
       <c r="H66" s="3">
-        <v>169200</v>
+        <v>199700</v>
       </c>
       <c r="I66" s="3">
-        <v>131100</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>4</v>
+        <v>170400</v>
+      </c>
+      <c r="J66" s="3">
+        <v>132000</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>4</v>
@@ -2889,14 +3047,17 @@
       <c r="M66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N66" s="3">
+      <c r="N66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O66" s="3">
         <v>200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2912,8 +3073,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2953,8 +3115,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2994,8 +3159,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3035,8 +3203,11 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3076,31 +3247,34 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-246300</v>
+        <v>-270300</v>
       </c>
       <c r="E72" s="3">
-        <v>-214700</v>
+        <v>-248000</v>
       </c>
       <c r="F72" s="3">
-        <v>-190600</v>
+        <v>-216200</v>
       </c>
       <c r="G72" s="3">
-        <v>-159700</v>
+        <v>-191900</v>
       </c>
       <c r="H72" s="3">
-        <v>-132800</v>
+        <v>-160700</v>
       </c>
       <c r="I72" s="3">
-        <v>-88000</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>4</v>
+        <v>-133700</v>
+      </c>
+      <c r="J72" s="3">
+        <v>-88600</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>4</v>
@@ -3111,14 +3285,17 @@
       <c r="M72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N72" s="3">
-        <v>0</v>
+      <c r="N72" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3158,8 +3335,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3199,8 +3379,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3240,31 +3423,34 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-20300</v>
+      </c>
+      <c r="E76" s="3">
         <v>2800</v>
       </c>
-      <c r="E76" s="3">
-        <v>13800</v>
-      </c>
       <c r="F76" s="3">
-        <v>15000</v>
+        <v>13900</v>
       </c>
       <c r="G76" s="3">
-        <v>41900</v>
+        <v>15100</v>
       </c>
       <c r="H76" s="3">
+        <v>42100</v>
+      </c>
+      <c r="I76" s="3">
         <v>1600</v>
       </c>
-      <c r="I76" s="3">
-        <v>46300</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>4</v>
+      <c r="J76" s="3">
+        <v>46600</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>4</v>
@@ -3275,14 +3461,17 @@
       <c r="M76" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N76" s="3">
-        <v>0</v>
+      <c r="N76" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O76" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3322,95 +3511,104 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-31600</v>
+        <v>-22300</v>
       </c>
       <c r="E81" s="3">
-        <v>-24100</v>
+        <v>-31800</v>
       </c>
       <c r="F81" s="3">
-        <v>-30900</v>
+        <v>-24300</v>
       </c>
       <c r="G81" s="3">
-        <v>-26800</v>
+        <v>-31100</v>
       </c>
       <c r="H81" s="3">
-        <v>-24000</v>
+        <v>-27000</v>
       </c>
       <c r="I81" s="3">
-        <v>-20800</v>
+        <v>-24200</v>
       </c>
       <c r="J81" s="3">
+        <v>-20900</v>
+      </c>
+      <c r="K81" s="3">
         <v>-19100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-15300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-10900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-8000</v>
       </c>
-      <c r="N81" s="3">
-        <v>0</v>
-      </c>
       <c r="O81" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3426,8 +3624,9 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3467,8 +3666,11 @@
       <c r="O83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3508,8 +3710,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3549,8 +3754,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3590,8 +3798,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3631,8 +3842,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3672,49 +3886,55 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>0</v>
+        <v>-4200</v>
       </c>
       <c r="E89" s="3">
-        <v>-11800</v>
+        <v>0</v>
       </c>
       <c r="F89" s="3">
-        <v>-13300</v>
+        <v>-11900</v>
       </c>
       <c r="G89" s="3">
+        <v>-13400</v>
+      </c>
+      <c r="H89" s="3">
         <v>-5000</v>
       </c>
-      <c r="H89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I89" s="3" t="s">
         <v>4</v>
       </c>
       <c r="J89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K89" s="3">
+      <c r="K89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L89" s="3">
         <v>-25900</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N89" s="3">
-        <v>0</v>
+      <c r="N89" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3730,8 +3950,9 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3771,8 +3992,11 @@
       <c r="O91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3812,8 +4036,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3853,25 +4080,28 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E94" s="3">
         <v>1900</v>
       </c>
-      <c r="E94" s="3">
-        <v>6900</v>
-      </c>
       <c r="F94" s="3">
-        <v>-12900</v>
+        <v>7000</v>
       </c>
       <c r="G94" s="3">
-        <v>-59500</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>4</v>
+        <v>-13000</v>
+      </c>
+      <c r="H94" s="3">
+        <v>-59900</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>4</v>
@@ -3879,12 +4109,12 @@
       <c r="J94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K94" s="3">
+      <c r="K94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L94" s="3">
         <v>-30400</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>4</v>
       </c>
@@ -3894,8 +4124,11 @@
       <c r="O94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3911,8 +4144,9 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3952,8 +4186,11 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3993,8 +4230,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4034,8 +4274,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4075,25 +4318,28 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-18700</v>
+        <v>23900</v>
       </c>
       <c r="E100" s="3">
-        <v>22600</v>
+        <v>-18800</v>
       </c>
       <c r="F100" s="3">
-        <v>5100</v>
+        <v>22800</v>
       </c>
       <c r="G100" s="3">
-        <v>77800</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>4</v>
+        <v>5200</v>
+      </c>
+      <c r="H100" s="3">
+        <v>78300</v>
       </c>
       <c r="I100" s="3" t="s">
         <v>4</v>
@@ -4101,12 +4347,12 @@
       <c r="J100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K100" s="3">
+      <c r="K100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L100" s="3">
         <v>51000</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>4</v>
       </c>
@@ -4116,66 +4362,72 @@
       <c r="O100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>100</v>
+      </c>
+      <c r="E101" s="3">
         <v>1700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>1300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>100</v>
       </c>
-      <c r="H101" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I101" s="3" t="s">
         <v>4</v>
       </c>
       <c r="J101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K101" s="3">
+      <c r="K101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L101" s="3">
         <v>-200</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
+      <c r="N101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-15000</v>
+        <v>28700</v>
       </c>
       <c r="E102" s="3">
-        <v>17300</v>
+        <v>-15200</v>
       </c>
       <c r="F102" s="3">
-        <v>-19800</v>
+        <v>17400</v>
       </c>
       <c r="G102" s="3">
-        <v>13400</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>4</v>
+        <v>-19900</v>
+      </c>
+      <c r="H102" s="3">
+        <v>13500</v>
       </c>
       <c r="I102" s="3" t="s">
         <v>4</v>
@@ -4183,19 +4435,22 @@
       <c r="J102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K102" s="3">
+      <c r="K102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L102" s="3">
         <v>-5600</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N102" s="3">
-        <v>0</v>
+      <c r="N102" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/THCH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/THCH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="92">
   <si>
     <t>THCH</t>
   </si>
@@ -656,212 +656,237 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>60700</v>
+        <v>47900</v>
       </c>
       <c r="E8" s="3">
-        <v>57200</v>
+        <v>54000</v>
       </c>
       <c r="F8" s="3">
-        <v>46800</v>
+        <v>60300</v>
       </c>
       <c r="G8" s="3">
-        <v>41900</v>
+        <v>56900</v>
       </c>
       <c r="H8" s="3">
-        <v>42500</v>
+        <v>46500</v>
       </c>
       <c r="I8" s="3">
+        <v>41700</v>
+      </c>
+      <c r="J8" s="3">
+        <v>42200</v>
+      </c>
+      <c r="K8" s="3">
         <v>24900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>31200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>30900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>25100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>19300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>14600</v>
       </c>
-      <c r="O8" s="3">
-        <v>0</v>
-      </c>
-      <c r="P8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+      <c r="R8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>25000</v>
+        <v>18500</v>
       </c>
       <c r="E9" s="3">
-        <v>22400</v>
+        <v>23700</v>
       </c>
       <c r="F9" s="3">
-        <v>18100</v>
+        <v>24800</v>
       </c>
       <c r="G9" s="3">
-        <v>15500</v>
+        <v>22300</v>
       </c>
       <c r="H9" s="3">
+        <v>18000</v>
+      </c>
+      <c r="I9" s="3">
+        <v>15400</v>
+      </c>
+      <c r="J9" s="3">
         <v>14700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>9300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>10900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>10800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>9000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>6700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>4900</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>35700</v>
+        <v>29500</v>
       </c>
       <c r="E10" s="3">
-        <v>34800</v>
+        <v>30300</v>
       </c>
       <c r="F10" s="3">
-        <v>28700</v>
+        <v>35500</v>
       </c>
       <c r="G10" s="3">
-        <v>26400</v>
+        <v>34600</v>
       </c>
       <c r="H10" s="3">
-        <v>27800</v>
+        <v>28500</v>
       </c>
       <c r="I10" s="3">
+        <v>26200</v>
+      </c>
+      <c r="J10" s="3">
+        <v>27600</v>
+      </c>
+      <c r="K10" s="3">
         <v>15600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>20300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>20100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>16100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>12600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>9700</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -878,8 +903,10 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -922,8 +949,14 @@
       <c r="P12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -966,72 +999,84 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E14" s="3">
+        <v>12400</v>
+      </c>
+      <c r="F14" s="3">
         <v>1800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>600</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>200</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>100</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>5100</v>
+        <v>4700</v>
       </c>
       <c r="E15" s="3">
+        <v>4900</v>
+      </c>
+      <c r="F15" s="3">
+        <v>5000</v>
+      </c>
+      <c r="G15" s="3">
         <v>4800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>4600</v>
       </c>
-      <c r="G15" s="3">
-        <v>16500</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>4</v>
+      <c r="I15" s="3">
+        <v>16400</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>4</v>
@@ -1042,11 +1087,11 @@
       <c r="L15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
-      <c r="N15" s="3">
-        <v>0</v>
+      <c r="M15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O15" s="3">
         <v>0</v>
@@ -1054,8 +1099,14 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1069,96 +1120,110 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>82900</v>
+        <v>65800</v>
       </c>
       <c r="E17" s="3">
-        <v>82100</v>
+        <v>86100</v>
       </c>
       <c r="F17" s="3">
-        <v>64900</v>
+        <v>82400</v>
       </c>
       <c r="G17" s="3">
-        <v>60200</v>
+        <v>81600</v>
       </c>
       <c r="H17" s="3">
-        <v>63400</v>
+        <v>64500</v>
       </c>
       <c r="I17" s="3">
+        <v>59800</v>
+      </c>
+      <c r="J17" s="3">
+        <v>63000</v>
+      </c>
+      <c r="K17" s="3">
         <v>47800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>50000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>48800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>40700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>29700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>23000</v>
       </c>
-      <c r="O17" s="3">
-        <v>0</v>
-      </c>
-      <c r="P17" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3">
+        <v>0</v>
+      </c>
+      <c r="R17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-22200</v>
+        <v>-17900</v>
       </c>
       <c r="E18" s="3">
-        <v>-24900</v>
+        <v>-32100</v>
       </c>
       <c r="F18" s="3">
+        <v>-22100</v>
+      </c>
+      <c r="G18" s="3">
+        <v>-24700</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-18000</v>
+      </c>
+      <c r="I18" s="3">
         <v>-18100</v>
       </c>
-      <c r="G18" s="3">
-        <v>-18300</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-20900</v>
-      </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
+        <v>-20800</v>
+      </c>
+      <c r="K18" s="3">
         <v>-22900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-18700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-17900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-15600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-10400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-8500</v>
       </c>
-      <c r="O18" s="3">
-        <v>0</v>
-      </c>
-      <c r="P18" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3">
+        <v>0</v>
+      </c>
+      <c r="R18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1175,69 +1240,77 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="F20" s="3">
         <v>600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-6100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-5500</v>
       </c>
-      <c r="G20" s="3">
-        <v>-12100</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="J20" s="3">
         <v>-5600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-1100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-1900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-800</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>-500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>400</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-21300</v>
+        <v>-14300</v>
       </c>
       <c r="E21" s="3">
-        <v>-30800</v>
+        <v>-42200</v>
       </c>
       <c r="F21" s="3">
-        <v>-19100</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>4</v>
+        <v>-21100</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-30600</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-18900</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>4</v>
@@ -1263,41 +1336,47 @@
       <c r="P21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="E22" s="3">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="F22" s="3">
         <v>600</v>
       </c>
       <c r="G22" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="H22" s="3">
         <v>600</v>
       </c>
       <c r="I22" s="3">
+        <v>600</v>
+      </c>
+      <c r="J22" s="3">
+        <v>600</v>
+      </c>
+      <c r="K22" s="3">
         <v>500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>200</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
       <c r="N22" s="3">
         <v>0</v>
       </c>
@@ -1307,57 +1386,69 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-22200</v>
+        <v>-19700</v>
       </c>
       <c r="E23" s="3">
-        <v>-31600</v>
+        <v>-43000</v>
       </c>
       <c r="F23" s="3">
-        <v>-24300</v>
+        <v>-22100</v>
       </c>
       <c r="G23" s="3">
-        <v>-31000</v>
+        <v>-31500</v>
       </c>
       <c r="H23" s="3">
-        <v>-27100</v>
+        <v>-24100</v>
       </c>
       <c r="I23" s="3">
+        <v>-30800</v>
+      </c>
+      <c r="J23" s="3">
+        <v>-26900</v>
+      </c>
+      <c r="K23" s="3">
         <v>-24400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-21000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-18900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-15600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-10900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-8100</v>
       </c>
-      <c r="O23" s="3">
-        <v>0</v>
-      </c>
-      <c r="P23" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3">
+        <v>0</v>
+      </c>
+      <c r="R23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E24" s="3">
         <v>0</v>
@@ -1395,8 +1486,14 @@
       <c r="P24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1439,96 +1536,114 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-22200</v>
+        <v>-19700</v>
       </c>
       <c r="E26" s="3">
-        <v>-31600</v>
+        <v>-43000</v>
       </c>
       <c r="F26" s="3">
-        <v>-24300</v>
+        <v>-22100</v>
       </c>
       <c r="G26" s="3">
-        <v>-31000</v>
+        <v>-31500</v>
       </c>
       <c r="H26" s="3">
-        <v>-27100</v>
+        <v>-24100</v>
       </c>
       <c r="I26" s="3">
+        <v>-30800</v>
+      </c>
+      <c r="J26" s="3">
+        <v>-26900</v>
+      </c>
+      <c r="K26" s="3">
         <v>-24400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-21000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-18900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-15600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-10900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-8100</v>
       </c>
-      <c r="O26" s="3">
-        <v>0</v>
-      </c>
-      <c r="P26" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3">
+        <v>0</v>
+      </c>
+      <c r="R26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-22300</v>
+        <v>-19900</v>
       </c>
       <c r="E27" s="3">
-        <v>-31800</v>
+        <v>-43100</v>
       </c>
       <c r="F27" s="3">
-        <v>-24300</v>
+        <v>-22200</v>
       </c>
       <c r="G27" s="3">
-        <v>-31100</v>
+        <v>-31600</v>
       </c>
       <c r="H27" s="3">
-        <v>-27000</v>
+        <v>-24200</v>
       </c>
       <c r="I27" s="3">
+        <v>-30900</v>
+      </c>
+      <c r="J27" s="3">
+        <v>-26900</v>
+      </c>
+      <c r="K27" s="3">
         <v>-24200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-20900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-19100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-15300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-10900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-8000</v>
       </c>
-      <c r="O27" s="3">
-        <v>0</v>
-      </c>
-      <c r="P27" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3">
+        <v>0</v>
+      </c>
+      <c r="R27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1571,8 +1686,14 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1615,8 +1736,14 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1659,8 +1786,14 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1703,96 +1836,114 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E32" s="3">
+        <v>10000</v>
+      </c>
+      <c r="F32" s="3">
         <v>-600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>6100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>5500</v>
       </c>
-      <c r="G32" s="3">
-        <v>12100</v>
-      </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
+        <v>12000</v>
+      </c>
+      <c r="J32" s="3">
         <v>5600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>1100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>1900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>800</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-400</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-22300</v>
+        <v>-19900</v>
       </c>
       <c r="E33" s="3">
-        <v>-31800</v>
+        <v>-43100</v>
       </c>
       <c r="F33" s="3">
-        <v>-24300</v>
+        <v>-22200</v>
       </c>
       <c r="G33" s="3">
-        <v>-31100</v>
+        <v>-31600</v>
       </c>
       <c r="H33" s="3">
-        <v>-27000</v>
+        <v>-24200</v>
       </c>
       <c r="I33" s="3">
+        <v>-30900</v>
+      </c>
+      <c r="J33" s="3">
+        <v>-26900</v>
+      </c>
+      <c r="K33" s="3">
         <v>-24200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-20900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-19100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-15300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-10900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-8000</v>
       </c>
-      <c r="O33" s="3">
-        <v>0</v>
-      </c>
-      <c r="P33" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3">
+        <v>0</v>
+      </c>
+      <c r="R33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1835,101 +1986,119 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-22300</v>
+        <v>-19900</v>
       </c>
       <c r="E35" s="3">
-        <v>-31800</v>
+        <v>-43100</v>
       </c>
       <c r="F35" s="3">
-        <v>-24300</v>
+        <v>-22200</v>
       </c>
       <c r="G35" s="3">
-        <v>-31100</v>
+        <v>-31600</v>
       </c>
       <c r="H35" s="3">
-        <v>-27000</v>
+        <v>-24200</v>
       </c>
       <c r="I35" s="3">
+        <v>-30900</v>
+      </c>
+      <c r="J35" s="3">
+        <v>-26900</v>
+      </c>
+      <c r="K35" s="3">
         <v>-24200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-20900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-19100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-15300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-10900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-8000</v>
       </c>
-      <c r="O35" s="3">
-        <v>0</v>
-      </c>
-      <c r="P35" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3">
+        <v>0</v>
+      </c>
+      <c r="R35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1946,8 +2115,10 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1964,38 +2135,40 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>64200</v>
+        <v>27200</v>
       </c>
       <c r="E41" s="3">
-        <v>35500</v>
+        <v>28100</v>
       </c>
       <c r="F41" s="3">
-        <v>50700</v>
+        <v>63800</v>
       </c>
       <c r="G41" s="3">
-        <v>33200</v>
+        <v>35300</v>
       </c>
       <c r="H41" s="3">
-        <v>53200</v>
+        <v>50400</v>
       </c>
       <c r="I41" s="3">
+        <v>33000</v>
+      </c>
+      <c r="J41" s="3">
+        <v>52800</v>
+      </c>
+      <c r="K41" s="3">
         <v>39600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>54300</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>4</v>
       </c>
@@ -2008,31 +2181,37 @@
       <c r="P41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3">
-        <v>0</v>
+      <c r="D42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E42" s="3">
-        <v>19000</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>34600</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>51800</v>
+        <v>18800</v>
       </c>
       <c r="H42" s="3">
-        <v>52500</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>4</v>
+        <v>34400</v>
+      </c>
+      <c r="I42" s="3">
+        <v>51400</v>
+      </c>
+      <c r="J42" s="3">
+        <v>52200</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>4</v>
@@ -2046,190 +2225,220 @@
       <c r="N42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="O42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E43" s="3">
+        <v>3800</v>
+      </c>
+      <c r="F43" s="3">
         <v>4700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>4100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>1600</v>
       </c>
-      <c r="G43" s="3">
-        <v>11900</v>
-      </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
+        <v>11800</v>
+      </c>
+      <c r="J43" s="3">
         <v>1100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>9300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>10800</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>4</v>
       </c>
       <c r="N43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
-      </c>
-      <c r="P43" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="O43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E44" s="3">
+        <v>7000</v>
+      </c>
+      <c r="F44" s="3">
         <v>10300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>10400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
+        <v>9800</v>
+      </c>
+      <c r="I44" s="3">
         <v>9900</v>
       </c>
-      <c r="G44" s="3">
-        <v>9900</v>
-      </c>
-      <c r="H44" s="3">
-        <v>7300</v>
-      </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
+        <v>7200</v>
+      </c>
+      <c r="K44" s="3">
         <v>7700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>5900</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M44" s="3" t="s">
         <v>4</v>
       </c>
       <c r="N44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
-      </c>
-      <c r="P44" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="O44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>18600</v>
+        <v>25700</v>
       </c>
       <c r="E45" s="3">
-        <v>18900</v>
+        <v>24400</v>
       </c>
       <c r="F45" s="3">
-        <v>16100</v>
+        <v>18500</v>
       </c>
       <c r="G45" s="3">
+        <v>18800</v>
+      </c>
+      <c r="H45" s="3">
+        <v>16000</v>
+      </c>
+      <c r="I45" s="3">
         <v>3900</v>
       </c>
-      <c r="H45" s="3">
-        <v>16400</v>
-      </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
+        <v>16300</v>
+      </c>
+      <c r="K45" s="3">
         <v>13300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>10400</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>4</v>
       </c>
       <c r="N45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q45" s="3">
         <v>200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>97800</v>
+        <v>62300</v>
       </c>
       <c r="E46" s="3">
-        <v>88000</v>
+        <v>63400</v>
       </c>
       <c r="F46" s="3">
-        <v>112800</v>
+        <v>97200</v>
       </c>
       <c r="G46" s="3">
-        <v>110800</v>
+        <v>87400</v>
       </c>
       <c r="H46" s="3">
-        <v>130400</v>
+        <v>112100</v>
       </c>
       <c r="I46" s="3">
+        <v>110100</v>
+      </c>
+      <c r="J46" s="3">
+        <v>129600</v>
+      </c>
+      <c r="K46" s="3">
         <v>70000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>81500</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>4</v>
       </c>
       <c r="N46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O46" s="3">
+      <c r="O46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q46" s="3">
         <v>200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2266,102 +2475,120 @@
       <c r="N47" s="3">
         <v>0</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P47" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>234300</v>
+        <v>190300</v>
       </c>
       <c r="E48" s="3">
-        <v>236100</v>
+        <v>212900</v>
       </c>
       <c r="F48" s="3">
+        <v>232800</v>
+      </c>
+      <c r="G48" s="3">
+        <v>234600</v>
+      </c>
+      <c r="H48" s="3">
+        <v>228900</v>
+      </c>
+      <c r="I48" s="3">
         <v>230300</v>
       </c>
-      <c r="G48" s="3">
-        <v>231700</v>
-      </c>
-      <c r="H48" s="3">
-        <v>88500</v>
-      </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
+        <v>88000</v>
+      </c>
+      <c r="K48" s="3">
         <v>81100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>77000</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>4</v>
       </c>
       <c r="N48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O48" s="3">
-        <v>0</v>
-      </c>
-      <c r="P48" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q48" s="3">
+        <v>0</v>
+      </c>
+      <c r="R48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>19000</v>
+        <v>20100</v>
       </c>
       <c r="E49" s="3">
-        <v>18800</v>
+        <v>20400</v>
       </c>
       <c r="F49" s="3">
-        <v>18200</v>
+        <v>18900</v>
       </c>
       <c r="G49" s="3">
+        <v>18700</v>
+      </c>
+      <c r="H49" s="3">
+        <v>18100</v>
+      </c>
+      <c r="I49" s="3">
         <v>13300</v>
       </c>
-      <c r="H49" s="3">
-        <v>12000</v>
-      </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
+        <v>11900</v>
+      </c>
+      <c r="K49" s="3">
         <v>11200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>10800</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M49" s="3" t="s">
         <v>4</v>
       </c>
       <c r="N49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O49" s="3">
-        <v>0</v>
-      </c>
-      <c r="P49" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2404,8 +2631,14 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2448,38 +2681,44 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>9500</v>
+      </c>
+      <c r="F52" s="3">
         <v>11300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>11600</v>
       </c>
-      <c r="F52" s="3">
-        <v>11200</v>
-      </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
+        <v>11100</v>
+      </c>
+      <c r="I52" s="3">
         <v>11400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>10900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>9700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>9400</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>4</v>
       </c>
@@ -2492,8 +2731,14 @@
       <c r="P52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2536,52 +2781,64 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>362500</v>
+        <v>281800</v>
       </c>
       <c r="E54" s="3">
-        <v>354500</v>
+        <v>306100</v>
       </c>
       <c r="F54" s="3">
-        <v>372500</v>
+        <v>360200</v>
       </c>
       <c r="G54" s="3">
-        <v>367300</v>
+        <v>352300</v>
       </c>
       <c r="H54" s="3">
-        <v>241800</v>
+        <v>370200</v>
       </c>
       <c r="I54" s="3">
+        <v>365000</v>
+      </c>
+      <c r="J54" s="3">
+        <v>240300</v>
+      </c>
+      <c r="K54" s="3">
         <v>172000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>178600</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>4</v>
       </c>
       <c r="N54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O54" s="3">
+      <c r="O54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q54" s="3">
         <v>200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2598,8 +2855,10 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2616,38 +2875,40 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>28800</v>
+        <v>35400</v>
       </c>
       <c r="E57" s="3">
-        <v>24000</v>
+        <v>31100</v>
       </c>
       <c r="F57" s="3">
-        <v>15100</v>
+        <v>28600</v>
       </c>
       <c r="G57" s="3">
-        <v>16000</v>
+        <v>23900</v>
       </c>
       <c r="H57" s="3">
-        <v>12800</v>
+        <v>15000</v>
       </c>
       <c r="I57" s="3">
+        <v>15900</v>
+      </c>
+      <c r="J57" s="3">
+        <v>12700</v>
+      </c>
+      <c r="K57" s="3">
         <v>8100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>9600</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>4</v>
       </c>
@@ -2660,170 +2921,194 @@
       <c r="P57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>91600</v>
+        <v>58400</v>
       </c>
       <c r="E58" s="3">
-        <v>54100</v>
+        <v>74400</v>
       </c>
       <c r="F58" s="3">
-        <v>62800</v>
+        <v>91000</v>
       </c>
       <c r="G58" s="3">
-        <v>56700</v>
+        <v>53800</v>
       </c>
       <c r="H58" s="3">
-        <v>50600</v>
+        <v>62400</v>
       </c>
       <c r="I58" s="3">
+        <v>56300</v>
+      </c>
+      <c r="J58" s="3">
+        <v>50300</v>
+      </c>
+      <c r="K58" s="3">
         <v>59300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>26700</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>4</v>
       </c>
       <c r="N58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O58" s="3">
+      <c r="O58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q58" s="3">
         <v>100</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>86800</v>
+        <v>107400</v>
       </c>
       <c r="E59" s="3">
-        <v>93500</v>
+        <v>87400</v>
       </c>
       <c r="F59" s="3">
-        <v>97400</v>
+        <v>86200</v>
       </c>
       <c r="G59" s="3">
-        <v>110600</v>
+        <v>93000</v>
       </c>
       <c r="H59" s="3">
-        <v>69500</v>
+        <v>96800</v>
       </c>
       <c r="I59" s="3">
+        <v>109900</v>
+      </c>
+      <c r="J59" s="3">
+        <v>69100</v>
+      </c>
+      <c r="K59" s="3">
         <v>44300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>42600</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>4</v>
       </c>
       <c r="N59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q59" s="3">
         <v>100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>207200</v>
+        <v>201100</v>
       </c>
       <c r="E60" s="3">
-        <v>171700</v>
+        <v>192800</v>
       </c>
       <c r="F60" s="3">
-        <v>175300</v>
+        <v>205900</v>
       </c>
       <c r="G60" s="3">
-        <v>183300</v>
+        <v>170600</v>
       </c>
       <c r="H60" s="3">
-        <v>132900</v>
+        <v>174200</v>
       </c>
       <c r="I60" s="3">
+        <v>182100</v>
+      </c>
+      <c r="J60" s="3">
+        <v>132000</v>
+      </c>
+      <c r="K60" s="3">
         <v>111700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>78900</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>4</v>
       </c>
       <c r="N60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O60" s="3">
+      <c r="O60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q60" s="3">
         <v>200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>57400</v>
+        <v>60600</v>
       </c>
       <c r="E61" s="3">
-        <v>56200</v>
+        <v>58900</v>
       </c>
       <c r="F61" s="3">
-        <v>52000</v>
+        <v>57100</v>
       </c>
       <c r="G61" s="3">
-        <v>50400</v>
+        <v>55800</v>
       </c>
       <c r="H61" s="3">
-        <v>51000</v>
+        <v>51700</v>
       </c>
       <c r="I61" s="3">
+        <v>50100</v>
+      </c>
+      <c r="J61" s="3">
+        <v>50700</v>
+      </c>
+      <c r="K61" s="3">
         <v>50800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>45900</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -2836,38 +3121,44 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>117600</v>
+        <v>98400</v>
       </c>
       <c r="E62" s="3">
-        <v>123400</v>
+        <v>112700</v>
       </c>
       <c r="F62" s="3">
-        <v>131000</v>
+        <v>116900</v>
       </c>
       <c r="G62" s="3">
-        <v>118200</v>
+        <v>122700</v>
       </c>
       <c r="H62" s="3">
-        <v>15700</v>
+        <v>130200</v>
       </c>
       <c r="I62" s="3">
+        <v>117500</v>
+      </c>
+      <c r="J62" s="3">
+        <v>15600</v>
+      </c>
+      <c r="K62" s="3">
         <v>7700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>6700</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>4</v>
       </c>
@@ -2880,8 +3171,14 @@
       <c r="P62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2924,8 +3221,14 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2968,8 +3271,14 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3012,52 +3321,64 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>382800</v>
+        <v>361000</v>
       </c>
       <c r="E66" s="3">
-        <v>351700</v>
+        <v>365100</v>
       </c>
       <c r="F66" s="3">
-        <v>358600</v>
+        <v>380400</v>
       </c>
       <c r="G66" s="3">
-        <v>352200</v>
+        <v>349500</v>
       </c>
       <c r="H66" s="3">
-        <v>199700</v>
+        <v>356400</v>
       </c>
       <c r="I66" s="3">
+        <v>350000</v>
+      </c>
+      <c r="J66" s="3">
+        <v>198400</v>
+      </c>
+      <c r="K66" s="3">
         <v>170400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>132000</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>4</v>
       </c>
       <c r="N66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O66" s="3">
+      <c r="O66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q66" s="3">
         <v>200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3074,8 +3395,10 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3118,8 +3441,14 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3162,8 +3491,14 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3206,8 +3541,14 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3250,52 +3591,64 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-270300</v>
+        <v>-331600</v>
       </c>
       <c r="E72" s="3">
-        <v>-248000</v>
+        <v>-311700</v>
       </c>
       <c r="F72" s="3">
-        <v>-216200</v>
+        <v>-268600</v>
       </c>
       <c r="G72" s="3">
-        <v>-191900</v>
+        <v>-246400</v>
       </c>
       <c r="H72" s="3">
-        <v>-160700</v>
+        <v>-214800</v>
       </c>
       <c r="I72" s="3">
+        <v>-190700</v>
+      </c>
+      <c r="J72" s="3">
+        <v>-159800</v>
+      </c>
+      <c r="K72" s="3">
         <v>-133700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-88600</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>4</v>
       </c>
       <c r="N72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O72" s="3">
-        <v>0</v>
-      </c>
-      <c r="P72" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="O72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q72" s="3">
+        <v>0</v>
+      </c>
+      <c r="R72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3338,8 +3691,14 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3382,8 +3741,14 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3426,52 +3791,64 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>-20300</v>
+        <v>-79200</v>
       </c>
       <c r="E76" s="3">
+        <v>-59000</v>
+      </c>
+      <c r="F76" s="3">
+        <v>-20200</v>
+      </c>
+      <c r="G76" s="3">
         <v>2800</v>
       </c>
-      <c r="F76" s="3">
-        <v>13900</v>
-      </c>
-      <c r="G76" s="3">
-        <v>15100</v>
-      </c>
       <c r="H76" s="3">
-        <v>42100</v>
+        <v>13800</v>
       </c>
       <c r="I76" s="3">
+        <v>15000</v>
+      </c>
+      <c r="J76" s="3">
+        <v>41900</v>
+      </c>
+      <c r="K76" s="3">
         <v>1600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>46600</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>4</v>
       </c>
       <c r="N76" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O76" s="3">
-        <v>0</v>
-      </c>
-      <c r="P76" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="O76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q76" s="3">
+        <v>0</v>
+      </c>
+      <c r="R76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3514,101 +3891,119 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-22300</v>
+        <v>-19900</v>
       </c>
       <c r="E81" s="3">
-        <v>-31800</v>
+        <v>-43100</v>
       </c>
       <c r="F81" s="3">
-        <v>-24300</v>
+        <v>-22200</v>
       </c>
       <c r="G81" s="3">
-        <v>-31100</v>
+        <v>-31600</v>
       </c>
       <c r="H81" s="3">
-        <v>-27000</v>
+        <v>-24200</v>
       </c>
       <c r="I81" s="3">
+        <v>-30900</v>
+      </c>
+      <c r="J81" s="3">
+        <v>-26900</v>
+      </c>
+      <c r="K81" s="3">
         <v>-24200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-20900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-19100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-15300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-10900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-8000</v>
       </c>
-      <c r="O81" s="3">
-        <v>0</v>
-      </c>
-      <c r="P81" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3">
+        <v>0</v>
+      </c>
+      <c r="R81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3625,8 +4020,10 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3669,8 +4066,14 @@
       <c r="P83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3">
+        <v>0</v>
+      </c>
+      <c r="R83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3713,8 +4116,14 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3757,8 +4166,14 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3801,8 +4216,14 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3845,8 +4266,14 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3889,52 +4316,64 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="F89" s="3">
         <v>-4200</v>
       </c>
-      <c r="E89" s="3">
-        <v>0</v>
-      </c>
-      <c r="F89" s="3">
-        <v>-11900</v>
-      </c>
       <c r="G89" s="3">
-        <v>-13400</v>
+        <v>0</v>
       </c>
       <c r="H89" s="3">
+        <v>-11800</v>
+      </c>
+      <c r="I89" s="3">
+        <v>-13300</v>
+      </c>
+      <c r="J89" s="3">
         <v>-5000</v>
       </c>
-      <c r="I89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L89" s="3">
+      <c r="L89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N89" s="3">
         <v>-25900</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O89" s="3">
-        <v>0</v>
-      </c>
-      <c r="P89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q89" s="3">
+        <v>0</v>
+      </c>
+      <c r="R89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3951,8 +4390,10 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3995,8 +4436,14 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4039,8 +4486,14 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4083,52 +4536,64 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>8900</v>
+        <v>-1000</v>
       </c>
       <c r="E94" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="F94" s="3">
+        <v>8800</v>
+      </c>
+      <c r="G94" s="3">
         <v>1900</v>
       </c>
-      <c r="F94" s="3">
-        <v>7000</v>
-      </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
+        <v>6900</v>
+      </c>
+      <c r="I94" s="3">
         <v>-13000</v>
       </c>
-      <c r="H94" s="3">
-        <v>-59900</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>4</v>
+      <c r="J94" s="3">
+        <v>-59600</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L94" s="3">
+      <c r="L94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N94" s="3">
         <v>-30400</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O94" s="3" t="s">
         <v>4</v>
       </c>
       <c r="P94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4145,8 +4610,10 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4189,8 +4656,14 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4233,8 +4706,14 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4277,8 +4756,14 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4321,136 +4806,160 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>23900</v>
+        <v>3600</v>
       </c>
       <c r="E100" s="3">
-        <v>-18800</v>
+        <v>-16500</v>
       </c>
       <c r="F100" s="3">
-        <v>22800</v>
+        <v>23700</v>
       </c>
       <c r="G100" s="3">
-        <v>5200</v>
+        <v>-18700</v>
       </c>
       <c r="H100" s="3">
-        <v>78300</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>4</v>
+        <v>22700</v>
+      </c>
+      <c r="I100" s="3">
+        <v>5100</v>
+      </c>
+      <c r="J100" s="3">
+        <v>77800</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L100" s="3">
+      <c r="L100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N100" s="3">
         <v>51000</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O100" s="3" t="s">
         <v>4</v>
       </c>
       <c r="P100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>200</v>
+      </c>
+      <c r="E101" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F101" s="3">
         <v>100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>1700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>1300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>100</v>
       </c>
-      <c r="I101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L101" s="3">
+      <c r="L101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N101" s="3">
         <v>-200</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>28700</v>
+        <v>-900</v>
       </c>
       <c r="E102" s="3">
-        <v>-15200</v>
+        <v>-35700</v>
       </c>
       <c r="F102" s="3">
-        <v>17400</v>
+        <v>28500</v>
       </c>
       <c r="G102" s="3">
-        <v>-19900</v>
+        <v>-15100</v>
       </c>
       <c r="H102" s="3">
-        <v>13500</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>4</v>
+        <v>17300</v>
+      </c>
+      <c r="I102" s="3">
+        <v>-19800</v>
+      </c>
+      <c r="J102" s="3">
+        <v>13400</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L102" s="3">
+      <c r="L102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N102" s="3">
         <v>-5600</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O102" s="3">
-        <v>0</v>
-      </c>
-      <c r="P102" s="3">
+      <c r="O102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q102" s="3">
+        <v>0</v>
+      </c>
+      <c r="R102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/THCH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/THCH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="92">
   <si>
     <t>THCH</t>
   </si>
@@ -656,237 +656,250 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>47900</v>
+        <v>51700</v>
       </c>
       <c r="E8" s="3">
-        <v>54000</v>
+        <v>46800</v>
       </c>
       <c r="F8" s="3">
-        <v>60300</v>
+        <v>55200</v>
       </c>
       <c r="G8" s="3">
-        <v>56900</v>
+        <v>61500</v>
       </c>
       <c r="H8" s="3">
-        <v>46500</v>
+        <v>58000</v>
       </c>
       <c r="I8" s="3">
-        <v>41700</v>
+        <v>47400</v>
       </c>
       <c r="J8" s="3">
+        <v>42500</v>
+      </c>
+      <c r="K8" s="3">
         <v>42200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>24900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>31200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>30900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>25100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>19300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>14600</v>
       </c>
-      <c r="Q8" s="3">
-        <v>0</v>
-      </c>
       <c r="R8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>18500</v>
+        <v>19000</v>
       </c>
       <c r="E9" s="3">
-        <v>23700</v>
+        <v>18000</v>
       </c>
       <c r="F9" s="3">
-        <v>24800</v>
+        <v>24200</v>
       </c>
       <c r="G9" s="3">
-        <v>22300</v>
+        <v>25300</v>
       </c>
       <c r="H9" s="3">
-        <v>18000</v>
+        <v>22700</v>
       </c>
       <c r="I9" s="3">
-        <v>15400</v>
+        <v>18400</v>
       </c>
       <c r="J9" s="3">
+        <v>15700</v>
+      </c>
+      <c r="K9" s="3">
         <v>14700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>9300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>10900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>10800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>9000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>6700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>4900</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>29500</v>
+        <v>32800</v>
       </c>
       <c r="E10" s="3">
-        <v>30300</v>
+        <v>28800</v>
       </c>
       <c r="F10" s="3">
-        <v>35500</v>
+        <v>30900</v>
       </c>
       <c r="G10" s="3">
-        <v>34600</v>
+        <v>36200</v>
       </c>
       <c r="H10" s="3">
-        <v>28500</v>
+        <v>35300</v>
       </c>
       <c r="I10" s="3">
-        <v>26200</v>
+        <v>29100</v>
       </c>
       <c r="J10" s="3">
+        <v>26800</v>
+      </c>
+      <c r="K10" s="3">
         <v>27600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>15600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>20300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>20100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>16100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>12600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>9700</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -905,8 +918,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -955,8 +969,11 @@
       <c r="R12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1005,81 +1022,87 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>2600</v>
+        <v>2300</v>
       </c>
       <c r="E14" s="3">
-        <v>12400</v>
+        <v>2700</v>
       </c>
       <c r="F14" s="3">
+        <v>12600</v>
+      </c>
+      <c r="G14" s="3">
         <v>1800</v>
-      </c>
-      <c r="G14" s="3">
-        <v>600</v>
       </c>
       <c r="H14" s="3">
         <v>600</v>
       </c>
       <c r="I14" s="3">
+        <v>600</v>
+      </c>
+      <c r="J14" s="3">
         <v>200</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>100</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>4</v>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E15" s="3">
         <v>4700</v>
-      </c>
-      <c r="E15" s="3">
-        <v>4900</v>
       </c>
       <c r="F15" s="3">
         <v>5000</v>
       </c>
       <c r="G15" s="3">
-        <v>4800</v>
+        <v>5100</v>
       </c>
       <c r="H15" s="3">
+        <v>4900</v>
+      </c>
+      <c r="I15" s="3">
         <v>4600</v>
       </c>
-      <c r="I15" s="3">
-        <v>16400</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>4</v>
+      <c r="J15" s="3">
+        <v>16700</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>4</v>
@@ -1093,8 +1116,8 @@
       <c r="N15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
+      <c r="O15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P15" s="3">
         <v>0</v>
@@ -1105,8 +1128,11 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1122,108 +1148,115 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>60900</v>
+      </c>
+      <c r="E17" s="3">
+        <v>63900</v>
+      </c>
+      <c r="F17" s="3">
+        <v>87900</v>
+      </c>
+      <c r="G17" s="3">
+        <v>84000</v>
+      </c>
+      <c r="H17" s="3">
+        <v>82200</v>
+      </c>
+      <c r="I17" s="3">
         <v>65800</v>
       </c>
-      <c r="E17" s="3">
-        <v>86100</v>
-      </c>
-      <c r="F17" s="3">
-        <v>82400</v>
-      </c>
-      <c r="G17" s="3">
-        <v>81600</v>
-      </c>
-      <c r="H17" s="3">
-        <v>64500</v>
-      </c>
-      <c r="I17" s="3">
-        <v>59800</v>
-      </c>
       <c r="J17" s="3">
+        <v>61000</v>
+      </c>
+      <c r="K17" s="3">
         <v>63000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>47800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>50000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>48800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>40700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>29700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>23000</v>
       </c>
-      <c r="Q17" s="3">
-        <v>0</v>
-      </c>
       <c r="R17" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-17100</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-32700</v>
+      </c>
+      <c r="G18" s="3">
+        <v>-22500</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-24200</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-18400</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-18500</v>
+      </c>
+      <c r="K18" s="3">
+        <v>-20800</v>
+      </c>
+      <c r="L18" s="3">
+        <v>-22900</v>
+      </c>
+      <c r="M18" s="3">
+        <v>-18700</v>
+      </c>
+      <c r="N18" s="3">
         <v>-17900</v>
       </c>
-      <c r="E18" s="3">
-        <v>-32100</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-22100</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-24700</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-18000</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-18100</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-20800</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-22900</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-18700</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-17900</v>
-      </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-15600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-10400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-8500</v>
       </c>
-      <c r="Q18" s="3">
-        <v>0</v>
-      </c>
       <c r="R18" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1242,78 +1275,82 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1100</v>
       </c>
-      <c r="E20" s="3">
-        <v>-10000</v>
-      </c>
       <c r="F20" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="G20" s="3">
         <v>600</v>
       </c>
-      <c r="G20" s="3">
-        <v>-6100</v>
-      </c>
       <c r="H20" s="3">
-        <v>-5500</v>
+        <v>-6200</v>
       </c>
       <c r="I20" s="3">
-        <v>-12000</v>
+        <v>-5600</v>
       </c>
       <c r="J20" s="3">
+        <v>-12300</v>
+      </c>
+      <c r="K20" s="3">
         <v>-5600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-800</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>-500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>400</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-14300</v>
+        <v>-13100</v>
       </c>
       <c r="E21" s="3">
-        <v>-42200</v>
+        <v>-13400</v>
       </c>
       <c r="F21" s="3">
-        <v>-21100</v>
+        <v>-43000</v>
       </c>
       <c r="G21" s="3">
-        <v>-30600</v>
+        <v>-21600</v>
       </c>
       <c r="H21" s="3">
-        <v>-18900</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>4</v>
+        <v>-30200</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-19300</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>4</v>
@@ -1342,25 +1379,28 @@
       <c r="R21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E22" s="3">
         <v>800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>700</v>
-      </c>
-      <c r="H22" s="3">
-        <v>600</v>
       </c>
       <c r="I22" s="3">
         <v>600</v>
@@ -1369,17 +1409,17 @@
         <v>600</v>
       </c>
       <c r="K22" s="3">
+        <v>600</v>
+      </c>
+      <c r="L22" s="3">
         <v>500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>200</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
       <c r="O22" s="3">
         <v>0</v>
       </c>
@@ -1392,63 +1432,69 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-19700</v>
+        <v>-13900</v>
       </c>
       <c r="E23" s="3">
-        <v>-43000</v>
+        <v>-19000</v>
       </c>
       <c r="F23" s="3">
-        <v>-22100</v>
+        <v>-43900</v>
       </c>
       <c r="G23" s="3">
-        <v>-31500</v>
+        <v>-22500</v>
       </c>
       <c r="H23" s="3">
-        <v>-24100</v>
+        <v>-31100</v>
       </c>
       <c r="I23" s="3">
-        <v>-30800</v>
+        <v>-24600</v>
       </c>
       <c r="J23" s="3">
+        <v>-31400</v>
+      </c>
+      <c r="K23" s="3">
         <v>-26900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-24400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-21000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-18900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-15600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-10900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-8100</v>
       </c>
-      <c r="Q23" s="3">
-        <v>0</v>
-      </c>
       <c r="R23" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>4</v>
+      <c r="D24" s="3">
+        <v>200</v>
       </c>
       <c r="E24" s="3">
         <v>0</v>
@@ -1492,8 +1538,11 @@
       <c r="R24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1542,108 +1591,117 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-19700</v>
+        <v>-14000</v>
       </c>
       <c r="E26" s="3">
-        <v>-43000</v>
+        <v>-19000</v>
       </c>
       <c r="F26" s="3">
-        <v>-22100</v>
+        <v>-43900</v>
       </c>
       <c r="G26" s="3">
-        <v>-31500</v>
+        <v>-22500</v>
       </c>
       <c r="H26" s="3">
-        <v>-24100</v>
+        <v>-31100</v>
       </c>
       <c r="I26" s="3">
-        <v>-30800</v>
+        <v>-24600</v>
       </c>
       <c r="J26" s="3">
+        <v>-31400</v>
+      </c>
+      <c r="K26" s="3">
         <v>-26900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-24400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-21000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-18900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-15600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-10900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-8100</v>
       </c>
-      <c r="Q26" s="3">
-        <v>0</v>
-      </c>
       <c r="R26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-19900</v>
+        <v>-14200</v>
       </c>
       <c r="E27" s="3">
-        <v>-43100</v>
+        <v>-19200</v>
       </c>
       <c r="F27" s="3">
-        <v>-22200</v>
+        <v>-44000</v>
       </c>
       <c r="G27" s="3">
+        <v>-22600</v>
+      </c>
+      <c r="H27" s="3">
+        <v>-31200</v>
+      </c>
+      <c r="I27" s="3">
+        <v>-24700</v>
+      </c>
+      <c r="J27" s="3">
         <v>-31600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="K27" s="3">
+        <v>-26900</v>
+      </c>
+      <c r="L27" s="3">
         <v>-24200</v>
       </c>
-      <c r="I27" s="3">
-        <v>-30900</v>
-      </c>
-      <c r="J27" s="3">
-        <v>-26900</v>
-      </c>
-      <c r="K27" s="3">
-        <v>-24200</v>
-      </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-20900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-19100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-15300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-10900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-8000</v>
       </c>
-      <c r="Q27" s="3">
-        <v>0</v>
-      </c>
       <c r="R27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1692,31 +1750,34 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="E29" s="3">
-        <v>0</v>
-      </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
-      <c r="G29" s="3">
-        <v>0</v>
+        <v>-1100</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H29" s="3">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="I29" s="3">
         <v>0</v>
       </c>
-      <c r="J29" s="3">
-        <v>0</v>
+      <c r="J29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
@@ -1742,8 +1803,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1792,8 +1856,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1842,108 +1909,117 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E32" s="3">
         <v>1100</v>
       </c>
-      <c r="E32" s="3">
-        <v>10000</v>
-      </c>
       <c r="F32" s="3">
+        <v>10200</v>
+      </c>
+      <c r="G32" s="3">
         <v>-600</v>
       </c>
-      <c r="G32" s="3">
-        <v>6100</v>
-      </c>
       <c r="H32" s="3">
-        <v>5500</v>
+        <v>6200</v>
       </c>
       <c r="I32" s="3">
-        <v>12000</v>
+        <v>5600</v>
       </c>
       <c r="J32" s="3">
+        <v>12300</v>
+      </c>
+      <c r="K32" s="3">
         <v>5600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>800</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-400</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-19900</v>
+        <v>-6700</v>
       </c>
       <c r="E33" s="3">
-        <v>-43100</v>
+        <v>-20300</v>
       </c>
       <c r="F33" s="3">
-        <v>-22200</v>
+        <v>-44000</v>
       </c>
       <c r="G33" s="3">
+        <v>-22600</v>
+      </c>
+      <c r="H33" s="3">
+        <v>-32200</v>
+      </c>
+      <c r="I33" s="3">
+        <v>-24700</v>
+      </c>
+      <c r="J33" s="3">
         <v>-31600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="K33" s="3">
+        <v>-26900</v>
+      </c>
+      <c r="L33" s="3">
         <v>-24200</v>
       </c>
-      <c r="I33" s="3">
-        <v>-30900</v>
-      </c>
-      <c r="J33" s="3">
-        <v>-26900</v>
-      </c>
-      <c r="K33" s="3">
-        <v>-24200</v>
-      </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-20900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-19100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-15300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-10900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-8000</v>
       </c>
-      <c r="Q33" s="3">
-        <v>0</v>
-      </c>
       <c r="R33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1992,113 +2068,122 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-19900</v>
+        <v>-6700</v>
       </c>
       <c r="E35" s="3">
-        <v>-43100</v>
+        <v>-20300</v>
       </c>
       <c r="F35" s="3">
-        <v>-22200</v>
+        <v>-44000</v>
       </c>
       <c r="G35" s="3">
+        <v>-22600</v>
+      </c>
+      <c r="H35" s="3">
+        <v>-32200</v>
+      </c>
+      <c r="I35" s="3">
+        <v>-24700</v>
+      </c>
+      <c r="J35" s="3">
         <v>-31600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="K35" s="3">
+        <v>-26900</v>
+      </c>
+      <c r="L35" s="3">
         <v>-24200</v>
       </c>
-      <c r="I35" s="3">
-        <v>-30900</v>
-      </c>
-      <c r="J35" s="3">
-        <v>-26900</v>
-      </c>
-      <c r="K35" s="3">
-        <v>-24200</v>
-      </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-20900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-19100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-15300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-10900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-8000</v>
       </c>
-      <c r="Q35" s="3">
-        <v>0</v>
-      </c>
       <c r="R35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2117,8 +2202,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2137,41 +2223,42 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>27200</v>
+        <v>23800</v>
       </c>
       <c r="E41" s="3">
-        <v>28100</v>
+        <v>27800</v>
       </c>
       <c r="F41" s="3">
-        <v>63800</v>
+        <v>28700</v>
       </c>
       <c r="G41" s="3">
-        <v>35300</v>
+        <v>65100</v>
       </c>
       <c r="H41" s="3">
-        <v>50400</v>
+        <v>36000</v>
       </c>
       <c r="I41" s="3">
-        <v>33000</v>
+        <v>51400</v>
       </c>
       <c r="J41" s="3">
+        <v>33700</v>
+      </c>
+      <c r="K41" s="3">
         <v>52800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>39600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>54300</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>4</v>
       </c>
@@ -2187,35 +2274,38 @@
       <c r="R41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E42" s="3">
-        <v>0</v>
+      <c r="D42" s="3">
+        <v>400</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F42" s="3">
         <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>18800</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>34400</v>
+        <v>19200</v>
       </c>
       <c r="I42" s="3">
-        <v>51400</v>
+        <v>35100</v>
       </c>
       <c r="J42" s="3">
+        <v>52500</v>
+      </c>
+      <c r="K42" s="3">
         <v>52200</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L42" s="3" t="s">
         <v>4</v>
       </c>
@@ -2231,47 +2321,50 @@
       <c r="P42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
+      <c r="Q42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>3800</v>
+        <v>15900</v>
       </c>
       <c r="E43" s="3">
-        <v>3800</v>
+        <v>3900</v>
       </c>
       <c r="F43" s="3">
-        <v>4700</v>
+        <v>3900</v>
       </c>
       <c r="G43" s="3">
-        <v>4100</v>
+        <v>4800</v>
       </c>
       <c r="H43" s="3">
+        <v>4200</v>
+      </c>
+      <c r="I43" s="3">
         <v>1600</v>
       </c>
-      <c r="I43" s="3">
-        <v>11800</v>
-      </c>
       <c r="J43" s="3">
+        <v>12100</v>
+      </c>
+      <c r="K43" s="3">
         <v>1100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>9300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>10800</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>4</v>
       </c>
@@ -2281,47 +2374,50 @@
       <c r="P43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
+      <c r="Q43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>5600</v>
+        <v>6100</v>
       </c>
       <c r="E44" s="3">
-        <v>7000</v>
+        <v>5700</v>
       </c>
       <c r="F44" s="3">
-        <v>10300</v>
+        <v>7200</v>
       </c>
       <c r="G44" s="3">
-        <v>10400</v>
+        <v>10500</v>
       </c>
       <c r="H44" s="3">
-        <v>9800</v>
+        <v>10600</v>
       </c>
       <c r="I44" s="3">
-        <v>9900</v>
+        <v>10000</v>
       </c>
       <c r="J44" s="3">
+        <v>10100</v>
+      </c>
+      <c r="K44" s="3">
         <v>7200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>7700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>5900</v>
       </c>
-      <c r="M44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N44" s="3" t="s">
         <v>4</v>
       </c>
@@ -2331,47 +2427,50 @@
       <c r="P44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>25700</v>
+        <v>23100</v>
       </c>
       <c r="E45" s="3">
-        <v>24400</v>
+        <v>26200</v>
       </c>
       <c r="F45" s="3">
-        <v>18500</v>
+        <v>24900</v>
       </c>
       <c r="G45" s="3">
-        <v>18800</v>
+        <v>18900</v>
       </c>
       <c r="H45" s="3">
-        <v>16000</v>
+        <v>19200</v>
       </c>
       <c r="I45" s="3">
-        <v>3900</v>
+        <v>16300</v>
       </c>
       <c r="J45" s="3">
+        <v>4000</v>
+      </c>
+      <c r="K45" s="3">
         <v>16300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>13300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>10400</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>4</v>
       </c>
@@ -2381,47 +2480,50 @@
       <c r="P45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="Q45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R45" s="3">
         <v>200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>62300</v>
+        <v>69400</v>
       </c>
       <c r="E46" s="3">
-        <v>63400</v>
+        <v>63600</v>
       </c>
       <c r="F46" s="3">
-        <v>97200</v>
+        <v>64700</v>
       </c>
       <c r="G46" s="3">
-        <v>87400</v>
+        <v>99200</v>
       </c>
       <c r="H46" s="3">
-        <v>112100</v>
+        <v>89200</v>
       </c>
       <c r="I46" s="3">
-        <v>110100</v>
+        <v>114400</v>
       </c>
       <c r="J46" s="3">
+        <v>112300</v>
+      </c>
+      <c r="K46" s="3">
         <v>129600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>70000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>81500</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>4</v>
       </c>
@@ -2431,14 +2533,17 @@
       <c r="P46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="Q46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R46" s="3">
         <v>200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2481,47 +2586,50 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>4</v>
+      <c r="Q47" s="3">
+        <v>0</v>
       </c>
       <c r="R47" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>190300</v>
+        <v>163500</v>
       </c>
       <c r="E48" s="3">
-        <v>212900</v>
+        <v>194200</v>
       </c>
       <c r="F48" s="3">
-        <v>232800</v>
+        <v>217200</v>
       </c>
       <c r="G48" s="3">
-        <v>234600</v>
+        <v>237600</v>
       </c>
       <c r="H48" s="3">
-        <v>228900</v>
+        <v>239400</v>
       </c>
       <c r="I48" s="3">
-        <v>230300</v>
+        <v>233500</v>
       </c>
       <c r="J48" s="3">
+        <v>235000</v>
+      </c>
+      <c r="K48" s="3">
         <v>88000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>81100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>77000</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>4</v>
       </c>
@@ -2531,47 +2639,50 @@
       <c r="P48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q48" s="3">
-        <v>0</v>
+      <c r="Q48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>20100</v>
+        <v>15200</v>
       </c>
       <c r="E49" s="3">
-        <v>20400</v>
+        <v>20500</v>
       </c>
       <c r="F49" s="3">
-        <v>18900</v>
+        <v>20800</v>
       </c>
       <c r="G49" s="3">
-        <v>18700</v>
+        <v>19300</v>
       </c>
       <c r="H49" s="3">
-        <v>18100</v>
+        <v>19000</v>
       </c>
       <c r="I49" s="3">
-        <v>13300</v>
+        <v>18500</v>
       </c>
       <c r="J49" s="3">
+        <v>13500</v>
+      </c>
+      <c r="K49" s="3">
         <v>11900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>11200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>10800</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N49" s="3" t="s">
         <v>4</v>
       </c>
@@ -2581,14 +2692,17 @@
       <c r="P49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q49" s="3">
-        <v>0</v>
+      <c r="Q49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2637,8 +2751,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2687,41 +2804,44 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>9000</v>
+        <v>8700</v>
       </c>
       <c r="E52" s="3">
-        <v>9500</v>
+        <v>9200</v>
       </c>
       <c r="F52" s="3">
+        <v>9600</v>
+      </c>
+      <c r="G52" s="3">
+        <v>11500</v>
+      </c>
+      <c r="H52" s="3">
+        <v>11800</v>
+      </c>
+      <c r="I52" s="3">
         <v>11300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="J52" s="3">
         <v>11600</v>
       </c>
-      <c r="H52" s="3">
-        <v>11100</v>
-      </c>
-      <c r="I52" s="3">
-        <v>11400</v>
-      </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>10900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>9700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>9400</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N52" s="3" t="s">
         <v>4</v>
       </c>
@@ -2737,8 +2857,11 @@
       <c r="R52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2787,41 +2910,44 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>281800</v>
+        <v>256800</v>
       </c>
       <c r="E54" s="3">
-        <v>306100</v>
+        <v>287500</v>
       </c>
       <c r="F54" s="3">
-        <v>360200</v>
+        <v>312300</v>
       </c>
       <c r="G54" s="3">
-        <v>352300</v>
+        <v>367600</v>
       </c>
       <c r="H54" s="3">
-        <v>370200</v>
+        <v>359500</v>
       </c>
       <c r="I54" s="3">
-        <v>365000</v>
+        <v>377700</v>
       </c>
       <c r="J54" s="3">
+        <v>372500</v>
+      </c>
+      <c r="K54" s="3">
         <v>240300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>172000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>178600</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>4</v>
       </c>
@@ -2831,14 +2957,17 @@
       <c r="P54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="Q54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R54" s="3">
         <v>200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2857,8 +2986,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2877,41 +3007,42 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>35400</v>
+        <v>28100</v>
       </c>
       <c r="E57" s="3">
-        <v>31100</v>
+        <v>36100</v>
       </c>
       <c r="F57" s="3">
-        <v>28600</v>
+        <v>31700</v>
       </c>
       <c r="G57" s="3">
-        <v>23900</v>
+        <v>29200</v>
       </c>
       <c r="H57" s="3">
-        <v>15000</v>
+        <v>24400</v>
       </c>
       <c r="I57" s="3">
-        <v>15900</v>
+        <v>15300</v>
       </c>
       <c r="J57" s="3">
+        <v>16200</v>
+      </c>
+      <c r="K57" s="3">
         <v>12700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>8100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>9600</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>4</v>
       </c>
@@ -2927,41 +3058,44 @@
       <c r="R57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>58400</v>
+        <v>55500</v>
       </c>
       <c r="E58" s="3">
-        <v>74400</v>
+        <v>59600</v>
       </c>
       <c r="F58" s="3">
-        <v>91000</v>
+        <v>75900</v>
       </c>
       <c r="G58" s="3">
-        <v>53800</v>
+        <v>92900</v>
       </c>
       <c r="H58" s="3">
-        <v>62400</v>
+        <v>54900</v>
       </c>
       <c r="I58" s="3">
-        <v>56300</v>
+        <v>63700</v>
       </c>
       <c r="J58" s="3">
+        <v>57500</v>
+      </c>
+      <c r="K58" s="3">
         <v>50300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>59300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>26700</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N58" s="3" t="s">
         <v>4</v>
       </c>
@@ -2971,47 +3105,50 @@
       <c r="P58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="Q58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R58" s="3">
         <v>100</v>
       </c>
-      <c r="R58" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>107400</v>
+        <v>70000</v>
       </c>
       <c r="E59" s="3">
-        <v>87400</v>
+        <v>109600</v>
       </c>
       <c r="F59" s="3">
-        <v>86200</v>
+        <v>89200</v>
       </c>
       <c r="G59" s="3">
-        <v>93000</v>
+        <v>88000</v>
       </c>
       <c r="H59" s="3">
-        <v>96800</v>
+        <v>94900</v>
       </c>
       <c r="I59" s="3">
-        <v>109900</v>
+        <v>98700</v>
       </c>
       <c r="J59" s="3">
+        <v>112200</v>
+      </c>
+      <c r="K59" s="3">
         <v>69100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>44300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>42600</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>4</v>
       </c>
@@ -3021,47 +3158,50 @@
       <c r="P59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q59" s="3">
-        <v>100</v>
+      <c r="Q59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R59" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>201100</v>
+        <v>153700</v>
       </c>
       <c r="E60" s="3">
-        <v>192800</v>
+        <v>205200</v>
       </c>
       <c r="F60" s="3">
-        <v>205900</v>
+        <v>196800</v>
       </c>
       <c r="G60" s="3">
-        <v>170600</v>
+        <v>210100</v>
       </c>
       <c r="H60" s="3">
-        <v>174200</v>
+        <v>174100</v>
       </c>
       <c r="I60" s="3">
-        <v>182100</v>
+        <v>177700</v>
       </c>
       <c r="J60" s="3">
+        <v>185800</v>
+      </c>
+      <c r="K60" s="3">
         <v>132000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>111700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>78900</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N60" s="3" t="s">
         <v>4</v>
       </c>
@@ -3071,47 +3211,50 @@
       <c r="P60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="Q60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R60" s="3">
         <v>200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>60600</v>
+        <v>120100</v>
       </c>
       <c r="E61" s="3">
-        <v>58900</v>
+        <v>61800</v>
       </c>
       <c r="F61" s="3">
-        <v>57100</v>
+        <v>60100</v>
       </c>
       <c r="G61" s="3">
-        <v>55800</v>
+        <v>58200</v>
       </c>
       <c r="H61" s="3">
-        <v>51700</v>
+        <v>57000</v>
       </c>
       <c r="I61" s="3">
-        <v>50100</v>
+        <v>52700</v>
       </c>
       <c r="J61" s="3">
+        <v>51200</v>
+      </c>
+      <c r="K61" s="3">
         <v>50700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>50800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>45900</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -3127,41 +3270,44 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>98400</v>
+        <v>68800</v>
       </c>
       <c r="E62" s="3">
-        <v>112700</v>
+        <v>100400</v>
       </c>
       <c r="F62" s="3">
-        <v>116900</v>
+        <v>115000</v>
       </c>
       <c r="G62" s="3">
-        <v>122700</v>
+        <v>119300</v>
       </c>
       <c r="H62" s="3">
-        <v>130200</v>
+        <v>125200</v>
       </c>
       <c r="I62" s="3">
-        <v>117500</v>
+        <v>132900</v>
       </c>
       <c r="J62" s="3">
+        <v>119900</v>
+      </c>
+      <c r="K62" s="3">
         <v>15600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>7700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>6700</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N62" s="3" t="s">
         <v>4</v>
       </c>
@@ -3177,8 +3323,11 @@
       <c r="R62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3227,8 +3376,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3277,8 +3429,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3327,41 +3482,44 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>361000</v>
+        <v>343600</v>
       </c>
       <c r="E66" s="3">
-        <v>365100</v>
+        <v>368400</v>
       </c>
       <c r="F66" s="3">
-        <v>380400</v>
+        <v>372600</v>
       </c>
       <c r="G66" s="3">
-        <v>349500</v>
+        <v>388200</v>
       </c>
       <c r="H66" s="3">
-        <v>356400</v>
+        <v>356600</v>
       </c>
       <c r="I66" s="3">
-        <v>350000</v>
+        <v>363600</v>
       </c>
       <c r="J66" s="3">
+        <v>357100</v>
+      </c>
+      <c r="K66" s="3">
         <v>198400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>170400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>132000</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>4</v>
       </c>
@@ -3371,14 +3529,17 @@
       <c r="P66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="Q66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R66" s="3">
         <v>200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3397,8 +3558,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3447,8 +3609,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3497,8 +3662,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3547,8 +3715,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3597,41 +3768,44 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-331600</v>
+        <v>-345100</v>
       </c>
       <c r="E72" s="3">
-        <v>-311700</v>
+        <v>-338400</v>
       </c>
       <c r="F72" s="3">
-        <v>-268600</v>
+        <v>-318100</v>
       </c>
       <c r="G72" s="3">
-        <v>-246400</v>
+        <v>-274100</v>
       </c>
       <c r="H72" s="3">
-        <v>-214800</v>
+        <v>-251500</v>
       </c>
       <c r="I72" s="3">
-        <v>-190700</v>
+        <v>-219200</v>
       </c>
       <c r="J72" s="3">
+        <v>-194600</v>
+      </c>
+      <c r="K72" s="3">
         <v>-159800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-133700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-88600</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>4</v>
       </c>
@@ -3641,14 +3815,17 @@
       <c r="P72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q72" s="3">
-        <v>0</v>
+      <c r="Q72" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3697,8 +3874,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3747,8 +3927,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3797,41 +3980,44 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>-79200</v>
+        <v>-86900</v>
       </c>
       <c r="E76" s="3">
-        <v>-59000</v>
+        <v>-80800</v>
       </c>
       <c r="F76" s="3">
-        <v>-20200</v>
+        <v>-60200</v>
       </c>
       <c r="G76" s="3">
+        <v>-20600</v>
+      </c>
+      <c r="H76" s="3">
         <v>2800</v>
       </c>
-      <c r="H76" s="3">
-        <v>13800</v>
-      </c>
       <c r="I76" s="3">
-        <v>15000</v>
+        <v>14100</v>
       </c>
       <c r="J76" s="3">
+        <v>15300</v>
+      </c>
+      <c r="K76" s="3">
         <v>41900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>46600</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>4</v>
       </c>
@@ -3841,14 +4027,17 @@
       <c r="P76" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q76" s="3">
-        <v>0</v>
+      <c r="Q76" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R76" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3897,113 +4086,122 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-19900</v>
+        <v>-6700</v>
       </c>
       <c r="E81" s="3">
-        <v>-43100</v>
+        <v>-20300</v>
       </c>
       <c r="F81" s="3">
-        <v>-22200</v>
+        <v>-44000</v>
       </c>
       <c r="G81" s="3">
+        <v>-22600</v>
+      </c>
+      <c r="H81" s="3">
+        <v>-32200</v>
+      </c>
+      <c r="I81" s="3">
+        <v>-24700</v>
+      </c>
+      <c r="J81" s="3">
         <v>-31600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="K81" s="3">
+        <v>-26900</v>
+      </c>
+      <c r="L81" s="3">
         <v>-24200</v>
       </c>
-      <c r="I81" s="3">
-        <v>-30900</v>
-      </c>
-      <c r="J81" s="3">
-        <v>-26900</v>
-      </c>
-      <c r="K81" s="3">
-        <v>-24200</v>
-      </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-20900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-19100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-15300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-10900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-8000</v>
       </c>
-      <c r="Q81" s="3">
-        <v>0</v>
-      </c>
       <c r="R81" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4022,8 +4220,9 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4072,8 +4271,11 @@
       <c r="R83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4122,8 +4324,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4172,8 +4377,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4222,8 +4430,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4272,8 +4483,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4322,58 +4536,64 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-3700</v>
+        <v>4500</v>
       </c>
       <c r="E89" s="3">
-        <v>-11100</v>
+        <v>-3800</v>
       </c>
       <c r="F89" s="3">
-        <v>-4200</v>
+        <v>-11400</v>
       </c>
       <c r="G89" s="3">
-        <v>0</v>
+        <v>-4300</v>
       </c>
       <c r="H89" s="3">
-        <v>-11800</v>
+        <v>0</v>
       </c>
       <c r="I89" s="3">
-        <v>-13300</v>
+        <v>-12000</v>
       </c>
       <c r="J89" s="3">
+        <v>-13500</v>
+      </c>
+      <c r="K89" s="3">
         <v>-5000</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L89" s="3" t="s">
         <v>4</v>
       </c>
       <c r="M89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N89" s="3">
+      <c r="N89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O89" s="3">
         <v>-25900</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q89" s="3">
-        <v>0</v>
+      <c r="Q89" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4392,8 +4612,9 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4442,8 +4663,11 @@
       <c r="R91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4492,8 +4716,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4542,47 +4769,50 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1000</v>
       </c>
-      <c r="E94" s="3">
-        <v>-9400</v>
-      </c>
       <c r="F94" s="3">
-        <v>8800</v>
+        <v>-9600</v>
       </c>
       <c r="G94" s="3">
-        <v>1900</v>
+        <v>9000</v>
       </c>
       <c r="H94" s="3">
-        <v>6900</v>
+        <v>2000</v>
       </c>
       <c r="I94" s="3">
-        <v>-13000</v>
+        <v>7100</v>
       </c>
       <c r="J94" s="3">
+        <v>-13200</v>
+      </c>
+      <c r="K94" s="3">
         <v>-59600</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>4</v>
       </c>
       <c r="M94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N94" s="3">
+      <c r="N94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O94" s="3">
         <v>-30400</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P94" s="3" t="s">
         <v>4</v>
       </c>
@@ -4592,8 +4822,11 @@
       <c r="R94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4612,8 +4845,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4662,8 +4896,11 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4712,8 +4949,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4762,8 +5002,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4812,47 +5055,50 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>3600</v>
+        <v>-5300</v>
       </c>
       <c r="E100" s="3">
-        <v>-16500</v>
+        <v>3700</v>
       </c>
       <c r="F100" s="3">
-        <v>23700</v>
+        <v>-16900</v>
       </c>
       <c r="G100" s="3">
-        <v>-18700</v>
+        <v>24200</v>
       </c>
       <c r="H100" s="3">
-        <v>22700</v>
+        <v>-19100</v>
       </c>
       <c r="I100" s="3">
-        <v>5100</v>
+        <v>23100</v>
       </c>
       <c r="J100" s="3">
+        <v>5200</v>
+      </c>
+      <c r="K100" s="3">
         <v>77800</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>4</v>
       </c>
       <c r="M100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N100" s="3">
+      <c r="N100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O100" s="3">
         <v>51000</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P100" s="3" t="s">
         <v>4</v>
       </c>
@@ -4862,104 +5108,113 @@
       <c r="R100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E101" s="3">
         <v>200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>1400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>1300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>100</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L101" s="3" t="s">
         <v>4</v>
       </c>
       <c r="M101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N101" s="3">
+      <c r="N101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O101" s="3">
         <v>-200</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-900</v>
       </c>
-      <c r="E102" s="3">
-        <v>-35700</v>
-      </c>
       <c r="F102" s="3">
-        <v>28500</v>
+        <v>-36400</v>
       </c>
       <c r="G102" s="3">
-        <v>-15100</v>
+        <v>29100</v>
       </c>
       <c r="H102" s="3">
-        <v>17300</v>
+        <v>-15400</v>
       </c>
       <c r="I102" s="3">
-        <v>-19800</v>
+        <v>17700</v>
       </c>
       <c r="J102" s="3">
+        <v>-20200</v>
+      </c>
+      <c r="K102" s="3">
         <v>13400</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L102" s="3" t="s">
         <v>4</v>
       </c>
       <c r="M102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N102" s="3">
+      <c r="N102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O102" s="3">
         <v>-5600</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q102" s="3">
-        <v>0</v>
+      <c r="Q102" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R102" s="3">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/THCH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/THCH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="92">
   <si>
     <t>THCH</t>
   </si>
@@ -656,250 +656,263 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>51700</v>
+        <v>51300</v>
       </c>
       <c r="E8" s="3">
-        <v>46800</v>
+        <v>50500</v>
       </c>
       <c r="F8" s="3">
+        <v>48000</v>
+      </c>
+      <c r="G8" s="3">
         <v>55200</v>
       </c>
-      <c r="G8" s="3">
-        <v>61500</v>
-      </c>
       <c r="H8" s="3">
-        <v>58000</v>
+        <v>59500</v>
       </c>
       <c r="I8" s="3">
-        <v>47400</v>
+        <v>56800</v>
       </c>
       <c r="J8" s="3">
+        <v>49000</v>
+      </c>
+      <c r="K8" s="3">
         <v>42500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>42200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>24900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>31200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>30900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>25100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>19300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>14600</v>
       </c>
-      <c r="R8" s="3">
-        <v>0</v>
-      </c>
       <c r="S8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>19000</v>
+        <v>30100</v>
       </c>
       <c r="E9" s="3">
-        <v>18000</v>
+        <v>32700</v>
       </c>
       <c r="F9" s="3">
-        <v>24200</v>
+        <v>36000</v>
       </c>
       <c r="G9" s="3">
-        <v>25300</v>
+        <v>40600</v>
       </c>
       <c r="H9" s="3">
-        <v>22700</v>
+        <v>41600</v>
       </c>
       <c r="I9" s="3">
-        <v>18400</v>
+        <v>40500</v>
       </c>
       <c r="J9" s="3">
+        <v>39000</v>
+      </c>
+      <c r="K9" s="3">
         <v>15700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>14700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>9300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>10900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>10800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>9000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>6700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>4900</v>
       </c>
-      <c r="R9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>32800</v>
+        <v>21200</v>
       </c>
       <c r="E10" s="3">
-        <v>28800</v>
+        <v>17800</v>
       </c>
       <c r="F10" s="3">
-        <v>30900</v>
+        <v>12000</v>
       </c>
       <c r="G10" s="3">
-        <v>36200</v>
+        <v>14600</v>
       </c>
       <c r="H10" s="3">
-        <v>35300</v>
+        <v>17800</v>
       </c>
       <c r="I10" s="3">
-        <v>29100</v>
+        <v>16300</v>
       </c>
       <c r="J10" s="3">
+        <v>10000</v>
+      </c>
+      <c r="K10" s="3">
         <v>26800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>27600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>15600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>20300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>20100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>16100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>12600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>9700</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -919,8 +932,9 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -972,8 +986,11 @@
       <c r="S12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1025,88 +1042,94 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>2300</v>
+        <v>6400</v>
       </c>
       <c r="E14" s="3">
-        <v>2700</v>
+        <v>5800</v>
       </c>
       <c r="F14" s="3">
-        <v>12600</v>
+        <v>4700</v>
       </c>
       <c r="G14" s="3">
-        <v>1800</v>
+        <v>21400</v>
       </c>
       <c r="H14" s="3">
-        <v>600</v>
+        <v>3900</v>
       </c>
       <c r="I14" s="3">
-        <v>600</v>
+        <v>1700</v>
       </c>
       <c r="J14" s="3">
+        <v>2900</v>
+      </c>
+      <c r="K14" s="3">
         <v>200</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>100</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>4</v>
+      <c r="R14" s="3">
+        <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>4300</v>
+        <v>4200</v>
       </c>
       <c r="E15" s="3">
+        <v>4200</v>
+      </c>
+      <c r="F15" s="3">
         <v>4700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>5000</v>
       </c>
-      <c r="G15" s="3">
-        <v>5100</v>
-      </c>
       <c r="H15" s="3">
-        <v>4900</v>
+        <v>5000</v>
       </c>
       <c r="I15" s="3">
-        <v>4600</v>
+        <v>4800</v>
       </c>
       <c r="J15" s="3">
+        <v>4800</v>
+      </c>
+      <c r="K15" s="3">
         <v>16700</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L15" s="3" t="s">
         <v>4</v>
       </c>
@@ -1119,8 +1142,8 @@
       <c r="O15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
+      <c r="P15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q15" s="3">
         <v>0</v>
@@ -1131,8 +1154,11 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1149,114 +1175,121 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>60900</v>
+        <v>56900</v>
       </c>
       <c r="E17" s="3">
-        <v>63900</v>
+        <v>57100</v>
       </c>
       <c r="F17" s="3">
-        <v>87900</v>
+        <v>63000</v>
       </c>
       <c r="G17" s="3">
-        <v>84000</v>
+        <v>74900</v>
       </c>
       <c r="H17" s="3">
-        <v>82200</v>
+        <v>76300</v>
       </c>
       <c r="I17" s="3">
-        <v>65800</v>
+        <v>80700</v>
       </c>
       <c r="J17" s="3">
+        <v>67200</v>
+      </c>
+      <c r="K17" s="3">
         <v>61000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>63000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>47800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>50000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>48800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>40700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>29700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>23000</v>
       </c>
-      <c r="R17" s="3">
-        <v>0</v>
-      </c>
       <c r="S17" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-9200</v>
+        <v>-5600</v>
       </c>
       <c r="E18" s="3">
-        <v>-17100</v>
+        <v>-6600</v>
       </c>
       <c r="F18" s="3">
-        <v>-32700</v>
+        <v>-15000</v>
       </c>
       <c r="G18" s="3">
-        <v>-22500</v>
+        <v>-19700</v>
       </c>
       <c r="H18" s="3">
-        <v>-24200</v>
+        <v>-16800</v>
       </c>
       <c r="I18" s="3">
-        <v>-18400</v>
+        <v>-23900</v>
       </c>
       <c r="J18" s="3">
+        <v>-18200</v>
+      </c>
+      <c r="K18" s="3">
         <v>-18500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-20800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-22900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-18700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-17900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-15600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-10400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-8500</v>
       </c>
-      <c r="R18" s="3">
-        <v>0</v>
-      </c>
       <c r="S18" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1276,84 +1309,88 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-3400</v>
+        <v>0</v>
       </c>
       <c r="E20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="G20" s="3">
+        <v>2300</v>
+      </c>
+      <c r="H20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I20" s="3">
+        <v>5300</v>
+      </c>
+      <c r="J20" s="3">
+        <v>4000</v>
+      </c>
+      <c r="K20" s="3">
+        <v>-12300</v>
+      </c>
+      <c r="L20" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="M20" s="3">
         <v>-1100</v>
       </c>
-      <c r="F20" s="3">
-        <v>-10200</v>
-      </c>
-      <c r="G20" s="3">
-        <v>600</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-6200</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-5600</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-12300</v>
-      </c>
-      <c r="K20" s="3">
-        <v>-5600</v>
-      </c>
-      <c r="L20" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-800</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>400</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-13100</v>
+        <v>-1400</v>
       </c>
       <c r="E21" s="3">
-        <v>-13400</v>
+        <v>-2400</v>
       </c>
       <c r="F21" s="3">
-        <v>-43000</v>
+        <v>-9800</v>
       </c>
       <c r="G21" s="3">
-        <v>-21600</v>
+        <v>-17000</v>
       </c>
       <c r="H21" s="3">
-        <v>-30200</v>
+        <v>-11700</v>
       </c>
       <c r="I21" s="3">
-        <v>-19300</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>4</v>
+        <v>-24500</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-17400</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>4</v>
@@ -1382,28 +1419,31 @@
       <c r="S21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>1300</v>
+        <v>600</v>
       </c>
       <c r="E22" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F22" s="3">
         <v>800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>700</v>
-      </c>
-      <c r="I22" s="3">
-        <v>600</v>
       </c>
       <c r="J22" s="3">
         <v>600</v>
@@ -1412,17 +1452,17 @@
         <v>600</v>
       </c>
       <c r="L22" s="3">
+        <v>600</v>
+      </c>
+      <c r="M22" s="3">
         <v>500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>200</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
       <c r="P22" s="3">
         <v>0</v>
       </c>
@@ -1435,84 +1475,90 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-13900</v>
+        <v>-12400</v>
       </c>
       <c r="E23" s="3">
-        <v>-19000</v>
+        <v>-13500</v>
       </c>
       <c r="F23" s="3">
+        <v>-19800</v>
+      </c>
+      <c r="G23" s="3">
         <v>-43900</v>
       </c>
-      <c r="G23" s="3">
-        <v>-22500</v>
-      </c>
       <c r="H23" s="3">
-        <v>-31100</v>
+        <v>-20200</v>
       </c>
       <c r="I23" s="3">
-        <v>-24600</v>
+        <v>-31400</v>
       </c>
       <c r="J23" s="3">
+        <v>-25400</v>
+      </c>
+      <c r="K23" s="3">
         <v>-31400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-26900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-24400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-21000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-18900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-15600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-10900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-8100</v>
       </c>
-      <c r="R23" s="3">
-        <v>0</v>
-      </c>
       <c r="S23" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G24" s="3">
         <v>0</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="H24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1541,8 +1587,11 @@
       <c r="S24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1594,114 +1643,123 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-14000</v>
+        <v>-12500</v>
       </c>
       <c r="E26" s="3">
-        <v>-19000</v>
+        <v>-13700</v>
       </c>
       <c r="F26" s="3">
+        <v>-19800</v>
+      </c>
+      <c r="G26" s="3">
         <v>-43900</v>
       </c>
-      <c r="G26" s="3">
-        <v>-22500</v>
-      </c>
       <c r="H26" s="3">
-        <v>-31100</v>
+        <v>-20200</v>
       </c>
       <c r="I26" s="3">
-        <v>-24600</v>
+        <v>-31400</v>
       </c>
       <c r="J26" s="3">
+        <v>-25400</v>
+      </c>
+      <c r="K26" s="3">
         <v>-31400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-26900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-24400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-21000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-18900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-15600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-10900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-8100</v>
       </c>
-      <c r="R26" s="3">
-        <v>0</v>
-      </c>
       <c r="S26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-14200</v>
+        <v>-12700</v>
       </c>
       <c r="E27" s="3">
-        <v>-19200</v>
+        <v>-6600</v>
       </c>
       <c r="F27" s="3">
+        <v>-19900</v>
+      </c>
+      <c r="G27" s="3">
         <v>-44000</v>
       </c>
-      <c r="G27" s="3">
-        <v>-22600</v>
-      </c>
       <c r="H27" s="3">
-        <v>-31200</v>
+        <v>-22000</v>
       </c>
       <c r="I27" s="3">
-        <v>-24700</v>
+        <v>-31500</v>
       </c>
       <c r="J27" s="3">
+        <v>-25500</v>
+      </c>
+      <c r="K27" s="3">
         <v>-31600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-26900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-24200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-20900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-19100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-15300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-10900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-8000</v>
       </c>
-      <c r="R27" s="3">
-        <v>0</v>
-      </c>
       <c r="S27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1753,34 +1811,37 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>7500</v>
+        <v>0</v>
       </c>
       <c r="E29" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>4</v>
+        <v>7300</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>-1000</v>
+        <v>-1700</v>
       </c>
       <c r="I29" s="3">
         <v>0</v>
       </c>
-      <c r="J29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K29" s="3">
-        <v>0</v>
+      <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L29" s="3">
         <v>0</v>
@@ -1806,8 +1867,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1859,8 +1923,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1912,114 +1979,123 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>3400</v>
+        <v>0</v>
       </c>
       <c r="E32" s="3">
+        <v>100</v>
+      </c>
+      <c r="F32" s="3">
+        <v>500</v>
+      </c>
+      <c r="G32" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="H32" s="3">
+        <v>100</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="K32" s="3">
+        <v>12300</v>
+      </c>
+      <c r="L32" s="3">
+        <v>5600</v>
+      </c>
+      <c r="M32" s="3">
         <v>1100</v>
       </c>
-      <c r="F32" s="3">
-        <v>10200</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-600</v>
-      </c>
-      <c r="H32" s="3">
-        <v>6200</v>
-      </c>
-      <c r="I32" s="3">
-        <v>5600</v>
-      </c>
-      <c r="J32" s="3">
-        <v>12300</v>
-      </c>
-      <c r="K32" s="3">
-        <v>5600</v>
-      </c>
-      <c r="L32" s="3">
-        <v>1100</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>800</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-400</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-6700</v>
+        <v>-12700</v>
       </c>
       <c r="E33" s="3">
-        <v>-20300</v>
+        <v>-6600</v>
       </c>
       <c r="F33" s="3">
+        <v>-19900</v>
+      </c>
+      <c r="G33" s="3">
         <v>-44000</v>
       </c>
-      <c r="G33" s="3">
-        <v>-22600</v>
-      </c>
       <c r="H33" s="3">
-        <v>-32200</v>
+        <v>-22000</v>
       </c>
       <c r="I33" s="3">
-        <v>-24700</v>
+        <v>-31500</v>
       </c>
       <c r="J33" s="3">
+        <v>-25500</v>
+      </c>
+      <c r="K33" s="3">
         <v>-31600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-26900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-24200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-20900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-19100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-15300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-10900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-8000</v>
       </c>
-      <c r="R33" s="3">
-        <v>0</v>
-      </c>
       <c r="S33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2071,119 +2147,128 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-6700</v>
+        <v>-12700</v>
       </c>
       <c r="E35" s="3">
-        <v>-20300</v>
+        <v>-6600</v>
       </c>
       <c r="F35" s="3">
+        <v>-19900</v>
+      </c>
+      <c r="G35" s="3">
         <v>-44000</v>
       </c>
-      <c r="G35" s="3">
-        <v>-22600</v>
-      </c>
       <c r="H35" s="3">
-        <v>-32200</v>
+        <v>-22000</v>
       </c>
       <c r="I35" s="3">
-        <v>-24700</v>
+        <v>-31500</v>
       </c>
       <c r="J35" s="3">
+        <v>-25500</v>
+      </c>
+      <c r="K35" s="3">
         <v>-31600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-26900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-24200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-20900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-19100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-15300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-10900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-8000</v>
       </c>
-      <c r="R35" s="3">
-        <v>0</v>
-      </c>
       <c r="S35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2203,8 +2288,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2224,44 +2310,45 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>23800</v>
+        <v>28000</v>
       </c>
       <c r="E41" s="3">
-        <v>27800</v>
+        <v>23200</v>
       </c>
       <c r="F41" s="3">
+        <v>27300</v>
+      </c>
+      <c r="G41" s="3">
         <v>28700</v>
       </c>
-      <c r="G41" s="3">
-        <v>65100</v>
-      </c>
       <c r="H41" s="3">
-        <v>36000</v>
+        <v>63300</v>
       </c>
       <c r="I41" s="3">
-        <v>51400</v>
+        <v>35200</v>
       </c>
       <c r="J41" s="3">
+        <v>53100</v>
+      </c>
+      <c r="K41" s="3">
         <v>33700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>52800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>39600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>54300</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>4</v>
       </c>
@@ -2277,38 +2364,41 @@
       <c r="S41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E42" s="3">
         <v>400</v>
       </c>
-      <c r="E42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>2900</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>3300</v>
       </c>
       <c r="H42" s="3">
-        <v>19200</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3">
-        <v>35100</v>
+        <v>18800</v>
       </c>
       <c r="J42" s="3">
+        <v>37000</v>
+      </c>
+      <c r="K42" s="3">
         <v>52500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>52200</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M42" s="3" t="s">
         <v>4</v>
       </c>
@@ -2324,50 +2414,53 @@
       <c r="Q42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R42" s="3">
-        <v>0</v>
+      <c r="R42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>15900</v>
+        <v>5900</v>
       </c>
       <c r="E43" s="3">
-        <v>3900</v>
+        <v>15600</v>
       </c>
       <c r="F43" s="3">
-        <v>3900</v>
+        <v>3800</v>
       </c>
       <c r="G43" s="3">
-        <v>4800</v>
+        <v>22500</v>
       </c>
       <c r="H43" s="3">
-        <v>4200</v>
+        <v>4600</v>
       </c>
       <c r="I43" s="3">
-        <v>1600</v>
+        <v>4100</v>
       </c>
       <c r="J43" s="3">
+        <v>14400</v>
+      </c>
+      <c r="K43" s="3">
         <v>12100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>9300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>10800</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>4</v>
       </c>
@@ -2377,50 +2470,53 @@
       <c r="Q43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R43" s="3">
-        <v>0</v>
+      <c r="R43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>6100</v>
+        <v>5000</v>
       </c>
       <c r="E44" s="3">
-        <v>5700</v>
+        <v>5900</v>
       </c>
       <c r="F44" s="3">
+        <v>5600</v>
+      </c>
+      <c r="G44" s="3">
         <v>7200</v>
       </c>
-      <c r="G44" s="3">
-        <v>10500</v>
-      </c>
       <c r="H44" s="3">
-        <v>10600</v>
+        <v>10200</v>
       </c>
       <c r="I44" s="3">
-        <v>10000</v>
+        <v>10400</v>
       </c>
       <c r="J44" s="3">
+        <v>10400</v>
+      </c>
+      <c r="K44" s="3">
         <v>10100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>7200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>7700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>5900</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O44" s="3" t="s">
         <v>4</v>
       </c>
@@ -2430,50 +2526,53 @@
       <c r="Q44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R44" s="3">
-        <v>0</v>
+      <c r="R44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>23100</v>
-      </c>
-      <c r="E45" s="3">
-        <v>26200</v>
-      </c>
-      <c r="F45" s="3">
-        <v>24900</v>
+      <c r="D45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G45" s="3">
-        <v>18900</v>
-      </c>
-      <c r="H45" s="3">
-        <v>19200</v>
-      </c>
-      <c r="I45" s="3">
+        <v>2100</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J45" s="3">
+        <v>2600</v>
+      </c>
+      <c r="K45" s="3">
+        <v>4000</v>
+      </c>
+      <c r="L45" s="3">
         <v>16300</v>
       </c>
-      <c r="J45" s="3">
-        <v>4000</v>
-      </c>
-      <c r="K45" s="3">
-        <v>16300</v>
-      </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>13300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>10400</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>4</v>
       </c>
@@ -2483,50 +2582,53 @@
       <c r="Q45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R45" s="3">
+      <c r="R45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S45" s="3">
         <v>200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>69400</v>
+        <v>63000</v>
       </c>
       <c r="E46" s="3">
-        <v>63600</v>
+        <v>67700</v>
       </c>
       <c r="F46" s="3">
+        <v>62400</v>
+      </c>
+      <c r="G46" s="3">
         <v>64700</v>
       </c>
-      <c r="G46" s="3">
-        <v>99200</v>
-      </c>
       <c r="H46" s="3">
-        <v>89200</v>
+        <v>96400</v>
       </c>
       <c r="I46" s="3">
-        <v>114400</v>
+        <v>87200</v>
       </c>
       <c r="J46" s="3">
+        <v>118200</v>
+      </c>
+      <c r="K46" s="3">
         <v>112300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>129600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>70000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>81500</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>4</v>
       </c>
@@ -2536,37 +2638,40 @@
       <c r="Q46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R46" s="3">
+      <c r="R46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S46" s="3">
         <v>200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2589,50 +2694,53 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>4</v>
+      <c r="R47" s="3">
+        <v>0</v>
       </c>
       <c r="S47" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>163500</v>
+        <v>152900</v>
       </c>
       <c r="E48" s="3">
-        <v>194200</v>
+        <v>159600</v>
       </c>
       <c r="F48" s="3">
-        <v>217200</v>
+        <v>190800</v>
       </c>
       <c r="G48" s="3">
-        <v>237600</v>
+        <v>217300</v>
       </c>
       <c r="H48" s="3">
-        <v>239400</v>
+        <v>231000</v>
       </c>
       <c r="I48" s="3">
-        <v>233500</v>
+        <v>234200</v>
       </c>
       <c r="J48" s="3">
+        <v>241200</v>
+      </c>
+      <c r="K48" s="3">
         <v>235000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>88000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>81100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>77000</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>4</v>
       </c>
@@ -2642,50 +2750,53 @@
       <c r="Q48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R48" s="3">
-        <v>0</v>
+      <c r="R48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>15200</v>
+        <v>14500</v>
       </c>
       <c r="E49" s="3">
-        <v>20500</v>
+        <v>14800</v>
       </c>
       <c r="F49" s="3">
+        <v>20200</v>
+      </c>
+      <c r="G49" s="3">
         <v>20800</v>
       </c>
-      <c r="G49" s="3">
-        <v>19300</v>
-      </c>
       <c r="H49" s="3">
-        <v>19000</v>
+        <v>18800</v>
       </c>
       <c r="I49" s="3">
-        <v>18500</v>
+        <v>18600</v>
       </c>
       <c r="J49" s="3">
+        <v>19100</v>
+      </c>
+      <c r="K49" s="3">
         <v>13500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>11900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>11200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>10800</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O49" s="3" t="s">
         <v>4</v>
       </c>
@@ -2695,14 +2806,17 @@
       <c r="Q49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R49" s="3">
-        <v>0</v>
+      <c r="R49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2754,8 +2868,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2807,44 +2924,47 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>8700</v>
+        <v>8600</v>
       </c>
       <c r="E52" s="3">
-        <v>9200</v>
+        <v>8500</v>
       </c>
       <c r="F52" s="3">
+        <v>9000</v>
+      </c>
+      <c r="G52" s="3">
         <v>9600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
+        <v>11200</v>
+      </c>
+      <c r="I52" s="3">
         <v>11500</v>
       </c>
-      <c r="H52" s="3">
-        <v>11800</v>
-      </c>
-      <c r="I52" s="3">
-        <v>11300</v>
-      </c>
       <c r="J52" s="3">
+        <v>11700</v>
+      </c>
+      <c r="K52" s="3">
         <v>11600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>10900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>9700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>9400</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>4</v>
       </c>
@@ -2860,8 +2980,11 @@
       <c r="S52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2913,44 +3036,47 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>256800</v>
+        <v>239000</v>
       </c>
       <c r="E54" s="3">
-        <v>287500</v>
+        <v>250600</v>
       </c>
       <c r="F54" s="3">
-        <v>312300</v>
+        <v>282500</v>
       </c>
       <c r="G54" s="3">
-        <v>367600</v>
+        <v>312400</v>
       </c>
       <c r="H54" s="3">
-        <v>359500</v>
+        <v>357300</v>
       </c>
       <c r="I54" s="3">
-        <v>377700</v>
+        <v>351600</v>
       </c>
       <c r="J54" s="3">
+        <v>390100</v>
+      </c>
+      <c r="K54" s="3">
         <v>372500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>240300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>172000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>178600</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>4</v>
       </c>
@@ -2960,14 +3086,17 @@
       <c r="Q54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R54" s="3">
+      <c r="R54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S54" s="3">
         <v>200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2987,8 +3116,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3008,44 +3138,45 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>28100</v>
+        <v>29000</v>
       </c>
       <c r="E57" s="3">
-        <v>36100</v>
+        <v>27500</v>
       </c>
       <c r="F57" s="3">
-        <v>31700</v>
+        <v>35500</v>
       </c>
       <c r="G57" s="3">
-        <v>29200</v>
+        <v>32300</v>
       </c>
       <c r="H57" s="3">
-        <v>24400</v>
+        <v>28400</v>
       </c>
       <c r="I57" s="3">
-        <v>15300</v>
+        <v>23800</v>
       </c>
       <c r="J57" s="3">
+        <v>16800</v>
+      </c>
+      <c r="K57" s="3">
         <v>16200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>12700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>8100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>9600</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>4</v>
       </c>
@@ -3061,44 +3192,47 @@
       <c r="S57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>55500</v>
+        <v>144600</v>
       </c>
       <c r="E58" s="3">
-        <v>59600</v>
+        <v>78600</v>
       </c>
       <c r="F58" s="3">
-        <v>75900</v>
+        <v>86900</v>
       </c>
       <c r="G58" s="3">
-        <v>92900</v>
+        <v>104200</v>
       </c>
       <c r="H58" s="3">
-        <v>54900</v>
+        <v>118000</v>
       </c>
       <c r="I58" s="3">
-        <v>63700</v>
+        <v>82200</v>
       </c>
       <c r="J58" s="3">
+        <v>91900</v>
+      </c>
+      <c r="K58" s="3">
         <v>57500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>50300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>59300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>26700</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O58" s="3" t="s">
         <v>4</v>
       </c>
@@ -3108,50 +3242,53 @@
       <c r="Q58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R58" s="3">
+      <c r="R58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S58" s="3">
         <v>100</v>
       </c>
-      <c r="S58" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>70000</v>
+        <v>37100</v>
       </c>
       <c r="E59" s="3">
-        <v>109600</v>
+        <v>43900</v>
       </c>
       <c r="F59" s="3">
-        <v>89200</v>
+        <v>79200</v>
       </c>
       <c r="G59" s="3">
-        <v>88000</v>
+        <v>40100</v>
       </c>
       <c r="H59" s="3">
-        <v>94900</v>
+        <v>57800</v>
       </c>
       <c r="I59" s="3">
-        <v>98700</v>
+        <v>64200</v>
       </c>
       <c r="J59" s="3">
+        <v>51200</v>
+      </c>
+      <c r="K59" s="3">
         <v>112200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>69100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>44300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>42600</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>4</v>
       </c>
@@ -3161,50 +3298,53 @@
       <c r="Q59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R59" s="3">
-        <v>100</v>
+      <c r="R59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S59" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>153700</v>
+        <v>210700</v>
       </c>
       <c r="E60" s="3">
-        <v>205200</v>
+        <v>150000</v>
       </c>
       <c r="F60" s="3">
+        <v>201600</v>
+      </c>
+      <c r="G60" s="3">
         <v>196800</v>
       </c>
-      <c r="G60" s="3">
-        <v>210100</v>
-      </c>
       <c r="H60" s="3">
-        <v>174100</v>
+        <v>204200</v>
       </c>
       <c r="I60" s="3">
-        <v>177700</v>
+        <v>170300</v>
       </c>
       <c r="J60" s="3">
+        <v>183500</v>
+      </c>
+      <c r="K60" s="3">
         <v>185800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>132000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>111700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>78900</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>4</v>
       </c>
@@ -3214,50 +3354,53 @@
       <c r="Q60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R60" s="3">
+      <c r="R60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S60" s="3">
         <v>200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>120100</v>
+        <v>123600</v>
       </c>
       <c r="E61" s="3">
-        <v>61800</v>
+        <v>182600</v>
       </c>
       <c r="F61" s="3">
-        <v>60100</v>
+        <v>144200</v>
       </c>
       <c r="G61" s="3">
-        <v>58200</v>
+        <v>159900</v>
       </c>
       <c r="H61" s="3">
-        <v>57000</v>
+        <v>162100</v>
       </c>
       <c r="I61" s="3">
-        <v>52700</v>
+        <v>166800</v>
       </c>
       <c r="J61" s="3">
+        <v>169200</v>
+      </c>
+      <c r="K61" s="3">
         <v>51200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>50700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>50800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>45900</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -3273,44 +3416,47 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>68800</v>
+        <v>1100</v>
       </c>
       <c r="E62" s="3">
-        <v>100400</v>
+        <v>1100</v>
       </c>
       <c r="F62" s="3">
-        <v>115000</v>
+        <v>14500</v>
       </c>
       <c r="G62" s="3">
-        <v>119300</v>
+        <v>14500</v>
       </c>
       <c r="H62" s="3">
-        <v>125200</v>
+        <v>9800</v>
       </c>
       <c r="I62" s="3">
-        <v>132900</v>
+        <v>10800</v>
       </c>
       <c r="J62" s="3">
+        <v>22000</v>
+      </c>
+      <c r="K62" s="3">
         <v>119900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>15600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>7700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>6700</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>4</v>
       </c>
@@ -3326,8 +3472,11 @@
       <c r="S62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3379,8 +3528,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3432,8 +3584,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3485,44 +3640,47 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>343600</v>
+        <v>336300</v>
       </c>
       <c r="E66" s="3">
-        <v>368400</v>
+        <v>334400</v>
       </c>
       <c r="F66" s="3">
-        <v>372600</v>
+        <v>361000</v>
       </c>
       <c r="G66" s="3">
-        <v>388200</v>
+        <v>372000</v>
       </c>
       <c r="H66" s="3">
-        <v>356600</v>
+        <v>376800</v>
       </c>
       <c r="I66" s="3">
-        <v>363600</v>
+        <v>348400</v>
       </c>
       <c r="J66" s="3">
+        <v>375200</v>
+      </c>
+      <c r="K66" s="3">
         <v>357100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>198400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>170400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>132000</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>4</v>
       </c>
@@ -3532,14 +3690,17 @@
       <c r="Q66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R66" s="3">
+      <c r="R66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S66" s="3">
         <v>200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3559,8 +3720,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3612,8 +3774,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3665,8 +3830,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3718,8 +3886,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3771,44 +3942,47 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-345100</v>
+        <v>-361700</v>
       </c>
       <c r="E72" s="3">
-        <v>-338400</v>
+        <v>-336900</v>
       </c>
       <c r="F72" s="3">
-        <v>-318100</v>
+        <v>-332500</v>
       </c>
       <c r="G72" s="3">
-        <v>-274100</v>
+        <v>-318200</v>
       </c>
       <c r="H72" s="3">
-        <v>-251500</v>
+        <v>-266500</v>
       </c>
       <c r="I72" s="3">
-        <v>-219200</v>
+        <v>-246000</v>
       </c>
       <c r="J72" s="3">
+        <v>-226400</v>
+      </c>
+      <c r="K72" s="3">
         <v>-194600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-159800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-133700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-88600</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>4</v>
       </c>
@@ -3818,14 +3992,17 @@
       <c r="Q72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R72" s="3">
-        <v>0</v>
+      <c r="R72" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3877,8 +4054,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3930,8 +4110,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3983,44 +4166,47 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>-86900</v>
+        <v>-98600</v>
       </c>
       <c r="E76" s="3">
-        <v>-80800</v>
+        <v>-84800</v>
       </c>
       <c r="F76" s="3">
+        <v>-79400</v>
+      </c>
+      <c r="G76" s="3">
         <v>-60200</v>
       </c>
-      <c r="G76" s="3">
-        <v>-20600</v>
-      </c>
       <c r="H76" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="I76" s="3">
         <v>2800</v>
       </c>
-      <c r="I76" s="3">
-        <v>14100</v>
-      </c>
       <c r="J76" s="3">
+        <v>14600</v>
+      </c>
+      <c r="K76" s="3">
         <v>15300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>41900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>46600</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>4</v>
       </c>
@@ -4030,14 +4216,17 @@
       <c r="Q76" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R76" s="3">
-        <v>0</v>
+      <c r="R76" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S76" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4089,119 +4278,128 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-6700</v>
+        <v>-12700</v>
       </c>
       <c r="E81" s="3">
-        <v>-20300</v>
+        <v>-6600</v>
       </c>
       <c r="F81" s="3">
+        <v>-19900</v>
+      </c>
+      <c r="G81" s="3">
         <v>-44000</v>
       </c>
-      <c r="G81" s="3">
-        <v>-22600</v>
-      </c>
       <c r="H81" s="3">
-        <v>-32200</v>
+        <v>-22000</v>
       </c>
       <c r="I81" s="3">
-        <v>-24700</v>
+        <v>-31500</v>
       </c>
       <c r="J81" s="3">
+        <v>-25500</v>
+      </c>
+      <c r="K81" s="3">
         <v>-31600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-26900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-24200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-20900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-19100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-15300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-10900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-8000</v>
       </c>
-      <c r="R81" s="3">
-        <v>0</v>
-      </c>
       <c r="S81" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4221,31 +4419,32 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>5600</v>
       </c>
       <c r="E83" s="3">
-        <v>0</v>
+        <v>4800</v>
       </c>
       <c r="F83" s="3">
-        <v>0</v>
+        <v>5600</v>
       </c>
       <c r="G83" s="3">
-        <v>0</v>
+        <v>4200</v>
       </c>
       <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
+        <v>5100</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J83" s="3">
-        <v>0</v>
+        <v>4600</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -4274,8 +4473,11 @@
       <c r="S83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4327,8 +4529,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4380,8 +4585,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4433,8 +4641,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4486,8 +4697,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4539,61 +4753,67 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>4500</v>
+        <v>-1900</v>
       </c>
       <c r="E89" s="3">
-        <v>-3800</v>
+        <v>4400</v>
       </c>
       <c r="F89" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="G89" s="3">
         <v>-11400</v>
       </c>
-      <c r="G89" s="3">
-        <v>-4300</v>
-      </c>
       <c r="H89" s="3">
-        <v>0</v>
+        <v>-4200</v>
       </c>
       <c r="I89" s="3">
-        <v>-12000</v>
+        <v>0</v>
       </c>
       <c r="J89" s="3">
+        <v>-12400</v>
+      </c>
+      <c r="K89" s="3">
         <v>-13500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-5000</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>4</v>
       </c>
       <c r="N89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O89" s="3">
+      <c r="O89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P89" s="3">
         <v>-25900</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R89" s="3">
-        <v>0</v>
+      <c r="R89" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4613,31 +4833,32 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>-154600</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-180400</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+        <v>-41200</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -4666,8 +4887,11 @@
       <c r="S91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4719,8 +4943,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4772,50 +4999,53 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-3000</v>
+        <v>1100</v>
       </c>
       <c r="E94" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="F94" s="3">
         <v>-1000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-9600</v>
       </c>
-      <c r="G94" s="3">
-        <v>9000</v>
-      </c>
       <c r="H94" s="3">
-        <v>2000</v>
+        <v>8700</v>
       </c>
       <c r="I94" s="3">
-        <v>7100</v>
+        <v>1900</v>
       </c>
       <c r="J94" s="3">
+        <v>7300</v>
+      </c>
+      <c r="K94" s="3">
         <v>-13200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-59600</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>4</v>
       </c>
       <c r="N94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O94" s="3">
+      <c r="O94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P94" s="3">
         <v>-30400</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q94" s="3" t="s">
         <v>4</v>
       </c>
@@ -4825,8 +5055,11 @@
       <c r="S94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4846,31 +5079,32 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -4899,8 +5133,11 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4952,8 +5189,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5005,8 +5245,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5058,50 +5301,53 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-5300</v>
+        <v>4000</v>
       </c>
       <c r="E100" s="3">
-        <v>3700</v>
+        <v>-5200</v>
       </c>
       <c r="F100" s="3">
+        <v>3600</v>
+      </c>
+      <c r="G100" s="3">
         <v>-16900</v>
       </c>
-      <c r="G100" s="3">
-        <v>24200</v>
-      </c>
       <c r="H100" s="3">
-        <v>-19100</v>
+        <v>23500</v>
       </c>
       <c r="I100" s="3">
-        <v>23100</v>
+        <v>-18700</v>
       </c>
       <c r="J100" s="3">
+        <v>23900</v>
+      </c>
+      <c r="K100" s="3">
         <v>5200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>77800</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>4</v>
       </c>
       <c r="N100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O100" s="3">
+      <c r="O100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P100" s="3">
         <v>51000</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>4</v>
       </c>
@@ -5111,110 +5357,119 @@
       <c r="S100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="E101" s="3">
-        <v>200</v>
+        <v>1700</v>
       </c>
       <c r="F101" s="3">
+        <v>-500</v>
+      </c>
+      <c r="G101" s="3">
         <v>1400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>100</v>
       </c>
-      <c r="H101" s="3">
-        <v>1700</v>
-      </c>
-      <c r="I101" s="3">
-        <v>-500</v>
+      <c r="I101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J101" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K101" s="3">
         <v>1300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>100</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M101" s="3" t="s">
         <v>4</v>
       </c>
       <c r="N101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O101" s="3">
+      <c r="O101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P101" s="3">
         <v>-200</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
+      <c r="R101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-4000</v>
+        <v>4000</v>
       </c>
       <c r="E102" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="F102" s="3">
         <v>-900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-36400</v>
       </c>
-      <c r="G102" s="3">
-        <v>29100</v>
-      </c>
       <c r="H102" s="3">
-        <v>-15400</v>
+        <v>28300</v>
       </c>
       <c r="I102" s="3">
-        <v>17700</v>
+        <v>-15000</v>
       </c>
       <c r="J102" s="3">
+        <v>18300</v>
+      </c>
+      <c r="K102" s="3">
         <v>-20200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>13400</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M102" s="3" t="s">
         <v>4</v>
       </c>
       <c r="N102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O102" s="3">
+      <c r="O102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P102" s="3">
         <v>-5600</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R102" s="3">
-        <v>0</v>
+      <c r="R102" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S102" s="3">
+        <v>0</v>
+      </c>
+      <c r="T102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/THCH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/THCH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="92">
   <si>
     <t>THCH</t>
   </si>
@@ -656,263 +656,275 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>45600</v>
+      </c>
+      <c r="E8" s="3">
         <v>51300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>50500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>48000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>55200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>59500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>56800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>49000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>42500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>42200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>24900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>31200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>30900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>25100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>19300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>14600</v>
       </c>
-      <c r="S8" s="3">
-        <v>0</v>
-      </c>
       <c r="T8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>28800</v>
+      </c>
+      <c r="E9" s="3">
         <v>30100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>32700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>36000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>40600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>41600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>40500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>39000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>15700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>14700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>9300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>10900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>10800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>9000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>6700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>4900</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>16700</v>
+      </c>
+      <c r="E10" s="3">
         <v>21200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>17800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>12000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>14600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>17800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>16300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>10000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>26800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>27600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>15600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>20300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>20100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>16100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>12600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>9700</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -933,8 +945,9 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -989,8 +1002,11 @@
       <c r="T12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1045,94 +1061,100 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E14" s="3">
         <v>6400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>5800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>4700</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>21400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>3900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>200</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>100</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>4</v>
+      <c r="S14" s="3">
+        <v>0</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>4200</v>
+        <v>4900</v>
       </c>
       <c r="E15" s="3">
         <v>4200</v>
       </c>
       <c r="F15" s="3">
+        <v>4200</v>
+      </c>
+      <c r="G15" s="3">
         <v>4700</v>
-      </c>
-      <c r="G15" s="3">
-        <v>5000</v>
       </c>
       <c r="H15" s="3">
         <v>5000</v>
       </c>
       <c r="I15" s="3">
-        <v>4800</v>
+        <v>5000</v>
       </c>
       <c r="J15" s="3">
         <v>4800</v>
       </c>
       <c r="K15" s="3">
+        <v>4800</v>
+      </c>
+      <c r="L15" s="3">
         <v>16700</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M15" s="3" t="s">
         <v>4</v>
       </c>
@@ -1145,8 +1167,8 @@
       <c r="P15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
+      <c r="Q15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R15" s="3">
         <v>0</v>
@@ -1157,8 +1179,11 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1176,120 +1201,127 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>59400</v>
+      </c>
+      <c r="E17" s="3">
         <v>56900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>57100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>63000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>74900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>76300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>80700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>67200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>61000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>63000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>47800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>50000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>48800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>40700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>29700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>23000</v>
       </c>
-      <c r="S17" s="3">
-        <v>0</v>
-      </c>
       <c r="T17" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-13800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-5600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-6600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-15000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-19700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-16800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-23900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-18200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-18500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-20800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-22900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-18700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-17900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-15600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-10400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-8500</v>
       </c>
-      <c r="S18" s="3">
-        <v>0</v>
-      </c>
       <c r="T18" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1310,91 +1342,95 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>5300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>4000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-12300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-5600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-800</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>-500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>400</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-1400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-2400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-9800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-17000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-11700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-24500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-17400</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1422,31 +1458,34 @@
       <c r="T21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>500</v>
+      </c>
+      <c r="E22" s="3">
         <v>600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>700</v>
-      </c>
-      <c r="J22" s="3">
-        <v>600</v>
       </c>
       <c r="K22" s="3">
         <v>600</v>
@@ -1455,17 +1494,17 @@
         <v>600</v>
       </c>
       <c r="M22" s="3">
+        <v>600</v>
+      </c>
+      <c r="N22" s="3">
         <v>500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>200</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
       <c r="Q22" s="3">
         <v>0</v>
       </c>
@@ -1478,64 +1517,70 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-18900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-12400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-13500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-19800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-43900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-20200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-31400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-25400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-31400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-26900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-24400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-21000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-18900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-15600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-10900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-8100</v>
       </c>
-      <c r="S23" s="3">
-        <v>0</v>
-      </c>
       <c r="T23" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1545,14 +1590,14 @@
       <c r="E24" s="3">
         <v>100</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>4</v>
+      <c r="F24" s="3">
+        <v>100</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H24" s="3">
+        <v>0</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>4</v>
@@ -1560,8 +1605,8 @@
       <c r="J24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
@@ -1590,8 +1635,11 @@
       <c r="T24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1646,120 +1694,129 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-19000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-12500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-13700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-19800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-43900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-20200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-31400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-25400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-31400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-26900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-24400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-21000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-18900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-15600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-10900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-8100</v>
       </c>
-      <c r="S26" s="3">
-        <v>0</v>
-      </c>
       <c r="T26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-18900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-12700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-6600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-19900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-44000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-22000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-31500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-25500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-31600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-26900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-24200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-20900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-19100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-15300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-10900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-8000</v>
       </c>
-      <c r="S27" s="3">
-        <v>0</v>
-      </c>
       <c r="T27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1814,8 +1871,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1823,28 +1883,28 @@
         <v>0</v>
       </c>
       <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
         <v>7300</v>
       </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
       <c r="G29" s="3">
         <v>0</v>
       </c>
       <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
         <v>-1700</v>
       </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L29" s="3">
-        <v>0</v>
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M29" s="3">
         <v>0</v>
@@ -1870,8 +1930,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1926,8 +1989,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1982,120 +2048,129 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-5300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-4000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>12300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>5600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>800</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-400</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-18900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-12700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-6600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-19900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-44000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-22000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-31500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-25500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-31600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-26900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-24200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-20900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-19100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-15300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-10900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-8000</v>
       </c>
-      <c r="S33" s="3">
-        <v>0</v>
-      </c>
       <c r="T33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2150,125 +2225,134 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-18900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-12700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-6600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-19900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-44000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-22000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-31500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-25500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-31600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-26900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-24200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-20900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-19100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-15300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-10900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-8000</v>
       </c>
-      <c r="S35" s="3">
-        <v>0</v>
-      </c>
       <c r="T35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2289,8 +2373,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2311,47 +2396,48 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>20900</v>
+      </c>
+      <c r="E41" s="3">
         <v>28000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>23200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>27300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>28700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>63300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>35200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>53100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>33700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>52800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>39600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>54300</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>4</v>
       </c>
@@ -2367,41 +2453,44 @@
       <c r="T41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>1000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>2900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>3300</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>18800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>37000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>52500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>52200</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N42" s="3" t="s">
         <v>4</v>
       </c>
@@ -2417,53 +2506,56 @@
       <c r="R42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S42" s="3">
-        <v>0</v>
+      <c r="S42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E43" s="3">
         <v>5900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>15600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>22500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>14400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>12100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>9300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>10800</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>4</v>
       </c>
@@ -2473,53 +2565,56 @@
       <c r="R43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S43" s="3">
-        <v>0</v>
+      <c r="S43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E44" s="3">
         <v>5000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>5900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>5600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>7200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>10200</v>
-      </c>
-      <c r="I44" s="3">
-        <v>10400</v>
       </c>
       <c r="J44" s="3">
         <v>10400</v>
       </c>
       <c r="K44" s="3">
+        <v>10400</v>
+      </c>
+      <c r="L44" s="3">
         <v>10100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>7200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>7700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>5900</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P44" s="3" t="s">
         <v>4</v>
       </c>
@@ -2529,14 +2624,17 @@
       <c r="R44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S44" s="3">
-        <v>0</v>
+      <c r="S44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2549,33 +2647,33 @@
       <c r="F45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H45" s="3">
         <v>2100</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K45" s="3">
         <v>2600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>4000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>16300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>13300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>10400</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>4</v>
       </c>
@@ -2585,53 +2683,56 @@
       <c r="R45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S45" s="3">
+      <c r="S45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T45" s="3">
         <v>200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>57100</v>
+      </c>
+      <c r="E46" s="3">
         <v>63000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>67700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>62400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>64700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>96400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>87200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>118200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>112300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>129600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>70000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>81500</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>4</v>
       </c>
@@ -2641,14 +2742,17 @@
       <c r="R46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S46" s="3">
+      <c r="S46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T46" s="3">
         <v>200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2673,8 +2777,8 @@
       <c r="J47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -2697,53 +2801,56 @@
       <c r="R47" s="3">
         <v>0</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>4</v>
+      <c r="S47" s="3">
+        <v>0</v>
       </c>
       <c r="T47" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>136400</v>
+      </c>
+      <c r="E48" s="3">
         <v>152900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>159600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>190800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>217300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>231000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>234200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>241200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>235000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>88000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>81100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>77000</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>4</v>
       </c>
@@ -2753,53 +2860,56 @@
       <c r="R48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S48" s="3">
-        <v>0</v>
+      <c r="S48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>13300</v>
+      </c>
+      <c r="E49" s="3">
         <v>14500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>14800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>20200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>20800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>18800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>18600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>19100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>13500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>11900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>11200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>10800</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P49" s="3" t="s">
         <v>4</v>
       </c>
@@ -2809,14 +2919,17 @@
       <c r="R49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S49" s="3">
-        <v>0</v>
+      <c r="S49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2871,8 +2984,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2927,47 +3043,50 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E52" s="3">
         <v>8600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>8500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>9000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>9600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>11200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>11500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>11700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>11600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>10900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>9700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>9400</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>4</v>
       </c>
@@ -2983,8 +3102,11 @@
       <c r="T52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3039,47 +3161,50 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>214200</v>
+      </c>
+      <c r="E54" s="3">
         <v>239000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>250600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>282500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>312400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>357300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>351600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>390100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>372500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>240300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>172000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>178600</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>4</v>
       </c>
@@ -3089,14 +3214,17 @@
       <c r="R54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S54" s="3">
+      <c r="S54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T54" s="3">
         <v>200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3117,8 +3245,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3139,47 +3268,48 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>30700</v>
+      </c>
+      <c r="E57" s="3">
         <v>29000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>27500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>35500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>32300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>28400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>23800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>16800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>16200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>12700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>8100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>9600</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>4</v>
       </c>
@@ -3195,47 +3325,50 @@
       <c r="T57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>141500</v>
+      </c>
+      <c r="E58" s="3">
         <v>144600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>78600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>86900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>104200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>118000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>82200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>91900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>57500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>50300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>59300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>26700</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P58" s="3" t="s">
         <v>4</v>
       </c>
@@ -3245,53 +3378,56 @@
       <c r="R58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S58" s="3">
+      <c r="S58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T58" s="3">
         <v>100</v>
       </c>
-      <c r="T58" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>38200</v>
+      </c>
+      <c r="E59" s="3">
         <v>37100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>43900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>79200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>40100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>57800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>64200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>51200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>112200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>69100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>44300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>42600</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>4</v>
       </c>
@@ -3301,53 +3437,56 @@
       <c r="R59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S59" s="3">
-        <v>100</v>
+      <c r="S59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T59" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>210400</v>
+      </c>
+      <c r="E60" s="3">
         <v>210700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>150000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>201600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>196800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>204200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>170300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>183500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>185800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>132000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>111700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>78900</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>4</v>
       </c>
@@ -3357,53 +3496,56 @@
       <c r="R60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S60" s="3">
+      <c r="S60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T60" s="3">
         <v>200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>115800</v>
+      </c>
+      <c r="E61" s="3">
         <v>123600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>182600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>144200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>159900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>162100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>166800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>169200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>51200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>50700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>50800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>45900</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -3419,8 +3561,11 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3431,35 +3576,35 @@
         <v>1100</v>
       </c>
       <c r="F62" s="3">
-        <v>14500</v>
+        <v>1100</v>
       </c>
       <c r="G62" s="3">
         <v>14500</v>
       </c>
       <c r="H62" s="3">
+        <v>14500</v>
+      </c>
+      <c r="I62" s="3">
         <v>9800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>10800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>22000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>119900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>15600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>7700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>6700</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>4</v>
       </c>
@@ -3475,8 +3620,11 @@
       <c r="T62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3531,8 +3679,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3587,8 +3738,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3643,47 +3797,50 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>328300</v>
+      </c>
+      <c r="E66" s="3">
         <v>336300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>334400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>361000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>372000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>376800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>348400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>375200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>357100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>198400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>170400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>132000</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>4</v>
       </c>
@@ -3693,14 +3850,17 @@
       <c r="R66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S66" s="3">
+      <c r="S66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T66" s="3">
         <v>200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3721,8 +3881,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3777,8 +3938,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3833,8 +3997,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3889,8 +4056,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3945,47 +4115,50 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-365600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-361700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-336900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-332500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-318200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-266500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-246000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-226400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-194600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-159800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-133700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-88600</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>4</v>
       </c>
@@ -3995,14 +4168,17 @@
       <c r="R72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S72" s="3">
-        <v>0</v>
+      <c r="S72" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4057,8 +4233,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4113,8 +4292,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4169,47 +4351,50 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-115200</v>
+      </c>
+      <c r="E76" s="3">
         <v>-98600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-84800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-79400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-60200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-20000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>14600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>15300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>41900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>46600</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>4</v>
       </c>
@@ -4219,14 +4404,17 @@
       <c r="R76" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S76" s="3">
-        <v>0</v>
+      <c r="S76" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T76" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4281,125 +4469,134 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-18900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-12700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-6600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-19900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-44000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-22000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-31500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-25500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-31600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-26900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-24200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-20900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-19100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-15300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-10900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-8000</v>
       </c>
-      <c r="S81" s="3">
-        <v>0</v>
-      </c>
       <c r="T81" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4420,35 +4617,36 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E83" s="3">
         <v>5600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>4800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>5600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>5100</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J83" s="3">
+      <c r="J83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K83" s="3">
         <v>4600</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
       <c r="L83" s="3">
         <v>0</v>
       </c>
@@ -4476,8 +4674,11 @@
       <c r="T83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4532,8 +4733,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4588,8 +4792,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4644,8 +4851,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4700,8 +4910,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4756,64 +4969,70 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-3700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-11400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-4200</v>
       </c>
-      <c r="I89" s="3">
-        <v>0</v>
-      </c>
       <c r="J89" s="3">
+        <v>0</v>
+      </c>
+      <c r="K89" s="3">
         <v>-12400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-13500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-5000</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N89" s="3" t="s">
         <v>4</v>
       </c>
       <c r="O89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P89" s="3">
+      <c r="P89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q89" s="3">
         <v>-25900</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S89" s="3">
-        <v>0</v>
+      <c r="S89" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4834,8 +5053,9 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4848,20 +5068,20 @@
       <c r="F91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G91" s="3">
+      <c r="G91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H91" s="3">
         <v>-41200</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I91" s="3" t="s">
         <v>4</v>
       </c>
       <c r="J91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -4890,8 +5110,11 @@
       <c r="T91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4946,8 +5169,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5002,53 +5228,56 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E94" s="3">
         <v>1100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-9600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>8700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>1900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>7300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-13200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-59600</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>4</v>
       </c>
       <c r="O94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P94" s="3">
+      <c r="P94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-30400</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>4</v>
       </c>
@@ -5058,8 +5287,11 @@
       <c r="T94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5080,8 +5312,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5106,8 +5339,8 @@
       <c r="J96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -5136,8 +5369,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5192,8 +5428,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5248,8 +5487,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5304,53 +5546,56 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E100" s="3">
         <v>4000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-5200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>3600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-16900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>23500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-18700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>23900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>5200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>77800</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>4</v>
       </c>
       <c r="O100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P100" s="3">
+      <c r="P100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q100" s="3">
         <v>51000</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>4</v>
       </c>
@@ -5360,116 +5605,125 @@
       <c r="T100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E101" s="3">
         <v>100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>1700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>100</v>
       </c>
-      <c r="I101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J101" s="3">
+      <c r="J101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K101" s="3">
         <v>-400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>100</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N101" s="3" t="s">
         <v>4</v>
       </c>
       <c r="O101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P101" s="3">
+      <c r="P101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q101" s="3">
         <v>-200</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
+      <c r="S101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E102" s="3">
         <v>4000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-3900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-36400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>28300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-15000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>18300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-20200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>13400</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N102" s="3" t="s">
         <v>4</v>
       </c>
       <c r="O102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P102" s="3">
+      <c r="P102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q102" s="3">
         <v>-5600</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S102" s="3">
-        <v>0</v>
+      <c r="S102" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T102" s="3">
+        <v>0</v>
+      </c>
+      <c r="U102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/THCH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/THCH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="92">
   <si>
     <t>THCH</t>
   </si>
@@ -656,275 +656,288 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>41400</v>
+      </c>
+      <c r="E8" s="3">
         <v>45600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>51300</v>
       </c>
-      <c r="F8" s="3">
-        <v>50500</v>
-      </c>
-      <c r="G8" s="3">
-        <v>48000</v>
+      <c r="G8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H8" s="3">
-        <v>55200</v>
-      </c>
-      <c r="I8" s="3">
+        <v>46000</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J8" s="3">
         <v>59500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>56800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>49000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>42500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>42200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>24900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>31200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>30900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>25100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>19300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>14600</v>
       </c>
-      <c r="T8" s="3">
-        <v>0</v>
-      </c>
       <c r="U8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>27200</v>
+      </c>
+      <c r="E9" s="3">
         <v>28800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>30100</v>
       </c>
-      <c r="F9" s="3">
-        <v>32700</v>
-      </c>
-      <c r="G9" s="3">
-        <v>36000</v>
+      <c r="G9" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H9" s="3">
-        <v>40600</v>
-      </c>
-      <c r="I9" s="3">
+        <v>34000</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J9" s="3">
         <v>41600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>40500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>39000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>15700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>14700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>9300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>10900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>10800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>9000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>6700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>4900</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>14200</v>
+      </c>
+      <c r="E10" s="3">
         <v>16700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>21200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H10" s="3">
+        <v>12000</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J10" s="3">
         <v>17800</v>
       </c>
-      <c r="G10" s="3">
-        <v>12000</v>
-      </c>
-      <c r="H10" s="3">
-        <v>14600</v>
-      </c>
-      <c r="I10" s="3">
-        <v>17800</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>16300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>10000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>26800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>27600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>15600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>20300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>20100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>16100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>12600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>9700</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -946,8 +959,9 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1005,8 +1019,11 @@
       <c r="U12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1064,100 +1081,106 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E14" s="3">
         <v>4600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>6400</v>
       </c>
-      <c r="F14" s="3">
-        <v>5800</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="3">
         <v>4700</v>
       </c>
-      <c r="H14" s="3">
-        <v>21400</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14" s="3">
         <v>3900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>200</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>500</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>100</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>4</v>
+      <c r="T14" s="3">
+        <v>0</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E15" s="3">
         <v>4900</v>
-      </c>
-      <c r="E15" s="3">
-        <v>4200</v>
       </c>
       <c r="F15" s="3">
         <v>4200</v>
       </c>
       <c r="G15" s="3">
-        <v>4700</v>
+        <v>0</v>
       </c>
       <c r="H15" s="3">
+        <v>4600</v>
+      </c>
+      <c r="I15" s="3">
+        <v>6200</v>
+      </c>
+      <c r="J15" s="3">
         <v>5000</v>
-      </c>
-      <c r="I15" s="3">
-        <v>5000</v>
-      </c>
-      <c r="J15" s="3">
-        <v>4800</v>
       </c>
       <c r="K15" s="3">
         <v>4800</v>
       </c>
       <c r="L15" s="3">
+        <v>4800</v>
+      </c>
+      <c r="M15" s="3">
         <v>16700</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N15" s="3" t="s">
         <v>4</v>
       </c>
@@ -1170,8 +1193,8 @@
       <c r="Q15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R15" s="3">
-        <v>0</v>
+      <c r="R15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S15" s="3">
         <v>0</v>
@@ -1182,8 +1205,11 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1202,126 +1228,133 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>51200</v>
+      </c>
+      <c r="E17" s="3">
         <v>59400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>56900</v>
       </c>
-      <c r="F17" s="3">
-        <v>57100</v>
-      </c>
-      <c r="G17" s="3">
+      <c r="G17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H17" s="3">
+        <v>59900</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J17" s="3">
+        <v>76300</v>
+      </c>
+      <c r="K17" s="3">
+        <v>80700</v>
+      </c>
+      <c r="L17" s="3">
+        <v>67200</v>
+      </c>
+      <c r="M17" s="3">
+        <v>61000</v>
+      </c>
+      <c r="N17" s="3">
         <v>63000</v>
       </c>
-      <c r="H17" s="3">
-        <v>74900</v>
-      </c>
-      <c r="I17" s="3">
-        <v>76300</v>
-      </c>
-      <c r="J17" s="3">
-        <v>80700</v>
-      </c>
-      <c r="K17" s="3">
-        <v>67200</v>
-      </c>
-      <c r="L17" s="3">
-        <v>61000</v>
-      </c>
-      <c r="M17" s="3">
-        <v>63000</v>
-      </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>47800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>50000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>48800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>40700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>29700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>23000</v>
       </c>
-      <c r="T17" s="3">
-        <v>0</v>
-      </c>
       <c r="U17" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-13800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-5600</v>
       </c>
-      <c r="F18" s="3">
-        <v>-6600</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-15000</v>
+      <c r="G18" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H18" s="3">
-        <v>-19700</v>
-      </c>
-      <c r="I18" s="3">
+        <v>-13900</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J18" s="3">
         <v>-16800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-23900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-18200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-18500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-20800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-22900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-18700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-17900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-15600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-10400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-8500</v>
       </c>
-      <c r="T18" s="3">
-        <v>0</v>
-      </c>
       <c r="U18" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1343,97 +1376,101 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E20" s="3">
         <v>100</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J20" s="3">
         <v>-100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="K20" s="3">
+        <v>5300</v>
+      </c>
+      <c r="L20" s="3">
+        <v>4000</v>
+      </c>
+      <c r="M20" s="3">
+        <v>-12300</v>
+      </c>
+      <c r="N20" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="O20" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="P20" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>-800</v>
+      </c>
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>-500</v>
       </c>
-      <c r="H20" s="3">
-        <v>2300</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="J20" s="3">
-        <v>5300</v>
-      </c>
-      <c r="K20" s="3">
-        <v>4000</v>
-      </c>
-      <c r="L20" s="3">
-        <v>-12300</v>
-      </c>
-      <c r="M20" s="3">
-        <v>-5600</v>
-      </c>
-      <c r="N20" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="O20" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="P20" s="3">
-        <v>-800</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
-      <c r="R20" s="3">
-        <v>-500</v>
-      </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>400</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="E21" s="3">
         <v>-9000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-1400</v>
       </c>
-      <c r="F21" s="3">
-        <v>-2400</v>
-      </c>
       <c r="G21" s="3">
-        <v>-9800</v>
+        <v>0</v>
       </c>
       <c r="H21" s="3">
-        <v>-17000</v>
+        <v>-8700</v>
       </c>
       <c r="I21" s="3">
+        <v>6200</v>
+      </c>
+      <c r="J21" s="3">
         <v>-11700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-24500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-17400</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1461,8 +1498,11 @@
       <c r="U21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1470,25 +1510,25 @@
         <v>500</v>
       </c>
       <c r="E22" s="3">
+        <v>500</v>
+      </c>
+      <c r="F22" s="3">
         <v>600</v>
       </c>
-      <c r="F22" s="3">
-        <v>1200</v>
-      </c>
-      <c r="G22" s="3">
+      <c r="G22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H22" s="3">
         <v>800</v>
       </c>
-      <c r="H22" s="3">
-        <v>900</v>
-      </c>
-      <c r="I22" s="3">
+      <c r="I22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J22" s="3">
         <v>600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>700</v>
-      </c>
-      <c r="K22" s="3">
-        <v>600</v>
       </c>
       <c r="L22" s="3">
         <v>600</v>
@@ -1497,17 +1537,17 @@
         <v>600</v>
       </c>
       <c r="N22" s="3">
+        <v>600</v>
+      </c>
+      <c r="O22" s="3">
         <v>500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>200</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
       <c r="R22" s="3">
         <v>0</v>
       </c>
@@ -1520,72 +1560,78 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-18900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-12400</v>
       </c>
-      <c r="F23" s="3">
-        <v>-13500</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-19800</v>
+      <c r="G23" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H23" s="3">
-        <v>-43900</v>
-      </c>
-      <c r="I23" s="3">
+        <v>-18700</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J23" s="3">
         <v>-20200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-31400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-25400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-31400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-26900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-24400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-21000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-18900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-15600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-10900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-8100</v>
       </c>
-      <c r="T23" s="3">
-        <v>0</v>
-      </c>
       <c r="U23" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>100</v>
+      <c r="D24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E24" s="3">
         <v>100</v>
@@ -1596,8 +1642,8 @@
       <c r="G24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
+      <c r="H24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>4</v>
@@ -1608,8 +1654,8 @@
       <c r="K24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="L24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -1638,8 +1684,11 @@
       <c r="U24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1697,126 +1746,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-19000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-12500</v>
       </c>
-      <c r="F26" s="3">
-        <v>-13700</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-19800</v>
+      <c r="G26" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H26" s="3">
-        <v>-43900</v>
-      </c>
-      <c r="I26" s="3">
+        <v>-18700</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J26" s="3">
         <v>-20200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-31400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-25400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-31400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-26900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-24400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-21000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-18900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-15600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-10900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-8100</v>
       </c>
-      <c r="T26" s="3">
-        <v>0</v>
-      </c>
       <c r="U26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-18900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-12700</v>
       </c>
-      <c r="F27" s="3">
-        <v>-6600</v>
-      </c>
-      <c r="G27" s="3">
+      <c r="G27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H27" s="3">
         <v>-19900</v>
       </c>
-      <c r="H27" s="3">
-        <v>-44000</v>
-      </c>
-      <c r="I27" s="3">
+      <c r="I27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J27" s="3">
         <v>-22000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-31500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-25500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-31600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-26900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-24200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-20900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-19100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-15300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-10900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-8000</v>
       </c>
-      <c r="T27" s="3">
-        <v>0</v>
-      </c>
       <c r="U27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1874,8 +1932,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1886,28 +1947,28 @@
         <v>0</v>
       </c>
       <c r="F29" s="3">
-        <v>7300</v>
+        <v>0</v>
       </c>
       <c r="G29" s="3">
         <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>0</v>
+        <v>-1100</v>
       </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>-1700</v>
       </c>
-      <c r="J29" s="3">
-        <v>0</v>
-      </c>
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M29" s="3">
-        <v>0</v>
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N29" s="3">
         <v>0</v>
@@ -1933,8 +1994,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1992,8 +2056,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2051,126 +2118,135 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-100</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H32" s="3">
+        <v>500</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J32" s="3">
         <v>100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="K32" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="L32" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="M32" s="3">
+        <v>12300</v>
+      </c>
+      <c r="N32" s="3">
+        <v>5600</v>
+      </c>
+      <c r="O32" s="3">
+        <v>1100</v>
+      </c>
+      <c r="P32" s="3">
+        <v>1900</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>800</v>
+      </c>
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>500</v>
       </c>
-      <c r="H32" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="I32" s="3">
-        <v>100</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-5300</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-4000</v>
-      </c>
-      <c r="L32" s="3">
-        <v>12300</v>
-      </c>
-      <c r="M32" s="3">
-        <v>5600</v>
-      </c>
-      <c r="N32" s="3">
-        <v>1100</v>
-      </c>
-      <c r="O32" s="3">
-        <v>1900</v>
-      </c>
-      <c r="P32" s="3">
-        <v>800</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
-      <c r="R32" s="3">
-        <v>500</v>
-      </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-400</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-18900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-12700</v>
       </c>
-      <c r="F33" s="3">
-        <v>-6600</v>
-      </c>
-      <c r="G33" s="3">
+      <c r="G33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H33" s="3">
         <v>-19900</v>
       </c>
-      <c r="H33" s="3">
-        <v>-44000</v>
-      </c>
-      <c r="I33" s="3">
+      <c r="I33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J33" s="3">
         <v>-22000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-31500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-25500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-31600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-26900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-24200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-20900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-19100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-15300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-10900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-8000</v>
       </c>
-      <c r="T33" s="3">
-        <v>0</v>
-      </c>
       <c r="U33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2228,131 +2304,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-18900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-12700</v>
       </c>
-      <c r="F35" s="3">
-        <v>-6600</v>
-      </c>
-      <c r="G35" s="3">
+      <c r="G35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H35" s="3">
         <v>-19900</v>
       </c>
-      <c r="H35" s="3">
-        <v>-44000</v>
-      </c>
-      <c r="I35" s="3">
+      <c r="I35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J35" s="3">
         <v>-22000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-31500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-25500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-31600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-26900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-24200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-20900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-19100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-15300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-10900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-8000</v>
       </c>
-      <c r="T35" s="3">
-        <v>0</v>
-      </c>
       <c r="U35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2374,8 +2459,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2397,50 +2483,51 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>25400</v>
+      </c>
+      <c r="E41" s="3">
         <v>20900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>28000</v>
       </c>
-      <c r="F41" s="3">
-        <v>23200</v>
-      </c>
-      <c r="G41" s="3">
+      <c r="G41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H41" s="3">
         <v>27300</v>
       </c>
-      <c r="H41" s="3">
-        <v>28700</v>
-      </c>
       <c r="I41" s="3">
+        <v>28500</v>
+      </c>
+      <c r="J41" s="3">
         <v>63300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>35200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>53100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>33700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>52800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>39600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>54300</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>4</v>
       </c>
@@ -2456,8 +2543,11 @@
       <c r="U41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2465,35 +2555,35 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F42" s="3">
         <v>1000</v>
       </c>
-      <c r="F42" s="3">
-        <v>400</v>
-      </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>2900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>3300</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>18800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>37000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>52500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>52200</v>
       </c>
-      <c r="N42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O42" s="3" t="s">
         <v>4</v>
       </c>
@@ -2509,56 +2599,59 @@
       <c r="S42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T42" s="3">
-        <v>0</v>
+      <c r="T42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>5000</v>
+        <v>4700</v>
       </c>
       <c r="E43" s="3">
+        <v>23400</v>
+      </c>
+      <c r="F43" s="3">
         <v>5900</v>
       </c>
-      <c r="F43" s="3">
-        <v>15600</v>
-      </c>
-      <c r="G43" s="3">
+      <c r="G43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H43" s="3">
         <v>3800</v>
       </c>
-      <c r="H43" s="3">
-        <v>22500</v>
-      </c>
       <c r="I43" s="3">
+        <v>22300</v>
+      </c>
+      <c r="J43" s="3">
         <v>4600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>14400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>12100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>9300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>10800</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>4</v>
       </c>
@@ -2568,56 +2661,59 @@
       <c r="S43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T43" s="3">
-        <v>0</v>
+      <c r="T43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E44" s="3">
         <v>5100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>5000</v>
       </c>
-      <c r="F44" s="3">
-        <v>5900</v>
-      </c>
-      <c r="G44" s="3">
+      <c r="G44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H44" s="3">
         <v>5600</v>
       </c>
-      <c r="H44" s="3">
-        <v>7200</v>
-      </c>
       <c r="I44" s="3">
+        <v>7000</v>
+      </c>
+      <c r="J44" s="3">
         <v>10200</v>
-      </c>
-      <c r="J44" s="3">
-        <v>10400</v>
       </c>
       <c r="K44" s="3">
         <v>10400</v>
       </c>
       <c r="L44" s="3">
+        <v>10400</v>
+      </c>
+      <c r="M44" s="3">
         <v>10100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>7200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>7700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>5900</v>
       </c>
-      <c r="P44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q44" s="3" t="s">
         <v>4</v>
       </c>
@@ -2627,22 +2723,25 @@
       <c r="S44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T44" s="3">
-        <v>0</v>
+      <c r="T44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>4</v>
+      <c r="E45" s="3">
+        <v>1400</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>4</v>
@@ -2650,33 +2749,33 @@
       <c r="G45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H45" s="3">
-        <v>2100</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>4</v>
+      <c r="H45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I45" s="3">
+        <v>2700</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L45" s="3">
         <v>2600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>16300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>13300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>10400</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>4</v>
       </c>
@@ -2686,56 +2785,59 @@
       <c r="S45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T45" s="3">
+      <c r="T45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U45" s="3">
         <v>200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>59800</v>
+      </c>
+      <c r="E46" s="3">
         <v>57100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>63000</v>
       </c>
-      <c r="F46" s="3">
-        <v>67700</v>
-      </c>
-      <c r="G46" s="3">
+      <c r="G46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H46" s="3">
         <v>62400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>64700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>96400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>87200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>118200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>112300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>129600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>70000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>81500</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>4</v>
       </c>
@@ -2745,14 +2847,17 @@
       <c r="S46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T46" s="3">
+      <c r="T46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U46" s="3">
         <v>200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2780,8 +2885,8 @@
       <c r="K47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -2804,56 +2909,59 @@
       <c r="S47" s="3">
         <v>0</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>4</v>
+      <c r="T47" s="3">
+        <v>0</v>
       </c>
       <c r="U47" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>125500</v>
+      </c>
+      <c r="E48" s="3">
         <v>136400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>152900</v>
       </c>
-      <c r="F48" s="3">
-        <v>159600</v>
-      </c>
-      <c r="G48" s="3">
+      <c r="G48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H48" s="3">
         <v>190800</v>
       </c>
-      <c r="H48" s="3">
-        <v>217300</v>
-      </c>
       <c r="I48" s="3">
+        <v>204700</v>
+      </c>
+      <c r="J48" s="3">
         <v>231000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>234200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>241200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>235000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>88000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>81100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>77000</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>4</v>
       </c>
@@ -2863,56 +2971,59 @@
       <c r="S48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T48" s="3">
-        <v>0</v>
+      <c r="T48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E49" s="3">
         <v>13300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>14500</v>
       </c>
-      <c r="F49" s="3">
-        <v>14800</v>
-      </c>
-      <c r="G49" s="3">
+      <c r="G49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H49" s="3">
         <v>20200</v>
       </c>
-      <c r="H49" s="3">
-        <v>20800</v>
-      </c>
       <c r="I49" s="3">
+        <v>15600</v>
+      </c>
+      <c r="J49" s="3">
         <v>18800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>18600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>19100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>13500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>11900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>11200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>10800</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q49" s="3" t="s">
         <v>4</v>
       </c>
@@ -2922,14 +3033,17 @@
       <c r="S49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T49" s="3">
-        <v>0</v>
+      <c r="T49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2987,8 +3101,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3046,8 +3163,11 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3055,41 +3175,41 @@
         <v>7400</v>
       </c>
       <c r="E52" s="3">
+        <v>7400</v>
+      </c>
+      <c r="F52" s="3">
         <v>8600</v>
       </c>
-      <c r="F52" s="3">
-        <v>8500</v>
-      </c>
-      <c r="G52" s="3">
+      <c r="G52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H52" s="3">
         <v>9000</v>
       </c>
-      <c r="H52" s="3">
-        <v>9600</v>
-      </c>
       <c r="I52" s="3">
+        <v>27400</v>
+      </c>
+      <c r="J52" s="3">
         <v>11200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>11500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>11700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>11600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>10900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>9700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>9400</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>4</v>
       </c>
@@ -3105,8 +3225,11 @@
       <c r="U52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3164,50 +3287,53 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>205300</v>
+      </c>
+      <c r="E54" s="3">
         <v>214200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>239000</v>
       </c>
-      <c r="F54" s="3">
-        <v>250600</v>
-      </c>
-      <c r="G54" s="3">
+      <c r="G54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H54" s="3">
         <v>282500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>312400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>357300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>351600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>390100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>372500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>240300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>172000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>178600</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>4</v>
       </c>
@@ -3217,14 +3343,17 @@
       <c r="S54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T54" s="3">
+      <c r="T54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U54" s="3">
         <v>200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3246,8 +3375,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3269,50 +3399,51 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>30700</v>
+        <v>30800</v>
       </c>
       <c r="E57" s="3">
+        <v>33500</v>
+      </c>
+      <c r="F57" s="3">
         <v>29000</v>
       </c>
-      <c r="F57" s="3">
-        <v>27500</v>
-      </c>
-      <c r="G57" s="3">
+      <c r="G57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H57" s="3">
         <v>35500</v>
       </c>
-      <c r="H57" s="3">
-        <v>32300</v>
-      </c>
       <c r="I57" s="3">
+        <v>31600</v>
+      </c>
+      <c r="J57" s="3">
         <v>28400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>23800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>16800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>16200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>12700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>8100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>9600</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>4</v>
       </c>
@@ -3328,50 +3459,53 @@
       <c r="U57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>151000</v>
+      </c>
+      <c r="E58" s="3">
         <v>141500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>144600</v>
       </c>
-      <c r="F58" s="3">
-        <v>78600</v>
-      </c>
-      <c r="G58" s="3">
+      <c r="G58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H58" s="3">
         <v>86900</v>
       </c>
-      <c r="H58" s="3">
-        <v>104200</v>
-      </c>
       <c r="I58" s="3">
+        <v>102700</v>
+      </c>
+      <c r="J58" s="3">
         <v>118000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>82200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>91900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>57500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>50300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>59300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>26700</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>4</v>
       </c>
@@ -3381,56 +3515,59 @@
       <c r="S58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T58" s="3">
+      <c r="T58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U58" s="3">
         <v>100</v>
       </c>
-      <c r="U58" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>38200</v>
+        <v>39200</v>
       </c>
       <c r="E59" s="3">
+        <v>23300</v>
+      </c>
+      <c r="F59" s="3">
         <v>37100</v>
       </c>
-      <c r="F59" s="3">
-        <v>43900</v>
-      </c>
-      <c r="G59" s="3">
+      <c r="G59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H59" s="3">
         <v>79200</v>
       </c>
-      <c r="H59" s="3">
-        <v>40100</v>
-      </c>
       <c r="I59" s="3">
+        <v>44300</v>
+      </c>
+      <c r="J59" s="3">
         <v>57800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>64200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>51200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>112200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>69100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>44300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>42600</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>4</v>
       </c>
@@ -3440,56 +3577,59 @@
       <c r="S59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T59" s="3">
-        <v>100</v>
+      <c r="T59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U59" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>221000</v>
+      </c>
+      <c r="E60" s="3">
         <v>210400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>210700</v>
       </c>
-      <c r="F60" s="3">
-        <v>150000</v>
-      </c>
-      <c r="G60" s="3">
+      <c r="G60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H60" s="3">
         <v>201600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>196800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>204200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>170300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>183500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>185800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>132000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>111700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>78900</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>4</v>
       </c>
@@ -3499,56 +3639,59 @@
       <c r="S60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T60" s="3">
+      <c r="T60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U60" s="3">
         <v>200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>104800</v>
+      </c>
+      <c r="E61" s="3">
         <v>115800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>123600</v>
       </c>
-      <c r="F61" s="3">
-        <v>182600</v>
-      </c>
       <c r="G61" s="3">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3">
         <v>144200</v>
       </c>
-      <c r="H61" s="3">
-        <v>159900</v>
-      </c>
       <c r="I61" s="3">
+        <v>152300</v>
+      </c>
+      <c r="J61" s="3">
         <v>162100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>166800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>169200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>51200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>50700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>50800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>45900</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -3564,8 +3707,11 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3578,36 +3724,36 @@
       <c r="F62" s="3">
         <v>1100</v>
       </c>
-      <c r="G62" s="3">
-        <v>14500</v>
+      <c r="G62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H62" s="3">
         <v>14500</v>
       </c>
       <c r="I62" s="3">
+        <v>22200</v>
+      </c>
+      <c r="J62" s="3">
         <v>9800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>10800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>22000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>119900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>15600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>7700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>6700</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>4</v>
       </c>
@@ -3623,8 +3769,11 @@
       <c r="U62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3682,8 +3831,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3741,8 +3893,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3800,50 +3955,53 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>327900</v>
+      </c>
+      <c r="E66" s="3">
         <v>328300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>336300</v>
       </c>
-      <c r="F66" s="3">
-        <v>334400</v>
-      </c>
-      <c r="G66" s="3">
+      <c r="G66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H66" s="3">
         <v>361000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>372000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>376800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>348400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>375200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>357100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>198400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>170400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>132000</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>4</v>
       </c>
@@ -3853,14 +4011,17 @@
       <c r="S66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T66" s="3">
+      <c r="T66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U66" s="3">
         <v>200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3882,8 +4043,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3941,8 +4103,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4000,8 +4165,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4059,8 +4227,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4118,50 +4289,53 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-375700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-365600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-361700</v>
       </c>
-      <c r="F72" s="3">
-        <v>-336900</v>
-      </c>
-      <c r="G72" s="3">
+      <c r="G72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H72" s="3">
         <v>-332500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-318200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-266500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-246000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-226400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-194600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-159800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-133700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-88600</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>4</v>
       </c>
@@ -4171,14 +4345,17 @@
       <c r="S72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T72" s="3">
-        <v>0</v>
+      <c r="T72" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4236,8 +4413,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4295,8 +4475,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4354,50 +4537,53 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-123500</v>
+      </c>
+      <c r="E76" s="3">
         <v>-115200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-98600</v>
       </c>
-      <c r="F76" s="3">
-        <v>-84800</v>
-      </c>
-      <c r="G76" s="3">
+      <c r="G76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H76" s="3">
         <v>-79400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-60200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-20000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>14600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>15300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>41900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>46600</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>4</v>
       </c>
@@ -4407,14 +4593,17 @@
       <c r="S76" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T76" s="3">
-        <v>0</v>
+      <c r="T76" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U76" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4472,131 +4661,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-18900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-12700</v>
       </c>
-      <c r="F81" s="3">
-        <v>-6600</v>
-      </c>
-      <c r="G81" s="3">
+      <c r="G81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H81" s="3">
         <v>-19900</v>
       </c>
-      <c r="H81" s="3">
-        <v>-44000</v>
-      </c>
-      <c r="I81" s="3">
+      <c r="I81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J81" s="3">
         <v>-22000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-31500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-25500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-31600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-26900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-24200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-20900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-19100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-15300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-10900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-8000</v>
       </c>
-      <c r="T81" s="3">
-        <v>0</v>
-      </c>
       <c r="U81" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4618,38 +4816,39 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>10300</v>
-      </c>
-      <c r="E83" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F83" s="3">
         <v>5600</v>
       </c>
-      <c r="F83" s="3">
-        <v>4800</v>
-      </c>
-      <c r="G83" s="3">
+      <c r="G83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H83" s="3">
         <v>5600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>4200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>5100</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K83" s="3">
+      <c r="K83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L83" s="3">
         <v>4600</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
       <c r="M83" s="3">
         <v>0</v>
       </c>
@@ -4677,8 +4876,11 @@
       <c r="U83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4736,8 +4938,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4795,8 +5000,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4854,8 +5062,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4913,8 +5124,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4972,67 +5186,73 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>0</v>
+      </c>
+      <c r="E89" s="3">
         <v>-4300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1900</v>
       </c>
-      <c r="F89" s="3">
-        <v>4400</v>
-      </c>
-      <c r="G89" s="3">
+      <c r="G89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H89" s="3">
         <v>-3700</v>
       </c>
-      <c r="H89" s="3">
-        <v>-11400</v>
-      </c>
-      <c r="I89" s="3">
+      <c r="I89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J89" s="3">
         <v>-4200</v>
       </c>
-      <c r="J89" s="3">
-        <v>0</v>
-      </c>
       <c r="K89" s="3">
+        <v>0</v>
+      </c>
+      <c r="L89" s="3">
         <v>-12400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-13500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-5000</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O89" s="3" t="s">
         <v>4</v>
       </c>
       <c r="P89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="Q89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R89" s="3">
         <v>-25900</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T89" s="3">
-        <v>0</v>
+      <c r="T89" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5054,8 +5274,9 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5071,8 +5292,8 @@
       <c r="G91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H91" s="3">
-        <v>-41200</v>
+      <c r="H91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I91" s="3" t="s">
         <v>4</v>
@@ -5083,8 +5304,8 @@
       <c r="K91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="L91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -5113,8 +5334,11 @@
       <c r="U91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5172,8 +5396,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5231,56 +5458,59 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E94" s="3">
         <v>1800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>1100</v>
       </c>
-      <c r="F94" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="G94" s="3">
+      <c r="G94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H94" s="3">
         <v>-1000</v>
       </c>
-      <c r="H94" s="3">
-        <v>-9600</v>
-      </c>
-      <c r="I94" s="3">
+      <c r="I94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J94" s="3">
         <v>8700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>1900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>7300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-13200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-59600</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O94" s="3" t="s">
         <v>4</v>
       </c>
       <c r="P94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="Q94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R94" s="3">
         <v>-30400</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>4</v>
       </c>
@@ -5290,8 +5520,11 @@
       <c r="U94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5313,8 +5546,9 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5342,8 +5576,8 @@
       <c r="K96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -5372,8 +5606,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5431,8 +5668,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5490,8 +5730,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5549,56 +5792,59 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E100" s="3">
         <v>1300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>4000</v>
       </c>
-      <c r="F100" s="3">
-        <v>-5200</v>
-      </c>
-      <c r="G100" s="3">
+      <c r="G100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H100" s="3">
         <v>3600</v>
       </c>
-      <c r="H100" s="3">
-        <v>-16900</v>
-      </c>
-      <c r="I100" s="3">
+      <c r="I100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J100" s="3">
         <v>23500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-18700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>23900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>5200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>77800</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O100" s="3" t="s">
         <v>4</v>
       </c>
       <c r="P100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="Q100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R100" s="3">
         <v>51000</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>4</v>
       </c>
@@ -5608,122 +5854,131 @@
       <c r="U100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>200</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F101" s="3">
+        <v>100</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H101" s="3">
+        <v>-500</v>
+      </c>
+      <c r="I101" s="3">
         <v>1400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="J101" s="3">
         <v>100</v>
       </c>
-      <c r="F101" s="3">
-        <v>1700</v>
-      </c>
-      <c r="G101" s="3">
-        <v>-500</v>
-      </c>
-      <c r="H101" s="3">
-        <v>1400</v>
-      </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L101" s="3">
+        <v>-400</v>
+      </c>
+      <c r="M101" s="3">
+        <v>1300</v>
+      </c>
+      <c r="N101" s="3">
         <v>100</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K101" s="3">
-        <v>-400</v>
-      </c>
-      <c r="L101" s="3">
-        <v>1300</v>
-      </c>
-      <c r="M101" s="3">
-        <v>100</v>
-      </c>
-      <c r="N101" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O101" s="3" t="s">
         <v>4</v>
       </c>
       <c r="P101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="Q101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R101" s="3">
         <v>-200</v>
       </c>
-      <c r="R101" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
+      <c r="T101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>4000</v>
       </c>
-      <c r="F102" s="3">
-        <v>-3900</v>
-      </c>
       <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
         <v>-900</v>
       </c>
-      <c r="H102" s="3">
-        <v>-36400</v>
-      </c>
       <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>28300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-15000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>18300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-20200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>13400</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O102" s="3" t="s">
         <v>4</v>
       </c>
       <c r="P102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="Q102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R102" s="3">
         <v>-5600</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T102" s="3">
-        <v>0</v>
+      <c r="T102" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U102" s="3">
+        <v>0</v>
+      </c>
+      <c r="V102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/THCH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/THCH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="92">
   <si>
     <t>THCH</t>
   </si>
@@ -656,288 +656,301 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>50300</v>
+      </c>
+      <c r="E8" s="3">
         <v>41400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>45600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>51300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>46000</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I8" s="3">
+      <c r="I8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J8" s="3">
         <v>59500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>49000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>56800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>49000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>42500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>42200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>24900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>31200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>30900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>25100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>19300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>14600</v>
       </c>
-      <c r="U8" s="3">
-        <v>0</v>
-      </c>
       <c r="V8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>29000</v>
+      </c>
+      <c r="E9" s="3">
         <v>27200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>28800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>30100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>34000</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I9" s="3">
+      <c r="I9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J9" s="3">
         <v>41600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>39000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>40500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>39000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>15700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>14700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>9300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>10900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>10800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>9000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>6700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>4900</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>21300</v>
+      </c>
+      <c r="E10" s="3">
         <v>14200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>16700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>21200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>12000</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I10" s="3">
+      <c r="I10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J10" s="3">
         <v>17800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>10000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>16300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>10000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>26800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>27600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>15600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>20300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>20100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>16100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>12600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>9700</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -960,8 +973,9 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1022,8 +1036,11 @@
       <c r="V12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1084,93 +1101,99 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E14" s="3">
         <v>-2100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>4600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>6400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>4700</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14" s="3">
         <v>3900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>200</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>100</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>4</v>
+      <c r="U14" s="3">
+        <v>0</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E15" s="3">
         <v>3900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>4900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>4200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>4600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>6200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>5000</v>
-      </c>
-      <c r="J15" s="3">
-        <v>4800</v>
       </c>
       <c r="K15" s="3">
         <v>4800</v>
@@ -1179,11 +1202,11 @@
         <v>4800</v>
       </c>
       <c r="M15" s="3">
+        <v>4800</v>
+      </c>
+      <c r="N15" s="3">
         <v>16700</v>
       </c>
-      <c r="N15" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O15" s="3" t="s">
         <v>4</v>
       </c>
@@ -1196,8 +1219,8 @@
       <c r="R15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S15" s="3">
-        <v>0</v>
+      <c r="S15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T15" s="3">
         <v>0</v>
@@ -1208,8 +1231,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1229,132 +1255,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>58100</v>
+      </c>
+      <c r="E17" s="3">
         <v>51200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>59400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>56900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>59900</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I17" s="3">
+      <c r="I17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J17" s="3">
         <v>76300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>67200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>80700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>67200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>61000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>63000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>47800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>50000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>48800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>40700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>29700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>23000</v>
       </c>
-      <c r="U17" s="3">
-        <v>0</v>
-      </c>
       <c r="V17" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-9800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-13800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-5600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-13900</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I18" s="3">
+      <c r="I18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J18" s="3">
         <v>-16800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-18200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-23900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-18200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-18500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-20800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-22900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-18700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-17900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-15600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-10400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-8500</v>
       </c>
-      <c r="U18" s="3">
-        <v>0</v>
-      </c>
       <c r="V18" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1377,103 +1410,107 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>100</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>-500</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="I20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J20" s="3">
         <v>-100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>4000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>5300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>4000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-12300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-5600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-800</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>-500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>400</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E21" s="3">
         <v>-5800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-9000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-1400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-8700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>6200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-11700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-17400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-24500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-17400</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1501,37 +1538,40 @@
       <c r="V21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="E22" s="3">
         <v>500</v>
       </c>
       <c r="F22" s="3">
+        <v>500</v>
+      </c>
+      <c r="G22" s="3">
         <v>600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>800</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I22" s="3">
-        <v>600</v>
+      <c r="I22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J22" s="3">
         <v>600</v>
       </c>
       <c r="K22" s="3">
+        <v>600</v>
+      </c>
+      <c r="L22" s="3">
         <v>700</v>
-      </c>
-      <c r="L22" s="3">
-        <v>600</v>
       </c>
       <c r="M22" s="3">
         <v>600</v>
@@ -1540,17 +1580,17 @@
         <v>600</v>
       </c>
       <c r="O22" s="3">
+        <v>600</v>
+      </c>
+      <c r="P22" s="3">
         <v>500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>200</v>
       </c>
-      <c r="R22" s="3">
-        <v>0</v>
-      </c>
       <c r="S22" s="3">
         <v>0</v>
       </c>
@@ -1563,84 +1603,90 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-8100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-18900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-12400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-18700</v>
       </c>
-      <c r="H23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I23" s="3">
+      <c r="I23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J23" s="3">
         <v>-20200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-25400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-31400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-25400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-31400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-26900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-24400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-21000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-18900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-15600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-10900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-8100</v>
       </c>
-      <c r="U23" s="3">
-        <v>0</v>
-      </c>
       <c r="V23" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E24" s="3">
-        <v>100</v>
+      <c r="E24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F24" s="3">
         <v>100</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>4</v>
+      <c r="G24" s="3">
+        <v>100</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>4</v>
@@ -1657,8 +1703,8 @@
       <c r="L24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -1687,8 +1733,11 @@
       <c r="V24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1749,132 +1798,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-8100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-19000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-12500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-18700</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I26" s="3">
+      <c r="I26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J26" s="3">
         <v>-20200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-25400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-31400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-25400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-31400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-26900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-24400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-21000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-18900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-15600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-10900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-8100</v>
       </c>
-      <c r="U26" s="3">
-        <v>0</v>
-      </c>
       <c r="V26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-8000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-18900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-12700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-19900</v>
       </c>
-      <c r="H27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I27" s="3">
+      <c r="I27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J27" s="3">
         <v>-22000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-25500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-31500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-25500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-31600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-26900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-24200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-20900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-19100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-15300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-10900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-8000</v>
       </c>
-      <c r="U27" s="3">
-        <v>0</v>
-      </c>
       <c r="V27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1935,8 +1993,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1950,28 +2011,28 @@
         <v>0</v>
       </c>
       <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
         <v>-1100</v>
       </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>-1700</v>
       </c>
-      <c r="J29" s="3">
-        <v>0</v>
-      </c>
       <c r="K29" s="3">
         <v>0</v>
       </c>
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N29" s="3">
-        <v>0</v>
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O29" s="3">
         <v>0</v>
@@ -1997,8 +2058,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2059,8 +2123,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2121,132 +2188,141 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E32" s="3">
         <v>100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>500</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="I32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J32" s="3">
         <v>100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-4000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-5300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-4000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>12300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>5600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>800</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-400</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-8000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-18900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-12700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-19900</v>
       </c>
-      <c r="H33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I33" s="3">
+      <c r="I33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J33" s="3">
         <v>-22000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-25500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-31500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-25500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-31600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-26900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-24200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-20900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-19100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-15300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-10900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-8000</v>
       </c>
-      <c r="U33" s="3">
-        <v>0</v>
-      </c>
       <c r="V33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2307,137 +2383,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-8000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-18900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-12700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-19900</v>
       </c>
-      <c r="H35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I35" s="3">
+      <c r="I35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J35" s="3">
         <v>-22000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-25500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-31500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-25500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-31600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-26900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-24200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-20900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-19100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-15300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-10900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-8000</v>
       </c>
-      <c r="U35" s="3">
-        <v>0</v>
-      </c>
       <c r="V35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2460,8 +2545,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2484,53 +2570,54 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>18500</v>
+      </c>
+      <c r="E41" s="3">
         <v>25400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>20900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>28000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>27300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>28500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>63300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>53100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>35200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>53100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>33700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>52800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>39600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>54300</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>4</v>
       </c>
@@ -2546,8 +2633,11 @@
       <c r="V41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2555,38 +2645,38 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>1200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>3300</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>37000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>18800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>37000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>52500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>52200</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P42" s="3" t="s">
         <v>4</v>
       </c>
@@ -2602,59 +2692,62 @@
       <c r="T42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U42" s="3">
-        <v>0</v>
+      <c r="U42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E43" s="3">
         <v>4700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>23400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>5900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>22300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>14400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>14400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>12100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>9300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>10800</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>4</v>
       </c>
@@ -2664,37 +2757,40 @@
       <c r="T43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U43" s="3">
-        <v>0</v>
+      <c r="U43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E44" s="3">
         <v>4700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>5100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>5000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>5600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>7000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>10200</v>
-      </c>
-      <c r="J44" s="3">
-        <v>10400</v>
       </c>
       <c r="K44" s="3">
         <v>10400</v>
@@ -2703,20 +2799,20 @@
         <v>10400</v>
       </c>
       <c r="M44" s="3">
+        <v>10400</v>
+      </c>
+      <c r="N44" s="3">
         <v>10100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>7200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>7700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>5900</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R44" s="3" t="s">
         <v>4</v>
       </c>
@@ -2726,59 +2822,62 @@
       <c r="T44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U44" s="3">
-        <v>0</v>
+      <c r="U44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F45" s="3">
         <v>1400</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I45" s="3">
         <v>2700</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K45" s="3">
         <v>2600</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M45" s="3">
         <v>2600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>16300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>13300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>10400</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>4</v>
       </c>
@@ -2788,59 +2887,62 @@
       <c r="T45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U45" s="3">
+      <c r="U45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V45" s="3">
         <v>200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>55700</v>
+      </c>
+      <c r="E46" s="3">
         <v>59800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>57100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>63000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>62400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>64700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>96400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>118200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>87200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>118200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>112300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>129600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>70000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>81500</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>4</v>
       </c>
@@ -2850,14 +2952,17 @@
       <c r="T46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U46" s="3">
+      <c r="U46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V46" s="3">
         <v>200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2888,8 +2993,8 @@
       <c r="L47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -2912,59 +3017,62 @@
       <c r="T47" s="3">
         <v>0</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>4</v>
+      <c r="U47" s="3">
+        <v>0</v>
       </c>
       <c r="V47" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>106800</v>
+      </c>
+      <c r="E48" s="3">
         <v>125500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>136400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>152900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>190800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>204700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>231000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>241200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>234200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>241200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>235000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>88000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>81100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>77000</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>4</v>
       </c>
@@ -2974,59 +3082,62 @@
       <c r="T48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U48" s="3">
-        <v>0</v>
+      <c r="U48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>12100</v>
+      </c>
+      <c r="E49" s="3">
         <v>12700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>13300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>14500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>20200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>15600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>18800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>19100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>18600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>19100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>13500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>11900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>11200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>10800</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R49" s="3" t="s">
         <v>4</v>
       </c>
@@ -3036,14 +3147,17 @@
       <c r="T49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U49" s="3">
-        <v>0</v>
+      <c r="U49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3104,8 +3218,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3166,53 +3283,56 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>7400</v>
+        <v>6700</v>
       </c>
       <c r="E52" s="3">
         <v>7400</v>
       </c>
       <c r="F52" s="3">
+        <v>7400</v>
+      </c>
+      <c r="G52" s="3">
         <v>8600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>9000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>27400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>11200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>11700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>11500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>11700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>11600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>10900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>9700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>9400</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>4</v>
       </c>
@@ -3228,8 +3348,11 @@
       <c r="V52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3290,53 +3413,56 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>181300</v>
+      </c>
+      <c r="E54" s="3">
         <v>205300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>214200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>239000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>282500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>312400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>357300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>390100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>351600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>390100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>372500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>240300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>172000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>178600</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>4</v>
       </c>
@@ -3346,14 +3472,17 @@
       <c r="T54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U54" s="3">
+      <c r="U54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V54" s="3">
         <v>200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3376,8 +3505,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3400,53 +3530,54 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>28100</v>
+      </c>
+      <c r="E57" s="3">
         <v>30800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>33500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>29000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>35500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>31600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>28400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>16800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>23800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>16800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>16200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>12700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>8100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>9600</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>4</v>
       </c>
@@ -3462,53 +3593,56 @@
       <c r="V57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>155800</v>
+      </c>
+      <c r="E58" s="3">
         <v>151000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>141500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>144600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>86900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>102700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>118000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>91900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>82200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>91900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>57500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>50300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>59300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>26700</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>4</v>
       </c>
@@ -3518,59 +3652,62 @@
       <c r="T58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U58" s="3">
+      <c r="U58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V58" s="3">
         <v>100</v>
       </c>
-      <c r="V58" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>43100</v>
+      </c>
+      <c r="E59" s="3">
         <v>39200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>23300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>37100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>79200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>44300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>57800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>51200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>64200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>51200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>112200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>69100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>44300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>42600</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>4</v>
       </c>
@@ -3580,59 +3717,62 @@
       <c r="T59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U59" s="3">
-        <v>100</v>
+      <c r="U59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V59" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>227000</v>
+      </c>
+      <c r="E60" s="3">
         <v>221000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>210400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>210700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>201600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>196800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>204200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>183500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>170300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>183500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>185800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>132000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>111700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>78900</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>4</v>
       </c>
@@ -3642,59 +3782,62 @@
       <c r="T60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U60" s="3">
+      <c r="U60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V60" s="3">
         <v>200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>96800</v>
+      </c>
+      <c r="E61" s="3">
         <v>104800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>115800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>123600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>144200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>152300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>162100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>169200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>166800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>169200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>51200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>50700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>50800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>45900</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -3710,13 +3853,16 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="E62" s="3">
         <v>1100</v>
@@ -3725,38 +3871,38 @@
         <v>1100</v>
       </c>
       <c r="G62" s="3">
+        <v>1100</v>
+      </c>
+      <c r="H62" s="3">
         <v>14500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>22200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>9800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>22000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>10800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>22000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>119900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>15600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>7700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>6700</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>4</v>
       </c>
@@ -3772,8 +3918,11 @@
       <c r="V62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3834,8 +3983,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3896,8 +4048,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3958,53 +4113,56 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>326200</v>
+      </c>
+      <c r="E66" s="3">
         <v>327900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>328300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>336300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>361000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>372000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>376800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>375200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>348400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>375200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>357100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>198400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>170400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>132000</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>4</v>
       </c>
@@ -4014,14 +4172,17 @@
       <c r="T66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U66" s="3">
+      <c r="U66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V66" s="3">
         <v>200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4044,8 +4205,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4106,8 +4268,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4168,8 +4333,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4230,8 +4398,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4292,53 +4463,56 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-403800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-375700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-365600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-361700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-332500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-318200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-266500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-226400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-246000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-226400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-194600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-159800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-133700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-88600</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>4</v>
       </c>
@@ -4348,14 +4522,17 @@
       <c r="T72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U72" s="3">
-        <v>0</v>
+      <c r="U72" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4416,8 +4593,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4478,8 +4658,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4540,53 +4723,56 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-145700</v>
+      </c>
+      <c r="E76" s="3">
         <v>-123500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-115200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-98600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-79400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-60200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-20000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>14600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>14600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>15300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>41900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>46600</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>4</v>
       </c>
@@ -4596,14 +4782,17 @@
       <c r="T76" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U76" s="3">
-        <v>0</v>
+      <c r="U76" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V76" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4664,137 +4853,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-8000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-18900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-12700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-19900</v>
       </c>
-      <c r="H81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I81" s="3">
+      <c r="I81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J81" s="3">
         <v>-22000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-25500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-31500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-25500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-31600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-26900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-24200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-20900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-19100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-15300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-10900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-8000</v>
       </c>
-      <c r="U81" s="3">
-        <v>0</v>
-      </c>
       <c r="V81" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4817,41 +5015,42 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E83" s="3">
-        <v>5600</v>
+      <c r="D83" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F83" s="3">
         <v>5600</v>
       </c>
       <c r="G83" s="3">
+        <v>5600</v>
+      </c>
+      <c r="H83" s="3">
         <v>4200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>5100</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J83" s="3">
+      <c r="J83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K83" s="3">
         <v>4600</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L83" s="3">
+      <c r="L83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M83" s="3">
         <v>4600</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
-      </c>
       <c r="N83" s="3">
         <v>0</v>
       </c>
@@ -4879,8 +5078,11 @@
       <c r="V83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4941,8 +5143,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5003,8 +5208,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5065,8 +5273,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5127,8 +5338,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5189,70 +5403,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E89" s="3">
+        <v>0</v>
+      </c>
+      <c r="F89" s="3">
         <v>-4300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-3700</v>
       </c>
-      <c r="H89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I89" s="3">
+      <c r="I89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J89" s="3">
         <v>-4200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-12400</v>
       </c>
-      <c r="K89" s="3">
-        <v>0</v>
-      </c>
       <c r="L89" s="3">
+        <v>0</v>
+      </c>
+      <c r="M89" s="3">
         <v>-12400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-13500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-5000</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P89" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Q89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R89" s="3">
+      <c r="R89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S89" s="3">
         <v>-25900</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U89" s="3">
-        <v>0</v>
+      <c r="U89" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5275,8 +5495,9 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5307,8 +5528,8 @@
       <c r="L91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
+      <c r="M91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -5337,8 +5558,11 @@
       <c r="V91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5399,8 +5623,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5461,59 +5688,62 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>1800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>1100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1000</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I94" s="3">
+      <c r="I94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J94" s="3">
         <v>8700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>7300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>1900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>7300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-13200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-59600</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P94" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R94" s="3">
+      <c r="R94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S94" s="3">
         <v>-30400</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T94" s="3" t="s">
         <v>4</v>
       </c>
@@ -5523,8 +5753,11 @@
       <c r="V94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5547,8 +5780,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5579,8 +5813,8 @@
       <c r="L96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -5609,8 +5843,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5671,8 +5908,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5733,8 +5973,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5795,59 +6038,62 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E100" s="3">
         <v>6100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>4000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>3600</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I100" s="3">
+      <c r="I100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J100" s="3">
         <v>23500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>23900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-18700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>23900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>5200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>77800</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P100" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Q100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R100" s="3">
+      <c r="R100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S100" s="3">
         <v>51000</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>4</v>
       </c>
@@ -5857,128 +6103,137 @@
       <c r="V100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E101" s="3">
+      <c r="D101" s="3">
+        <v>200</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F101" s="3">
         <v>100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>100</v>
       </c>
-      <c r="I101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J101" s="3">
+      <c r="J101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K101" s="3">
         <v>-400</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L101" s="3">
+      <c r="L101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M101" s="3">
         <v>-400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>1300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>100</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P101" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Q101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R101" s="3">
+      <c r="R101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S101" s="3">
         <v>-200</v>
       </c>
-      <c r="S101" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
+      <c r="U101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E102" s="3">
         <v>3700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>4000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-900</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
       <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>28300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>18300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-15000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>18300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-20200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>13400</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P102" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Q102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R102" s="3">
+      <c r="R102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S102" s="3">
         <v>-5600</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U102" s="3">
-        <v>0</v>
+      <c r="U102" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V102" s="3">
+        <v>0</v>
+      </c>
+      <c r="W102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/THCH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/THCH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="92">
   <si>
     <t>THCH</t>
   </si>
@@ -656,301 +656,313 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45747</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45565</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45107</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45016</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44926</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44834</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44742</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44651</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44561</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44469</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44377</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44286</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44196</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>44100</v>
+      </c>
+      <c r="E8" s="3">
         <v>50300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>41400</v>
       </c>
-      <c r="F8" s="3">
-        <v>45600</v>
-      </c>
-      <c r="G8" s="3">
+      <c r="G8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H8" s="3">
         <v>51300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>46000</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="J8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K8" s="3">
         <v>59500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>49000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>56800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>49000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>42500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>42200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>24900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>31200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>30900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>25100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>19300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>14600</v>
       </c>
-      <c r="V8" s="3">
-        <v>0</v>
-      </c>
       <c r="W8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>27400</v>
+      </c>
+      <c r="E9" s="3">
         <v>29000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>27200</v>
       </c>
-      <c r="F9" s="3">
-        <v>28800</v>
-      </c>
-      <c r="G9" s="3">
+      <c r="G9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H9" s="3">
         <v>30100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>34000</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J9" s="3">
+      <c r="J9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K9" s="3">
         <v>41600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>39000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>40500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>39000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>15700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>14700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>9300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>10900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>10800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>9000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>6700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>4900</v>
       </c>
-      <c r="V9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>16700</v>
+      </c>
+      <c r="E10" s="3">
         <v>21300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>14200</v>
       </c>
-      <c r="F10" s="3">
-        <v>16700</v>
-      </c>
-      <c r="G10" s="3">
+      <c r="G10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H10" s="3">
         <v>21200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>12000</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="J10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K10" s="3">
         <v>17800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>10000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>16300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>10000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>26800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>27600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>15600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>20300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>20100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>16100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>12600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>9700</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -974,8 +986,9 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1039,8 +1052,11 @@
       <c r="W12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1104,73 +1120,79 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>19600</v>
+      </c>
+      <c r="E14" s="3">
         <v>2200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-2100</v>
       </c>
-      <c r="F14" s="3">
-        <v>4600</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="3">
         <v>6400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>4700</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K14" s="3">
         <v>3900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>2900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>200</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>300</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>100</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
         <v>0</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>4</v>
+      <c r="V14" s="3">
+        <v>0</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1178,25 +1200,25 @@
         <v>3700</v>
       </c>
       <c r="E15" s="3">
+        <v>3700</v>
+      </c>
+      <c r="F15" s="3">
         <v>3900</v>
       </c>
-      <c r="F15" s="3">
-        <v>4900</v>
-      </c>
       <c r="G15" s="3">
+        <v>6300</v>
+      </c>
+      <c r="H15" s="3">
         <v>4200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>4600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>6200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>5000</v>
-      </c>
-      <c r="K15" s="3">
-        <v>4800</v>
       </c>
       <c r="L15" s="3">
         <v>4800</v>
@@ -1205,11 +1227,11 @@
         <v>4800</v>
       </c>
       <c r="N15" s="3">
+        <v>4800</v>
+      </c>
+      <c r="O15" s="3">
         <v>16700</v>
       </c>
-      <c r="O15" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P15" s="3" t="s">
         <v>4</v>
       </c>
@@ -1222,8 +1244,8 @@
       <c r="S15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T15" s="3">
-        <v>0</v>
+      <c r="T15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U15" s="3">
         <v>0</v>
@@ -1234,8 +1256,11 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1256,138 +1281,145 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>56400</v>
+      </c>
+      <c r="E17" s="3">
         <v>58100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>51200</v>
       </c>
-      <c r="F17" s="3">
-        <v>59400</v>
-      </c>
-      <c r="G17" s="3">
+      <c r="G17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H17" s="3">
         <v>56900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>59900</v>
       </c>
-      <c r="I17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="J17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K17" s="3">
         <v>76300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>67200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>80700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>67200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>61000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>63000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>47800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>50000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>48800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>40700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>29700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>23000</v>
       </c>
-      <c r="V17" s="3">
-        <v>0</v>
-      </c>
       <c r="W17" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-12300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-7800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-9800</v>
       </c>
-      <c r="F18" s="3">
-        <v>-13800</v>
-      </c>
-      <c r="G18" s="3">
+      <c r="G18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H18" s="3">
         <v>-5600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-13900</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="J18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K18" s="3">
         <v>-16800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-18200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-23900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-18200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-18500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-20800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-22900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-18700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-17900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-15600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-10400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-8500</v>
       </c>
-      <c r="V18" s="3">
-        <v>0</v>
-      </c>
       <c r="W18" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1411,8 +1443,9 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1420,100 +1453,103 @@
         <v>100</v>
       </c>
       <c r="E20" s="3">
+        <v>100</v>
+      </c>
+      <c r="F20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3">
-        <v>100</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
+      <c r="G20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>-500</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="J20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K20" s="3">
         <v>-100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>4000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>5300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>4000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-12300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-5600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-800</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>-500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>400</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-4100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-5800</v>
       </c>
-      <c r="F21" s="3">
-        <v>-9000</v>
-      </c>
       <c r="G21" s="3">
+        <v>6300</v>
+      </c>
+      <c r="H21" s="3">
         <v>-1400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-8700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>6200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-11700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-17400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-24500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-17400</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1541,8 +1577,11 @@
       <c r="W21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1550,31 +1589,31 @@
         <v>600</v>
       </c>
       <c r="E22" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="F22" s="3">
         <v>500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="G22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H22" s="3">
         <v>600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>800</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J22" s="3">
-        <v>600</v>
+      <c r="J22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K22" s="3">
         <v>600</v>
       </c>
       <c r="L22" s="3">
+        <v>600</v>
+      </c>
+      <c r="M22" s="3">
         <v>700</v>
-      </c>
-      <c r="M22" s="3">
-        <v>600</v>
       </c>
       <c r="N22" s="3">
         <v>600</v>
@@ -1583,17 +1622,17 @@
         <v>600</v>
       </c>
       <c r="P22" s="3">
+        <v>600</v>
+      </c>
+      <c r="Q22" s="3">
         <v>500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>200</v>
       </c>
-      <c r="S22" s="3">
-        <v>0</v>
-      </c>
       <c r="T22" s="3">
         <v>0</v>
       </c>
@@ -1606,91 +1645,97 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-32500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-10400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-8100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H23" s="3">
+        <v>-12400</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-18700</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K23" s="3">
+        <v>-20200</v>
+      </c>
+      <c r="L23" s="3">
+        <v>-25400</v>
+      </c>
+      <c r="M23" s="3">
+        <v>-31400</v>
+      </c>
+      <c r="N23" s="3">
+        <v>-25400</v>
+      </c>
+      <c r="O23" s="3">
+        <v>-31400</v>
+      </c>
+      <c r="P23" s="3">
+        <v>-26900</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>-24400</v>
+      </c>
+      <c r="R23" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="S23" s="3">
         <v>-18900</v>
       </c>
-      <c r="G23" s="3">
-        <v>-12400</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-18700</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J23" s="3">
-        <v>-20200</v>
-      </c>
-      <c r="K23" s="3">
-        <v>-25400</v>
-      </c>
-      <c r="L23" s="3">
-        <v>-31400</v>
-      </c>
-      <c r="M23" s="3">
-        <v>-25400</v>
-      </c>
-      <c r="N23" s="3">
-        <v>-31400</v>
-      </c>
-      <c r="O23" s="3">
-        <v>-26900</v>
-      </c>
-      <c r="P23" s="3">
-        <v>-24400</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>-21000</v>
-      </c>
-      <c r="R23" s="3">
-        <v>-18900</v>
-      </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-15600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-10900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-8100</v>
       </c>
-      <c r="V23" s="3">
-        <v>0</v>
-      </c>
       <c r="W23" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>4</v>
+      <c r="D24" s="3">
+        <v>0</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F24" s="3">
+      <c r="F24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H24" s="3">
         <v>100</v>
       </c>
-      <c r="G24" s="3">
-        <v>100</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I24" s="3" t="s">
         <v>4</v>
       </c>
@@ -1706,8 +1751,8 @@
       <c r="M24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
+      <c r="N24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O24" s="3">
         <v>0</v>
@@ -1736,8 +1781,11 @@
       <c r="W24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1801,138 +1849,147 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-32500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-10400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-8100</v>
       </c>
-      <c r="F26" s="3">
-        <v>-19000</v>
-      </c>
-      <c r="G26" s="3">
+      <c r="G26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H26" s="3">
         <v>-12500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-18700</v>
       </c>
-      <c r="I26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="J26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K26" s="3">
         <v>-20200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-25400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-31400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-25400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-31400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-26900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-24400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-21000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-18900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-15600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-10900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-8100</v>
       </c>
-      <c r="V26" s="3">
-        <v>0</v>
-      </c>
       <c r="W26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-32600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-10200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-8000</v>
       </c>
-      <c r="F27" s="3">
-        <v>-18900</v>
-      </c>
-      <c r="G27" s="3">
+      <c r="G27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H27" s="3">
         <v>-12700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-19900</v>
       </c>
-      <c r="I27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J27" s="3">
+      <c r="J27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K27" s="3">
         <v>-22000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-25500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-31500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-25500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-31600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-26900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-24200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-20900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-19100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-15300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-10900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-8000</v>
       </c>
-      <c r="V27" s="3">
-        <v>0</v>
-      </c>
       <c r="W27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1996,8 +2053,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2014,28 +2074,28 @@
         <v>0</v>
       </c>
       <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
         <v>-1100</v>
       </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
       <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>-1700</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
       <c r="L29" s="3">
         <v>0</v>
       </c>
       <c r="M29" s="3">
         <v>0</v>
       </c>
-      <c r="N29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O29" s="3">
-        <v>0</v>
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P29" s="3">
         <v>0</v>
@@ -2061,8 +2121,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2126,8 +2189,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2191,8 +2257,11 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2200,129 +2269,135 @@
         <v>-100</v>
       </c>
       <c r="E32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
+      <c r="G32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>500</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="J32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K32" s="3">
         <v>100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-4000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-5300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-4000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>12300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>5600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>800</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-400</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-32600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-10200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-8000</v>
       </c>
-      <c r="F33" s="3">
-        <v>-18900</v>
-      </c>
-      <c r="G33" s="3">
+      <c r="G33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H33" s="3">
         <v>-12700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-19900</v>
       </c>
-      <c r="I33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J33" s="3">
+      <c r="J33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K33" s="3">
         <v>-22000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-25500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-31500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-25500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-31600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-26900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-24200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-20900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-19100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-15300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-10900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-8000</v>
       </c>
-      <c r="V33" s="3">
-        <v>0</v>
-      </c>
       <c r="W33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2386,143 +2461,152 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-32600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-10200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-8000</v>
       </c>
-      <c r="F35" s="3">
-        <v>-18900</v>
-      </c>
-      <c r="G35" s="3">
+      <c r="G35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H35" s="3">
         <v>-12700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-19900</v>
       </c>
-      <c r="I35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J35" s="3">
+      <c r="J35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K35" s="3">
         <v>-22000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-25500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-31500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-25500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-31600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-26900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-24200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-20900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-19100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-15300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-10900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-8000</v>
       </c>
-      <c r="V35" s="3">
-        <v>0</v>
-      </c>
       <c r="W35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45747</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45565</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45107</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45016</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44926</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44834</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44742</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44651</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44561</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44469</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44377</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44286</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44196</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2546,8 +2630,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2571,56 +2656,57 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>17400</v>
+      </c>
+      <c r="E41" s="3">
         <v>18500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>25400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>20900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>28000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>27300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>28500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>63300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>53100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>35200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>53100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>33700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>52800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>39600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>54300</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>4</v>
       </c>
@@ -2636,50 +2722,53 @@
       <c r="W41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="E42" s="3">
         <v>0</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>1200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>3300</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>37000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>18800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>37000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>52500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>52200</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q42" s="3" t="s">
         <v>4</v>
       </c>
@@ -2695,62 +2784,65 @@
       <c r="U42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V42" s="3">
-        <v>0</v>
+      <c r="V42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>18500</v>
+      </c>
+      <c r="E43" s="3">
         <v>2900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>23400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>5900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>22300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>14400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>14400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>12100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>9300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>10800</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>4</v>
       </c>
@@ -2760,40 +2852,43 @@
       <c r="U43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V43" s="3">
-        <v>0</v>
+      <c r="V43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E44" s="3">
         <v>5700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>4700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>5100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>5000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>5600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>7000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>10200</v>
-      </c>
-      <c r="K44" s="3">
-        <v>10400</v>
       </c>
       <c r="L44" s="3">
         <v>10400</v>
@@ -2802,20 +2897,20 @@
         <v>10400</v>
       </c>
       <c r="N44" s="3">
+        <v>10400</v>
+      </c>
+      <c r="O44" s="3">
         <v>10100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>7200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>7700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>5900</v>
       </c>
-      <c r="R44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S44" s="3" t="s">
         <v>4</v>
       </c>
@@ -2825,62 +2920,65 @@
       <c r="U44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V44" s="3">
-        <v>0</v>
+      <c r="V44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>4</v>
+      <c r="D45" s="3">
+        <v>1700</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F45" s="3">
+      <c r="F45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G45" s="3">
         <v>1400</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J45" s="3">
         <v>2700</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L45" s="3">
         <v>2600</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N45" s="3">
         <v>2600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>16300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>13300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>10400</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>4</v>
       </c>
@@ -2890,62 +2988,65 @@
       <c r="U45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V45" s="3">
+      <c r="V45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W45" s="3">
         <v>200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>46700</v>
+      </c>
+      <c r="E46" s="3">
         <v>55700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>59800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>57100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>63000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>62400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>64700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>96400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>118200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>87200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>118200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>112300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>129600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>70000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>81500</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>4</v>
       </c>
@@ -2955,14 +3056,17 @@
       <c r="U46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V46" s="3">
+      <c r="V46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W46" s="3">
         <v>200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2996,8 +3100,8 @@
       <c r="M47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N47" s="3">
-        <v>0</v>
+      <c r="N47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O47" s="3">
         <v>0</v>
@@ -3020,62 +3124,65 @@
       <c r="U47" s="3">
         <v>0</v>
       </c>
-      <c r="V47" s="3" t="s">
-        <v>4</v>
+      <c r="V47" s="3">
+        <v>0</v>
       </c>
       <c r="W47" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>97400</v>
+      </c>
+      <c r="E48" s="3">
         <v>106800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>125500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>136400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>152900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>190800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>204700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>231000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>241200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>234200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>241200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>235000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>88000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>81100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>77000</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>4</v>
       </c>
@@ -3085,62 +3192,65 @@
       <c r="U48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V48" s="3">
-        <v>0</v>
+      <c r="V48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>11600</v>
+      </c>
+      <c r="E49" s="3">
         <v>12100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>12700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>13300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>14500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>20200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>15600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>18800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>19100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>18600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>19100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>13500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>11900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>11200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>10800</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S49" s="3" t="s">
         <v>4</v>
       </c>
@@ -3150,14 +3260,17 @@
       <c r="U49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V49" s="3">
-        <v>0</v>
+      <c r="V49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3221,8 +3334,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3286,56 +3402,59 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E52" s="3">
         <v>6700</v>
-      </c>
-      <c r="E52" s="3">
-        <v>7400</v>
       </c>
       <c r="F52" s="3">
         <v>7400</v>
       </c>
       <c r="G52" s="3">
+        <v>7400</v>
+      </c>
+      <c r="H52" s="3">
         <v>8600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>9000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>27400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>11200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>11700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>11500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>11700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>11600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>10900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>9700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>9400</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>4</v>
       </c>
@@ -3351,8 +3470,11 @@
       <c r="W52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3416,56 +3538,59 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>168200</v>
+      </c>
+      <c r="E54" s="3">
         <v>181300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>205300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>214200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>239000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>282500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>312400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>357300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>390100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>351600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>390100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>372500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>240300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>172000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>178600</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>4</v>
       </c>
@@ -3475,14 +3600,17 @@
       <c r="U54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V54" s="3">
+      <c r="V54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W54" s="3">
         <v>200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3506,8 +3634,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3531,56 +3660,57 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>29300</v>
+      </c>
+      <c r="E57" s="3">
         <v>28100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>30800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>33500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>29000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>35500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>31600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>28400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>16800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>23800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>16800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>16200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>12700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>8100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>9600</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>4</v>
       </c>
@@ -3596,56 +3726,59 @@
       <c r="W57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>82300</v>
+      </c>
+      <c r="E58" s="3">
         <v>155800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>151000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>141500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>144600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>86900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>102700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>118000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>91900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>82200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>91900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>57500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>50300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>59300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>26700</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>4</v>
       </c>
@@ -3655,62 +3788,65 @@
       <c r="U58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V58" s="3">
+      <c r="V58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W58" s="3">
         <v>100</v>
       </c>
-      <c r="W58" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>17200</v>
+      </c>
+      <c r="E59" s="3">
         <v>43100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>39200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>23300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>37100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>79200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>44300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>57800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>51200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>64200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>51200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>112200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>69100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>44300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>42600</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>4</v>
       </c>
@@ -3720,62 +3856,65 @@
       <c r="U59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V59" s="3">
-        <v>100</v>
+      <c r="V59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W59" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>143300</v>
+      </c>
+      <c r="E60" s="3">
         <v>227000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>221000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>210400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>210700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>201600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>196800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>204200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>183500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>170300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>183500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>185800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>132000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>111700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>78900</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>4</v>
       </c>
@@ -3785,62 +3924,65 @@
       <c r="U60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V60" s="3">
+      <c r="V60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W60" s="3">
         <v>200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>199200</v>
+      </c>
+      <c r="E61" s="3">
         <v>96800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>104800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>115800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>123600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>144200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>152300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>162100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>169200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>166800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>169200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>51200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>50700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>50800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>45900</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -3856,16 +3998,19 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E62" s="3">
         <v>1000</v>
-      </c>
-      <c r="E62" s="3">
-        <v>1100</v>
       </c>
       <c r="F62" s="3">
         <v>1100</v>
@@ -3874,38 +4019,38 @@
         <v>1100</v>
       </c>
       <c r="H62" s="3">
+        <v>1100</v>
+      </c>
+      <c r="I62" s="3">
         <v>14500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>22200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>9800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>22000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>10800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>22000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>119900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>15600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>7700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>6700</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>4</v>
       </c>
@@ -3921,8 +4066,11 @@
       <c r="W62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3986,8 +4134,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4051,8 +4202,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4116,56 +4270,59 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>345000</v>
+      </c>
+      <c r="E66" s="3">
         <v>326200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>327900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>328300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>336300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>361000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>372000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>376800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>375200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>348400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>375200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>357100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>198400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>170400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>132000</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>4</v>
       </c>
@@ -4175,14 +4332,17 @@
       <c r="U66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V66" s="3">
+      <c r="V66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W66" s="3">
         <v>200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4206,8 +4366,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4271,8 +4432,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4336,8 +4500,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4401,8 +4568,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4466,56 +4636,59 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-443600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-403800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-375700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-365600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-361700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-332500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-318200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-266500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-226400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-246000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-226400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-194600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-159800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-133700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-88600</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>4</v>
       </c>
@@ -4525,14 +4698,17 @@
       <c r="U72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V72" s="3">
-        <v>0</v>
+      <c r="V72" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4596,8 +4772,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4661,8 +4840,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4726,56 +4908,59 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-177700</v>
+      </c>
+      <c r="E76" s="3">
         <v>-145700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-123500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-115200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-98600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-79400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-60200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-20000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>14600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>14600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>15300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>41900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>46600</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>4</v>
       </c>
@@ -4785,14 +4970,17 @@
       <c r="U76" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V76" s="3">
-        <v>0</v>
+      <c r="V76" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W76" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4856,143 +5044,152 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45747</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45565</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45107</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45016</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44926</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44834</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44742</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44651</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44561</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44469</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44377</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44286</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44196</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-32600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-10200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-8000</v>
       </c>
-      <c r="F81" s="3">
-        <v>-18900</v>
-      </c>
-      <c r="G81" s="3">
+      <c r="G81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H81" s="3">
         <v>-12700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-19900</v>
       </c>
-      <c r="I81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J81" s="3">
+      <c r="J81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K81" s="3">
         <v>-22000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-25500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-31500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-25500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-31600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-26900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-24200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-20900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-19100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-15300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-10900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-8000</v>
       </c>
-      <c r="V81" s="3">
-        <v>0</v>
-      </c>
       <c r="W81" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5016,44 +5213,45 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E83" s="3">
         <v>5800</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F83" s="3">
-        <v>5600</v>
+      <c r="F83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G83" s="3">
         <v>5600</v>
       </c>
       <c r="H83" s="3">
+        <v>5600</v>
+      </c>
+      <c r="I83" s="3">
         <v>4200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>5100</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K83" s="3">
+      <c r="K83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L83" s="3">
         <v>4600</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M83" s="3">
+      <c r="M83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N83" s="3">
         <v>4600</v>
       </c>
-      <c r="N83" s="3">
-        <v>0</v>
-      </c>
       <c r="O83" s="3">
         <v>0</v>
       </c>
@@ -5081,8 +5279,11 @@
       <c r="W83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5146,8 +5347,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5211,8 +5415,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5276,8 +5483,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5341,8 +5551,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5406,73 +5619,79 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-200</v>
       </c>
-      <c r="E89" s="3">
-        <v>0</v>
-      </c>
       <c r="F89" s="3">
-        <v>-4300</v>
-      </c>
-      <c r="G89" s="3">
+        <v>0</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H89" s="3">
         <v>-1900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-3700</v>
       </c>
-      <c r="I89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J89" s="3">
+      <c r="J89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K89" s="3">
         <v>-4200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-12400</v>
       </c>
-      <c r="L89" s="3">
-        <v>0</v>
-      </c>
       <c r="M89" s="3">
+        <v>0</v>
+      </c>
+      <c r="N89" s="3">
         <v>-12400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-13500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-5000</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S89" s="3">
+      <c r="S89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T89" s="3">
         <v>-25900</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V89" s="3">
-        <v>0</v>
+      <c r="V89" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5496,13 +5715,14 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>4</v>
+      <c r="D91" s="3">
+        <v>-9400</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>4</v>
@@ -5531,8 +5751,8 @@
       <c r="M91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
+      <c r="N91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O91" s="3">
         <v>0</v>
@@ -5561,8 +5781,11 @@
       <c r="W91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5626,8 +5849,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5691,62 +5917,65 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2300</v>
       </c>
-      <c r="F94" s="3">
-        <v>1800</v>
-      </c>
-      <c r="G94" s="3">
+      <c r="G94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H94" s="3">
         <v>1100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1000</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J94" s="3">
+      <c r="J94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K94" s="3">
         <v>8700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>7300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>1900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>7300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-13200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-59600</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q94" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S94" s="3">
+      <c r="S94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T94" s="3">
         <v>-30400</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>4</v>
       </c>
@@ -5756,8 +5985,11 @@
       <c r="W94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5781,8 +6013,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5816,8 +6049,8 @@
       <c r="M96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
+      <c r="N96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O96" s="3">
         <v>0</v>
@@ -5846,8 +6079,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5911,8 +6147,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5976,8 +6215,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6041,62 +6283,65 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>6100</v>
       </c>
-      <c r="F100" s="3">
-        <v>1300</v>
-      </c>
-      <c r="G100" s="3">
+      <c r="G100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H100" s="3">
         <v>4000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>3600</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="J100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K100" s="3">
         <v>23500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>23900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-18700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>23900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>5200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>77800</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S100" s="3">
+      <c r="S100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T100" s="3">
         <v>51000</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>4</v>
       </c>
@@ -6106,134 +6351,143 @@
       <c r="W100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>800</v>
+      </c>
+      <c r="E101" s="3">
         <v>200</v>
       </c>
-      <c r="E101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F101" s="3">
+      <c r="F101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G101" s="3">
         <v>100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>1400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>100</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K101" s="3">
+      <c r="K101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L101" s="3">
         <v>-400</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M101" s="3">
+      <c r="M101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N101" s="3">
         <v>-400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>1300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>100</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q101" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S101" s="3">
+      <c r="S101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T101" s="3">
         <v>-200</v>
       </c>
-      <c r="T101" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
+      <c r="V101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>3700</v>
       </c>
-      <c r="F102" s="3">
-        <v>-1700</v>
-      </c>
       <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
         <v>4000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-900</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>28300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>18300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-15000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>18300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-20200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>13400</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q102" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S102" s="3">
+      <c r="S102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T102" s="3">
         <v>-5600</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V102" s="3">
-        <v>0</v>
+      <c r="V102" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W102" s="3">
+        <v>0</v>
+      </c>
+      <c r="X102" s="3">
         <v>0</v>
       </c>
     </row>
